--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
-    <sheet name="特殊装备" sheetId="7" r:id="rId2"/>
-    <sheet name="技能书" sheetId="8" r:id="rId3"/>
-    <sheet name="珍宝" sheetId="4" r:id="rId4"/>
+    <sheet name="宠物" sheetId="9" r:id="rId2"/>
+    <sheet name="特殊装备" sheetId="7" r:id="rId3"/>
+    <sheet name="技能书" sheetId="8" r:id="rId4"/>
+    <sheet name="珍宝" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -204,6 +205,64 @@
       <text>
         <r>
           <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 普通道具
+2，装备
+3，技能书
+5，材料
+6，buff</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+格式为</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
@@ -244,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="190">
   <si>
     <t>_id</t>
   </si>
@@ -313,6 +372,429 @@
   </si>
   <si>
     <t>210001,220001,230001</t>
+  </si>
+  <si>
+    <t>狼宝宝</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>骷髅宝宝</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>兽人宝宝</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>蜘蛛宝宝</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>岩蝎宝宝</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>鬃狮宝宝</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>毒蛆宝宝</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>蜈蚣宝宝</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>双头宝宝</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>蛛王宝宝</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>蛇宝宝</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>巨鳄宝宝</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>乌鸦宝宝</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>行尸宝宝</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>尸鬼宝宝</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>蝙蝠宝宝</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>尸魔宝宝</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>尸卫宝宝</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>花妖宝宝</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>树精宝宝</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>鱼人宝宝</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>狼人宝宝</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>蠕虫宝宝</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>角鹿宝宝</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>恶犬宝宝</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>守卫宝宝</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>射手宝宝</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>幽灵宝宝</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>法师宝宝</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>骸骨宝宝</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>战猪宝宝</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>勇猪宝宝</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>力猪宝宝</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>萨满宝宝</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>战将宝宝</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>亲卫宝宝</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>花宝宝</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>甲虫宝宝</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>火蛇宝宝</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>赤炎宝宝</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>魔姬宝宝</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>炎魔宝宝</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>冰蝎宝宝</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>寒冰宝宝</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>龙龟宝宝</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>霜骑宝宝</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>巨霜宝宝</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>鬼蛛宝宝</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>蛇姬宝宝</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>巨蜥宝宝</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>暗夜宝宝</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>祭司宝宝</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>女骑宝宝</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>人马宝宝</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>巨熊宝宝</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>屠戮宝宝</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>牛头宝宝</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>蛮卫宝宝</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>魔瞳宝宝</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>收割宝宝</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>血魔宝宝</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>恶魔宝宝</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>黑骑宝宝</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>巫师宝宝</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>三头宝宝</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>女巫宝宝</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>魇兽宝宝</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>大魔宝宝</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>领主宝宝</t>
+  </si>
+  <si>
+    <t>72</t>
   </si>
   <si>
     <t>一阶四格</t>
@@ -1045,7 +1527,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1069,6 +1551,17 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1078,6 +1571,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1466,7 +1960,7 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="15" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1480,7 +1974,7 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="15" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1494,7 +1988,7 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="15" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1508,7 +2002,7 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="15" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1522,7 +2016,7 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="15" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1536,7 +2030,7 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="16" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1556,8 +2050,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="C1:F77"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
@@ -1616,17 +2110,1011 @@
       </c>
     </row>
     <row r="6" s="6" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="6">
-        <v>30001</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="9">
+        <v>180001</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="6">
-        <v>3</v>
-      </c>
-      <c r="F6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:6">
+      <c r="C7" s="9">
+        <v>180002</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="6">
+        <v>18</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:6">
+      <c r="C8" s="9">
+        <v>180003</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="6">
+        <v>18</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:6">
+      <c r="C9" s="9">
+        <v>180004</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="6">
+        <v>18</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:6">
+      <c r="C10" s="9">
+        <v>180005</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="6">
+        <v>18</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:6">
+      <c r="C11" s="9">
+        <v>180006</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="6">
+        <v>18</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:6">
+      <c r="C12" s="9">
+        <v>180007</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="6">
+        <v>18</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:6">
+      <c r="C13" s="9">
+        <v>180008</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="6">
+        <v>18</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:6">
+      <c r="C14" s="9">
+        <v>180009</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="6">
+        <v>18</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:6">
+      <c r="C15" s="9">
+        <v>180010</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="6">
+        <v>18</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:6">
+      <c r="C16" s="9">
+        <v>180011</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="6">
+        <v>18</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:6">
+      <c r="C17" s="9">
+        <v>180012</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="6">
+        <v>18</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:6">
+      <c r="C18" s="9">
+        <v>180013</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="6">
+        <v>18</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:6">
+      <c r="C19" s="9">
+        <v>180014</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="6">
+        <v>18</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:6">
+      <c r="C20" s="9">
+        <v>180015</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="6">
+        <v>18</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:6">
+      <c r="C21" s="9">
+        <v>180016</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="6">
+        <v>18</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:6">
+      <c r="C22" s="9">
+        <v>180017</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="6">
+        <v>18</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:6">
+      <c r="C23" s="9">
+        <v>180018</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E23" s="6">
+        <v>18</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:6">
+      <c r="C24" s="9">
+        <v>180019</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="6">
+        <v>18</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:6">
+      <c r="C25" s="9">
+        <v>180020</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="6">
+        <v>18</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:6">
+      <c r="C26" s="9">
+        <v>180021</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" s="6">
+        <v>18</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:6">
+      <c r="C27" s="9">
+        <v>180022</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="6">
+        <v>18</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:6">
+      <c r="C28" s="9">
+        <v>180023</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" s="6">
+        <v>18</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:6">
+      <c r="C29" s="9">
+        <v>180024</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="6">
+        <v>18</v>
+      </c>
+      <c r="F29" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:6">
+      <c r="C30" s="9">
+        <v>180025</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="6">
+        <v>18</v>
+      </c>
+      <c r="F30" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:6">
+      <c r="C31" s="9">
+        <v>180026</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="6">
+        <v>18</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:6">
+      <c r="C32" s="9">
+        <v>180027</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" s="6">
+        <v>18</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:6">
+      <c r="C33" s="9">
+        <v>180028</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="6">
+        <v>18</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:6">
+      <c r="C34" s="9">
+        <v>180029</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="6">
+        <v>18</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:6">
+      <c r="C35" s="9">
+        <v>180030</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="6">
+        <v>18</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:6">
+      <c r="C36" s="9">
+        <v>180031</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="6">
+        <v>18</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:6">
+      <c r="C37" s="9">
+        <v>180032</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E37" s="6">
+        <v>18</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:6">
+      <c r="C38" s="9">
+        <v>180033</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" s="6">
+        <v>18</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:6">
+      <c r="C39" s="9">
+        <v>180034</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="6">
+        <v>18</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:6">
+      <c r="C40" s="9">
+        <v>180035</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="6">
+        <v>18</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:6">
+      <c r="C41" s="9">
+        <v>180036</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="6">
+        <v>18</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:6">
+      <c r="C42" s="9">
+        <v>180037</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E42" s="6">
+        <v>18</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:6">
+      <c r="C43" s="9">
+        <v>180038</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E43" s="6">
+        <v>18</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:6">
+      <c r="C44" s="9">
+        <v>180039</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" s="6">
+        <v>18</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:6">
+      <c r="C45" s="9">
+        <v>180040</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E45" s="6">
+        <v>18</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:6">
+      <c r="C46" s="9">
+        <v>180041</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="6">
+        <v>18</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:6">
+      <c r="C47" s="9">
+        <v>180042</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E47" s="6">
+        <v>18</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:6">
+      <c r="C48" s="9">
+        <v>180043</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E48" s="6">
+        <v>18</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:6">
+      <c r="C49" s="9">
+        <v>180044</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E49" s="6">
+        <v>18</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:6">
+      <c r="C50" s="9">
+        <v>180045</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E50" s="6">
+        <v>18</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:6">
+      <c r="C51" s="9">
+        <v>180046</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E51" s="6">
+        <v>18</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:6">
+      <c r="C52" s="9">
+        <v>180047</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E52" s="6">
+        <v>18</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:6">
+      <c r="C53" s="9">
+        <v>180048</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E53" s="6">
+        <v>18</v>
+      </c>
+      <c r="F53" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:6">
+      <c r="C54" s="9">
+        <v>180049</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" s="6">
+        <v>18</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:6">
+      <c r="C55" s="9">
+        <v>180050</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55" s="6">
+        <v>18</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:6">
+      <c r="C56" s="9">
+        <v>180051</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="E56" s="6">
+        <v>18</v>
+      </c>
+      <c r="F56" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:6">
+      <c r="C57" s="9">
+        <v>180052</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E57" s="6">
+        <v>18</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:6">
+      <c r="C58" s="9">
+        <v>180053</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" s="6">
+        <v>18</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:6">
+      <c r="C59" s="9">
+        <v>180054</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="E59" s="6">
+        <v>18</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:6">
+      <c r="C60" s="9">
+        <v>180055</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E60" s="6">
+        <v>18</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:6">
+      <c r="C61" s="9">
+        <v>180056</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E61" s="6">
+        <v>18</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:6">
+      <c r="C62" s="9">
+        <v>180057</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" s="6">
+        <v>18</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:6">
+      <c r="C63" s="9">
+        <v>180058</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="E63" s="6">
+        <v>18</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:6">
+      <c r="C64" s="9">
+        <v>180059</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="E64" s="6">
+        <v>18</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:6">
+      <c r="C65" s="9">
+        <v>180060</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E65" s="6">
+        <v>18</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:6">
+      <c r="C66" s="9">
+        <v>180061</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E66" s="6">
+        <v>18</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:6">
+      <c r="C67" s="9">
+        <v>180062</v>
+      </c>
+      <c r="D67" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E67" s="6">
+        <v>18</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:6">
+      <c r="C68" s="9">
+        <v>180063</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E68" s="6">
+        <v>18</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:6">
+      <c r="C69" s="9">
+        <v>180064</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E69" s="6">
+        <v>18</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:6">
+      <c r="C70" s="9">
+        <v>180065</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E70" s="6">
+        <v>18</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:6">
+      <c r="C71" s="9">
+        <v>180066</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E71" s="6">
+        <v>18</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:6">
+      <c r="C72" s="9">
+        <v>180067</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="E72" s="6">
+        <v>18</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:6">
+      <c r="C73" s="9">
+        <v>180068</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E73" s="6">
+        <v>18</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:6">
+      <c r="C74" s="9">
+        <v>180069</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E74" s="6">
+        <v>18</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:6">
+      <c r="C75" s="9">
+        <v>180070</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E75" s="6">
+        <v>18</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:6">
+      <c r="C76" s="9">
+        <v>180071</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E76" s="6">
+        <v>18</v>
+      </c>
+      <c r="F76" s="17" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:6">
+      <c r="C77" s="9">
+        <v>180072</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E77" s="6">
+        <v>18</v>
+      </c>
+      <c r="F77" s="17" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -1642,6 +3130,97 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:F22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.0833333333333" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="6" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="6">
+        <v>30001</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="6">
+        <v>3</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
+      <c r="C22" s="9"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:F32"/>
@@ -1709,13 +3288,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>26</v>
+      <c r="F6" s="18" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -1723,13 +3302,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>168</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>28</v>
+      <c r="F7" s="18" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -1737,13 +3316,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>30</v>
+      <c r="F8" s="18" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -1751,13 +3330,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>32</v>
+      <c r="F9" s="18" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -1765,13 +3344,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="12" t="s">
-        <v>34</v>
+      <c r="F10" s="18" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -1779,13 +3358,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="12" t="s">
-        <v>36</v>
+      <c r="F11" s="18" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -1793,13 +3372,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>37</v>
+        <v>178</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
-      <c r="F12" s="12" t="s">
-        <v>38</v>
+      <c r="F12" s="18" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -1807,13 +3386,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="13" t="s">
-        <v>40</v>
+      <c r="F13" s="19" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -1821,13 +3400,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>42</v>
+      <c r="F14" s="19" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -1869,7 +3448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G21"/>
@@ -1936,7 +3515,7 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -1950,7 +3529,7 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -1964,7 +3543,7 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -1978,7 +3557,7 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>46</v>
+        <v>187</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -1992,7 +3571,7 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -2008,7 +3587,7 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>48</v>
+        <v>189</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -303,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="250">
   <si>
     <t>_id</t>
   </si>
@@ -338,40 +338,220 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>0级链头</t>
+    <t>1级链头</t>
   </si>
   <si>
     <t>210003,220003,230003,210004,220004,230004</t>
   </si>
   <si>
-    <t>0级手镯</t>
+    <t>1级手镯</t>
   </si>
   <si>
     <t>210005,220005,230005</t>
   </si>
   <si>
-    <t>0级戒指</t>
+    <t>1级戒指</t>
   </si>
   <si>
     <t>210006,220006,230006</t>
   </si>
   <si>
-    <t>0级腰鞋</t>
+    <t>1级腰鞋</t>
   </si>
   <si>
     <t>210007,220007,230007,210008,220008,230008</t>
   </si>
   <si>
-    <t>0级衣服</t>
+    <t>1级衣服</t>
   </si>
   <si>
     <t>210002,220002,230002</t>
   </si>
   <si>
-    <t>0级武器</t>
+    <t>1级武器</t>
   </si>
   <si>
     <t>210001,220001,230001</t>
+  </si>
+  <si>
+    <t>10级链头</t>
+  </si>
+  <si>
+    <t>210013,220013,230013,210014,220014,230014</t>
+  </si>
+  <si>
+    <t>10级手镯</t>
+  </si>
+  <si>
+    <t>210015,220015,230015</t>
+  </si>
+  <si>
+    <t>10级戒指</t>
+  </si>
+  <si>
+    <t>210016,220016,230016</t>
+  </si>
+  <si>
+    <t>10级腰鞋</t>
+  </si>
+  <si>
+    <t>210017,220017,230017,210018,220018,230018</t>
+  </si>
+  <si>
+    <t>10级衣服</t>
+  </si>
+  <si>
+    <t>210012,220012,230012</t>
+  </si>
+  <si>
+    <t>10级武器</t>
+  </si>
+  <si>
+    <t>210011,220011,230011</t>
+  </si>
+  <si>
+    <t>20级链头</t>
+  </si>
+  <si>
+    <t>210023,220023,230023,210024,220024,230024</t>
+  </si>
+  <si>
+    <t>20级手镯</t>
+  </si>
+  <si>
+    <t>210025,220025,230025</t>
+  </si>
+  <si>
+    <t>20级戒指</t>
+  </si>
+  <si>
+    <t>210026,220026,230026</t>
+  </si>
+  <si>
+    <t>20级腰鞋</t>
+  </si>
+  <si>
+    <t>210027,220027,230027,210028,220028,230028</t>
+  </si>
+  <si>
+    <t>20级衣服</t>
+  </si>
+  <si>
+    <t>210022,220022,230022</t>
+  </si>
+  <si>
+    <t>20级武器</t>
+  </si>
+  <si>
+    <t>210021,220021,230021</t>
+  </si>
+  <si>
+    <t>30级链头</t>
+  </si>
+  <si>
+    <t>210033,220033,230033,210034,220034,230034</t>
+  </si>
+  <si>
+    <t>30级手镯</t>
+  </si>
+  <si>
+    <t>210035,220035,230035</t>
+  </si>
+  <si>
+    <t>30级戒指</t>
+  </si>
+  <si>
+    <t>210036,220036,230036</t>
+  </si>
+  <si>
+    <t>30级腰鞋</t>
+  </si>
+  <si>
+    <t>210037,220037,230037,210038,220038,230038</t>
+  </si>
+  <si>
+    <t>30级衣服</t>
+  </si>
+  <si>
+    <t>210032,220032,230032</t>
+  </si>
+  <si>
+    <t>30级武器</t>
+  </si>
+  <si>
+    <t>210031,220031,230031</t>
+  </si>
+  <si>
+    <t>40级链头</t>
+  </si>
+  <si>
+    <t>210043,220043,230043,210044,220044,230044</t>
+  </si>
+  <si>
+    <t>40级手镯</t>
+  </si>
+  <si>
+    <t>210045,220045,230045</t>
+  </si>
+  <si>
+    <t>40级戒指</t>
+  </si>
+  <si>
+    <t>210046,220046,230046</t>
+  </si>
+  <si>
+    <t>40级腰鞋</t>
+  </si>
+  <si>
+    <t>210047,220047,230047,210048,220048,230048</t>
+  </si>
+  <si>
+    <t>40级衣服</t>
+  </si>
+  <si>
+    <t>210042,220042,230042</t>
+  </si>
+  <si>
+    <t>40级武器</t>
+  </si>
+  <si>
+    <t>210041,220041,230041</t>
+  </si>
+  <si>
+    <t>50级链头</t>
+  </si>
+  <si>
+    <t>210053,220053,230053,210054,220054,230054</t>
+  </si>
+  <si>
+    <t>50级手镯</t>
+  </si>
+  <si>
+    <t>210055,220055,230055</t>
+  </si>
+  <si>
+    <t>50级戒指</t>
+  </si>
+  <si>
+    <t>210056,220056,230056</t>
+  </si>
+  <si>
+    <t>50级腰鞋</t>
+  </si>
+  <si>
+    <t>210057,220057,230057,210058,220058,230058</t>
+  </si>
+  <si>
+    <t>50级衣服</t>
+  </si>
+  <si>
+    <t>210052,220052,230052</t>
+  </si>
+  <si>
+    <t>50级武器</t>
+  </si>
+  <si>
+    <t>210051,220051,230051</t>
   </si>
   <si>
     <t>狼宝宝</t>
@@ -1062,12 +1242,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1897,7 +2077,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F11"/>
+  <dimension ref="C3:F41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -2032,6 +2212,426 @@
       </c>
       <c r="F11" s="16" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:6">
+      <c r="C12" s="1">
+        <v>20007</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:6">
+      <c r="C13" s="1">
+        <v>20008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:6">
+      <c r="C14" s="1">
+        <v>20009</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:6">
+      <c r="C15" s="1">
+        <v>20010</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:6">
+      <c r="C16" s="1">
+        <v>20011</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:6">
+      <c r="C17" s="1">
+        <v>20012</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:6">
+      <c r="C18" s="1">
+        <v>20013</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:6">
+      <c r="C19" s="1">
+        <v>20014</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:6">
+      <c r="C20" s="1">
+        <v>20015</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="1">
+        <v>2</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:6">
+      <c r="C21" s="1">
+        <v>20016</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:6">
+      <c r="C22" s="1">
+        <v>20017</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:6">
+      <c r="C23" s="1">
+        <v>20018</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:6">
+      <c r="C24" s="1">
+        <v>20019</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:6">
+      <c r="C25" s="1">
+        <v>20020</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:6">
+      <c r="C26" s="1">
+        <v>20021</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:6">
+      <c r="C27" s="1">
+        <v>20022</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:6">
+      <c r="C28" s="1">
+        <v>20023</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="1">
+        <v>2</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:6">
+      <c r="C29" s="1">
+        <v>20024</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:6">
+      <c r="C30" s="1">
+        <v>20025</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:6">
+      <c r="C31" s="1">
+        <v>20026</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:6">
+      <c r="C32" s="1">
+        <v>20027</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:6">
+      <c r="C33" s="1">
+        <v>20028</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:6">
+      <c r="C34" s="1">
+        <v>20029</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:6">
+      <c r="C35" s="1">
+        <v>20030</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:6">
+      <c r="C36" s="1">
+        <v>20031</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:6">
+      <c r="C37" s="1">
+        <v>20032</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:6">
+      <c r="C38" s="1">
+        <v>20033</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:6">
+      <c r="C39" s="1">
+        <v>20034</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:6">
+      <c r="C40" s="1">
+        <v>20035</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:6">
+      <c r="C41" s="1">
+        <v>20036</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="1">
+        <v>2</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2114,13 +2714,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -2128,13 +2728,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -2142,13 +2742,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -2156,13 +2756,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -2170,13 +2770,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -2184,13 +2784,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -2198,13 +2798,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>36</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -2212,13 +2812,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>37</v>
+        <v>97</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -2226,13 +2826,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -2240,13 +2840,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -2254,13 +2854,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -2268,13 +2868,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -2282,13 +2882,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -2296,13 +2896,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>50</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -2310,13 +2910,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -2324,13 +2924,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -2338,13 +2938,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>56</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -2352,13 +2952,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>57</v>
+        <v>117</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -2366,13 +2966,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -2380,13 +2980,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -2394,13 +2994,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -2408,13 +3008,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -2422,13 +3022,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>67</v>
+        <v>127</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -2436,13 +3036,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -2450,13 +3050,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -2464,13 +3064,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -2478,13 +3078,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>76</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -2492,13 +3092,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -2506,13 +3106,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -2520,13 +3120,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -2534,13 +3134,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>84</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -2548,13 +3148,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -2562,13 +3162,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -2576,13 +3176,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -2590,13 +3190,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -2604,13 +3204,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -2618,13 +3218,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -2632,13 +3232,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>98</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -2646,13 +3246,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>99</v>
+        <v>159</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>100</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -2660,13 +3260,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -2674,13 +3274,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>104</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -2688,13 +3288,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>105</v>
+        <v>165</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -2702,13 +3302,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>108</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -2716,13 +3316,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -2730,13 +3330,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>112</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -2744,13 +3344,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -2758,13 +3358,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -2772,13 +3372,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -2786,13 +3386,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -2800,13 +3400,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -2814,13 +3414,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="17" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -2828,13 +3428,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -2842,13 +3442,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>127</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -2856,13 +3456,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>128</v>
+        <v>188</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -2870,13 +3470,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>131</v>
+        <v>191</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -2884,13 +3484,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>133</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -2898,13 +3498,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>134</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -2912,13 +3512,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>136</v>
+        <v>196</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -2926,13 +3526,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>137</v>
+        <v>197</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>138</v>
+        <v>198</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -2940,13 +3540,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>139</v>
+        <v>199</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>140</v>
+        <v>200</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -2954,13 +3554,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>141</v>
+        <v>201</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -2968,13 +3568,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -2982,13 +3582,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -2996,13 +3596,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>148</v>
+        <v>208</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -3010,13 +3610,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>149</v>
+        <v>209</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="17" t="s">
-        <v>150</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -3024,13 +3624,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>152</v>
+        <v>212</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -3038,13 +3638,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="17" t="s">
-        <v>153</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -3052,13 +3652,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="17" t="s">
-        <v>155</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -3066,13 +3666,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>156</v>
+        <v>216</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>157</v>
+        <v>217</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -3080,13 +3680,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -3094,13 +3694,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -3108,13 +3708,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>162</v>
+        <v>222</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>163</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -3196,13 +3796,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>164</v>
+        <v>224</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -3288,13 +3888,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>166</v>
+        <v>226</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>167</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3302,13 +3902,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3316,13 +3916,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3330,13 +3930,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3344,13 +3944,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3358,13 +3958,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3372,13 +3972,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>179</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3386,13 +3986,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>181</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -3400,13 +4000,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>183</v>
+        <v>243</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -3515,7 +4115,7 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
@@ -3529,7 +4129,7 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
@@ -3543,7 +4143,7 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
@@ -3557,7 +4157,7 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
@@ -3571,7 +4171,7 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="E10" s="1">
         <v>5</v>
@@ -3587,7 +4187,7 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>189</v>
+        <v>249</v>
       </c>
       <c r="E11" s="1">
         <v>5</v>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -7,11 +7,12 @@
     <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="普通装备" sheetId="1" r:id="rId1"/>
-    <sheet name="宠物" sheetId="9" r:id="rId2"/>
-    <sheet name="特殊装备" sheetId="7" r:id="rId3"/>
-    <sheet name="技能书" sheetId="8" r:id="rId4"/>
-    <sheet name="珍宝" sheetId="4" r:id="rId5"/>
+    <sheet name="定制通用" sheetId="10" r:id="rId1"/>
+    <sheet name="普通装备" sheetId="1" r:id="rId2"/>
+    <sheet name="宠物" sheetId="9" r:id="rId3"/>
+    <sheet name="特殊装备" sheetId="7" r:id="rId4"/>
+    <sheet name="技能书" sheetId="8" r:id="rId5"/>
+    <sheet name="珍宝" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,16 +41,25 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">admin:
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 1 普通道具
 2，装备
 3，技能书
-6，buff
-</t>
+5，材料
+6，buff</t>
         </r>
       </text>
     </comment>
@@ -89,25 +99,16 @@
       <text>
         <r>
           <rPr>
-            <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">admin:
 1 普通道具
 2，装备
 3，技能书
-5，材料
-6，buff</t>
+6，buff
+</t>
         </r>
       </text>
     </comment>
@@ -263,16 +264,83 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">admin:
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 1 普通道具
 2，装备
 3，技能书
-6，buff
-</t>
+5，材料
+6，buff</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+格式为</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 普通道具
+2，装备
+3，技能书
+5，材料
+6，buff</t>
         </r>
       </text>
     </comment>
@@ -303,7 +371,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="282">
   <si>
     <t>_id</t>
   </si>
@@ -338,6 +406,48 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>铜矿石</t>
+  </si>
+  <si>
+    <t>5001</t>
+  </si>
+  <si>
+    <t>黑铁石</t>
+  </si>
+  <si>
+    <t>5002</t>
+  </si>
+  <si>
+    <t>皮肤碎片</t>
+  </si>
+  <si>
+    <t>5003</t>
+  </si>
+  <si>
+    <t>四格碎片</t>
+  </si>
+  <si>
+    <t>5011,5012,5013,5014</t>
+  </si>
+  <si>
+    <t>前4区域低级珍宝</t>
+  </si>
+  <si>
+    <t>40000001,40000004,40000007,40000010</t>
+  </si>
+  <si>
+    <t>前4区域中级珍宝</t>
+  </si>
+  <si>
+    <t>40000002,40000005,40000008,40000011</t>
+  </si>
+  <si>
+    <t>前4区域高级珍宝</t>
+  </si>
+  <si>
+    <t>40000003,40000006,40000009,40000012</t>
+  </si>
+  <si>
     <t>1级链头</t>
   </si>
   <si>
@@ -1037,22 +1147,76 @@
     <t>1009,2009,3009</t>
   </si>
   <si>
-    <t>鸡毛</t>
-  </si>
-  <si>
-    <t>鸡蛋</t>
-  </si>
-  <si>
-    <t>鸡冠</t>
-  </si>
-  <si>
-    <t>鹿角</t>
-  </si>
-  <si>
-    <t>鹿茸</t>
+    <t>狼毛</t>
+  </si>
+  <si>
+    <t>40000001</t>
+  </si>
+  <si>
+    <t>蛛丝</t>
+  </si>
+  <si>
+    <t>40000002</t>
+  </si>
+  <si>
+    <t>雄狮利爪</t>
+  </si>
+  <si>
+    <t>40000003</t>
+  </si>
+  <si>
+    <t>虫卵</t>
+  </si>
+  <si>
+    <t>40000004</t>
+  </si>
+  <si>
+    <t>蛇皮</t>
+  </si>
+  <si>
+    <t>40000005</t>
+  </si>
+  <si>
+    <t>巨鳄之泪</t>
+  </si>
+  <si>
+    <t>40000006</t>
+  </si>
+  <si>
+    <t>乌鸦羽</t>
+  </si>
+  <si>
+    <t>40000007</t>
+  </si>
+  <si>
+    <t>蝙蝠牙</t>
+  </si>
+  <si>
+    <t>40000008</t>
+  </si>
+  <si>
+    <t>尸王之心</t>
+  </si>
+  <si>
+    <t>40000009</t>
+  </si>
+  <si>
+    <t>树叶</t>
+  </si>
+  <si>
+    <t>40000010</t>
+  </si>
+  <si>
+    <t>鱼鳞</t>
+  </si>
+  <si>
+    <t>40000011</t>
   </si>
   <si>
     <t>鹿血</t>
+  </si>
+  <si>
+    <t>40000012</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1229,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1091,6 +1255,13 @@
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1577,137 +1748,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1725,6 +1896,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1742,16 +1914,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2077,6 +2261,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="C1:F22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="2" width="9" style="8"/>
+    <col min="3" max="3" width="8.75" style="8" customWidth="1"/>
+    <col min="4" max="4" width="15" style="8" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="8" customWidth="1"/>
+    <col min="6" max="6" width="30.75" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="8" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" s="8" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" s="8" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" s="8" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C4" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="8" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="16" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="16">
+        <v>1</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="16">
+        <v>5</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:6">
+      <c r="C7" s="16">
+        <v>2</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="16">
+        <v>5</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:6">
+      <c r="C8" s="16">
+        <v>3</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="16">
+        <v>5</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:6">
+      <c r="C9" s="16">
+        <v>4</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="16">
+        <v>5</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:6">
+      <c r="C10" s="8">
+        <v>5</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="8">
+        <v>6</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:6">
+      <c r="C11" s="8">
+        <v>6</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="8">
+        <v>6</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:6">
+      <c r="C12" s="8">
+        <v>7</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="8">
+        <v>6</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" s="16" customFormat="1" customHeight="1" spans="3:3">
+      <c r="C22" s="18"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C3:F41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
@@ -2135,13 +2494,13 @@
         <v>20001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="15" t="s">
-        <v>12</v>
+      <c r="F6" s="21" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -2149,13 +2508,13 @@
         <v>20002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>14</v>
+      <c r="F7" s="21" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -2163,13 +2522,13 @@
         <v>20003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="15" t="s">
-        <v>16</v>
+      <c r="F8" s="21" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -2177,13 +2536,13 @@
         <v>20004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>18</v>
+      <c r="F9" s="21" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -2191,13 +2550,13 @@
         <v>20005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="15" t="s">
-        <v>20</v>
+      <c r="F10" s="21" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -2205,13 +2564,13 @@
         <v>20006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="16" t="s">
-        <v>22</v>
+      <c r="F11" s="22" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -2219,13 +2578,13 @@
         <v>20007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>24</v>
+      <c r="F12" s="21" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -2233,13 +2592,13 @@
         <v>20008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="15" t="s">
-        <v>26</v>
+      <c r="F13" s="21" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -2247,13 +2606,13 @@
         <v>20009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="15" t="s">
-        <v>28</v>
+      <c r="F14" s="21" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -2261,13 +2620,13 @@
         <v>20010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="15" t="s">
-        <v>30</v>
+      <c r="F15" s="21" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -2275,13 +2634,13 @@
         <v>20011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="15" t="s">
-        <v>32</v>
+      <c r="F16" s="21" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -2289,13 +2648,13 @@
         <v>20012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="16" t="s">
-        <v>34</v>
+      <c r="F17" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -2303,13 +2662,13 @@
         <v>20013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="15" t="s">
-        <v>36</v>
+      <c r="F18" s="21" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -2317,13 +2676,13 @@
         <v>20014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>38</v>
+      <c r="F19" s="21" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -2331,13 +2690,13 @@
         <v>20015</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>40</v>
+      <c r="F20" s="21" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -2345,13 +2704,13 @@
         <v>20016</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>42</v>
+      <c r="F21" s="21" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -2359,13 +2718,13 @@
         <v>20017</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>44</v>
+      <c r="F22" s="21" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -2373,13 +2732,13 @@
         <v>20018</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="16" t="s">
-        <v>46</v>
+      <c r="F23" s="22" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -2387,13 +2746,13 @@
         <v>20019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>48</v>
+      <c r="F24" s="21" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -2401,13 +2760,13 @@
         <v>20020</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="15" t="s">
-        <v>50</v>
+      <c r="F25" s="21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -2415,13 +2774,13 @@
         <v>20021</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="15" t="s">
-        <v>52</v>
+      <c r="F26" s="21" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -2429,13 +2788,13 @@
         <v>20022</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="15" t="s">
-        <v>54</v>
+      <c r="F27" s="21" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -2443,13 +2802,13 @@
         <v>20023</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="15" t="s">
-        <v>56</v>
+      <c r="F28" s="21" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -2457,13 +2816,13 @@
         <v>20024</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="16" t="s">
-        <v>58</v>
+      <c r="F29" s="22" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -2471,13 +2830,13 @@
         <v>20025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>60</v>
+      <c r="F30" s="21" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -2485,13 +2844,13 @@
         <v>20026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="15" t="s">
-        <v>62</v>
+      <c r="F31" s="21" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -2499,13 +2858,13 @@
         <v>20027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="15" t="s">
-        <v>64</v>
+      <c r="F32" s="21" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -2513,13 +2872,13 @@
         <v>20028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="15" t="s">
-        <v>66</v>
+      <c r="F33" s="21" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -2527,13 +2886,13 @@
         <v>20029</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="15" t="s">
-        <v>68</v>
+      <c r="F34" s="21" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -2541,13 +2900,13 @@
         <v>20030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="16" t="s">
-        <v>70</v>
+      <c r="F35" s="22" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -2555,13 +2914,13 @@
         <v>20031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="15" t="s">
-        <v>72</v>
+      <c r="F36" s="21" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -2569,13 +2928,13 @@
         <v>20032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="15" t="s">
-        <v>74</v>
+      <c r="F37" s="21" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -2583,13 +2942,13 @@
         <v>20033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="15" t="s">
-        <v>76</v>
+      <c r="F38" s="21" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -2597,13 +2956,13 @@
         <v>20034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="15" t="s">
-        <v>78</v>
+      <c r="F39" s="21" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -2611,13 +2970,13 @@
         <v>20035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="15" t="s">
-        <v>80</v>
+      <c r="F40" s="21" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -2625,13 +2984,13 @@
         <v>20036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="16" t="s">
-        <v>82</v>
+      <c r="F41" s="22" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2647,7 +3006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:F77"/>
@@ -2710,1011 +3069,1011 @@
       </c>
     </row>
     <row r="6" s="6" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <v>180001</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>83</v>
+      <c r="D6" s="11" t="s">
+        <v>97</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>84</v>
+      <c r="F6" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="9">
+      <c r="C7" s="10">
         <v>180002</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>85</v>
+      <c r="D7" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
-      <c r="F7" s="17" t="s">
-        <v>86</v>
+      <c r="F7" s="20" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <v>180003</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>87</v>
+      <c r="D8" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>88</v>
+      <c r="F8" s="20" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <v>180004</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>89</v>
+      <c r="D9" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="17" t="s">
-        <v>90</v>
+      <c r="F9" s="20" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <v>180005</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>91</v>
+      <c r="D10" s="11" t="s">
+        <v>105</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>92</v>
+      <c r="F10" s="20" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
-      <c r="C11" s="9">
+      <c r="C11" s="10">
         <v>180006</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>93</v>
+      <c r="D11" s="12" t="s">
+        <v>107</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>94</v>
+      <c r="F11" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
-      <c r="C12" s="9">
+      <c r="C12" s="10">
         <v>180007</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>95</v>
+      <c r="D12" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>96</v>
+      <c r="F12" s="20" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
-      <c r="C13" s="9">
+      <c r="C13" s="10">
         <v>180008</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>97</v>
+      <c r="D13" s="13" t="s">
+        <v>111</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
-      <c r="F13" s="17" t="s">
-        <v>98</v>
+      <c r="F13" s="20" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <v>180009</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>99</v>
+      <c r="D14" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>100</v>
+      <c r="F14" s="20" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
-      <c r="C15" s="9">
+      <c r="C15" s="10">
         <v>180010</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>101</v>
+      <c r="D15" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
-      <c r="F15" s="17" t="s">
-        <v>102</v>
+      <c r="F15" s="20" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <v>180011</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>103</v>
+      <c r="D16" s="11" t="s">
+        <v>117</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>104</v>
+      <c r="F16" s="20" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="9">
+      <c r="C17" s="10">
         <v>180012</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>105</v>
+      <c r="D17" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
-      <c r="F17" s="17" t="s">
-        <v>106</v>
+      <c r="F17" s="20" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="9">
+      <c r="C18" s="10">
         <v>180013</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>107</v>
+      <c r="D18" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
-      <c r="F18" s="17" t="s">
-        <v>108</v>
+      <c r="F18" s="20" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="9">
+      <c r="C19" s="10">
         <v>180014</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>109</v>
+      <c r="D19" s="11" t="s">
+        <v>123</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
-      <c r="F19" s="17" t="s">
-        <v>110</v>
+      <c r="F19" s="20" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="9">
+      <c r="C20" s="10">
         <v>180015</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>111</v>
+      <c r="D20" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
-      <c r="F20" s="17" t="s">
-        <v>112</v>
+      <c r="F20" s="20" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
-      <c r="C21" s="9">
+      <c r="C21" s="10">
         <v>180016</v>
       </c>
-      <c r="D21" s="10" t="s">
-        <v>113</v>
+      <c r="D21" s="11" t="s">
+        <v>127</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
-      <c r="F21" s="17" t="s">
-        <v>114</v>
+      <c r="F21" s="20" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
-      <c r="C22" s="9">
+      <c r="C22" s="10">
         <v>180017</v>
       </c>
-      <c r="D22" s="10" t="s">
-        <v>115</v>
+      <c r="D22" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>116</v>
+      <c r="F22" s="20" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
-      <c r="C23" s="9">
+      <c r="C23" s="10">
         <v>180018</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>117</v>
+      <c r="D23" s="12" t="s">
+        <v>131</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>118</v>
+      <c r="F23" s="20" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
-      <c r="C24" s="9">
+      <c r="C24" s="10">
         <v>180019</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>119</v>
+      <c r="D24" s="11" t="s">
+        <v>133</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>120</v>
+      <c r="F24" s="20" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
-      <c r="C25" s="9">
+      <c r="C25" s="10">
         <v>180020</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>121</v>
+      <c r="D25" s="11" t="s">
+        <v>135</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
-      <c r="F25" s="17" t="s">
-        <v>122</v>
+      <c r="F25" s="20" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
-      <c r="C26" s="9">
+      <c r="C26" s="10">
         <v>180021</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>123</v>
+      <c r="D26" s="11" t="s">
+        <v>137</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
-      <c r="F26" s="17" t="s">
-        <v>124</v>
+      <c r="F26" s="20" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
-      <c r="C27" s="9">
+      <c r="C27" s="10">
         <v>180022</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>125</v>
+      <c r="D27" s="11" t="s">
+        <v>139</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
-      <c r="F27" s="17" t="s">
-        <v>126</v>
+      <c r="F27" s="20" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
-      <c r="C28" s="9">
+      <c r="C28" s="10">
         <v>180023</v>
       </c>
-      <c r="D28" s="12" t="s">
-        <v>127</v>
+      <c r="D28" s="13" t="s">
+        <v>141</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
-      <c r="F28" s="17" t="s">
-        <v>128</v>
+      <c r="F28" s="20" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
-      <c r="C29" s="9">
+      <c r="C29" s="10">
         <v>180024</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>129</v>
+      <c r="D29" s="12" t="s">
+        <v>143</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
-      <c r="F29" s="17" t="s">
-        <v>130</v>
+      <c r="F29" s="20" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
-      <c r="C30" s="9">
+      <c r="C30" s="10">
         <v>180025</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>131</v>
+      <c r="D30" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
-      <c r="F30" s="17" t="s">
-        <v>132</v>
+      <c r="F30" s="20" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
-      <c r="C31" s="9">
+      <c r="C31" s="10">
         <v>180026</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>133</v>
+      <c r="D31" s="11" t="s">
+        <v>147</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
-      <c r="F31" s="17" t="s">
-        <v>134</v>
+      <c r="F31" s="20" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
-      <c r="C32" s="9">
+      <c r="C32" s="10">
         <v>180027</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>135</v>
+      <c r="D32" s="14" t="s">
+        <v>149</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
-      <c r="F32" s="17" t="s">
-        <v>136</v>
+      <c r="F32" s="20" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
-      <c r="C33" s="9">
+      <c r="C33" s="10">
         <v>180028</v>
       </c>
-      <c r="D33" s="10" t="s">
-        <v>137</v>
+      <c r="D33" s="11" t="s">
+        <v>151</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
-      <c r="F33" s="17" t="s">
-        <v>138</v>
+      <c r="F33" s="20" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
-      <c r="C34" s="9">
+      <c r="C34" s="10">
         <v>180029</v>
       </c>
-      <c r="D34" s="13" t="s">
-        <v>139</v>
+      <c r="D34" s="14" t="s">
+        <v>153</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
-      <c r="F34" s="17" t="s">
-        <v>140</v>
+      <c r="F34" s="20" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
-      <c r="C35" s="9">
+      <c r="C35" s="10">
         <v>180030</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>141</v>
+      <c r="D35" s="12" t="s">
+        <v>155</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
-      <c r="F35" s="17" t="s">
-        <v>142</v>
+      <c r="F35" s="20" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
-      <c r="C36" s="9">
+      <c r="C36" s="10">
         <v>180031</v>
       </c>
-      <c r="D36" s="10" t="s">
-        <v>143</v>
+      <c r="D36" s="11" t="s">
+        <v>157</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
-      <c r="F36" s="17" t="s">
-        <v>144</v>
+      <c r="F36" s="20" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
-      <c r="C37" s="9">
+      <c r="C37" s="10">
         <v>180032</v>
       </c>
-      <c r="D37" s="10" t="s">
-        <v>145</v>
+      <c r="D37" s="11" t="s">
+        <v>159</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
-      <c r="F37" s="17" t="s">
-        <v>146</v>
+      <c r="F37" s="20" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
-      <c r="C38" s="9">
+      <c r="C38" s="10">
         <v>180033</v>
       </c>
-      <c r="D38" s="10" t="s">
-        <v>147</v>
+      <c r="D38" s="11" t="s">
+        <v>161</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
-      <c r="F38" s="17" t="s">
-        <v>148</v>
+      <c r="F38" s="20" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
-      <c r="C39" s="9">
+      <c r="C39" s="10">
         <v>180034</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>149</v>
+      <c r="D39" s="11" t="s">
+        <v>163</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
-      <c r="F39" s="17" t="s">
-        <v>150</v>
+      <c r="F39" s="20" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
-      <c r="C40" s="9">
+      <c r="C40" s="10">
         <v>180035</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>151</v>
+      <c r="D40" s="11" t="s">
+        <v>165</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
-      <c r="F40" s="17" t="s">
-        <v>152</v>
+      <c r="F40" s="20" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
-      <c r="C41" s="9">
+      <c r="C41" s="10">
         <v>180036</v>
       </c>
-      <c r="D41" s="11" t="s">
-        <v>153</v>
+      <c r="D41" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
-      <c r="F41" s="17" t="s">
-        <v>154</v>
+      <c r="F41" s="20" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
-      <c r="C42" s="9">
+      <c r="C42" s="10">
         <v>180037</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>155</v>
+      <c r="D42" s="13" t="s">
+        <v>169</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
-      <c r="F42" s="17" t="s">
-        <v>156</v>
+      <c r="F42" s="20" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
-      <c r="C43" s="9">
+      <c r="C43" s="10">
         <v>180038</v>
       </c>
-      <c r="D43" s="10" t="s">
-        <v>157</v>
+      <c r="D43" s="11" t="s">
+        <v>171</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
-      <c r="F43" s="17" t="s">
-        <v>158</v>
+      <c r="F43" s="20" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
-      <c r="C44" s="9">
+      <c r="C44" s="10">
         <v>180039</v>
       </c>
-      <c r="D44" s="12" t="s">
-        <v>159</v>
+      <c r="D44" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
-      <c r="F44" s="17" t="s">
-        <v>160</v>
+      <c r="F44" s="20" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
-      <c r="C45" s="9">
+      <c r="C45" s="10">
         <v>180040</v>
       </c>
-      <c r="D45" s="10" t="s">
-        <v>161</v>
+      <c r="D45" s="11" t="s">
+        <v>175</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
-      <c r="F45" s="17" t="s">
-        <v>162</v>
+      <c r="F45" s="20" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
-      <c r="C46" s="9">
+      <c r="C46" s="10">
         <v>180041</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E46" s="6">
+        <v>18</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:6">
+      <c r="C47" s="10">
+        <v>180042</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" s="6">
+        <v>18</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:6">
+      <c r="C48" s="10">
+        <v>180043</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E48" s="6">
+        <v>18</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:6">
+      <c r="C49" s="10">
+        <v>180044</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" s="6">
+        <v>18</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:6">
+      <c r="C50" s="10">
+        <v>180045</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E50" s="6">
+        <v>18</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:6">
+      <c r="C51" s="10">
+        <v>180046</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="E51" s="6">
+        <v>18</v>
+      </c>
+      <c r="F51" s="20" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:6">
+      <c r="C52" s="10">
+        <v>180047</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="E52" s="6">
+        <v>18</v>
+      </c>
+      <c r="F52" s="20" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:6">
+      <c r="C53" s="10">
+        <v>180048</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E53" s="6">
+        <v>18</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:6">
+      <c r="C54" s="10">
+        <v>180049</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E54" s="6">
+        <v>18</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:6">
+      <c r="C55" s="10">
+        <v>180050</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="E55" s="6">
+        <v>18</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:6">
+      <c r="C56" s="10">
+        <v>180051</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E56" s="6">
+        <v>18</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:6">
+      <c r="C57" s="10">
+        <v>180052</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E57" s="6">
+        <v>18</v>
+      </c>
+      <c r="F57" s="20" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:6">
+      <c r="C58" s="10">
+        <v>180053</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E58" s="6">
+        <v>18</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:6">
+      <c r="C59" s="10">
+        <v>180054</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="E59" s="6">
+        <v>18</v>
+      </c>
+      <c r="F59" s="20" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:6">
+      <c r="C60" s="10">
+        <v>180055</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="E60" s="6">
+        <v>18</v>
+      </c>
+      <c r="F60" s="20" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:6">
+      <c r="C61" s="10">
+        <v>180056</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E61" s="6">
+        <v>18</v>
+      </c>
+      <c r="F61" s="20" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:6">
+      <c r="C62" s="10">
+        <v>180057</v>
+      </c>
+      <c r="D62" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="E46" s="6">
-        <v>18</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:6">
-      <c r="C47" s="9">
-        <v>180042</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E47" s="6">
-        <v>18</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:6">
-      <c r="C48" s="9">
-        <v>180043</v>
-      </c>
-      <c r="D48" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E48" s="6">
-        <v>18</v>
-      </c>
-      <c r="F48" s="17" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:6">
-      <c r="C49" s="9">
-        <v>180044</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="E49" s="6">
-        <v>18</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:6">
-      <c r="C50" s="9">
-        <v>180045</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E50" s="6">
-        <v>18</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:6">
-      <c r="C51" s="9">
-        <v>180046</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E51" s="6">
-        <v>18</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:6">
-      <c r="C52" s="9">
-        <v>180047</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="E52" s="6">
-        <v>18</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:6">
-      <c r="C53" s="9">
-        <v>180048</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>169</v>
-      </c>
-      <c r="E53" s="6">
-        <v>18</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:6">
-      <c r="C54" s="9">
-        <v>180049</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="E54" s="6">
-        <v>18</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:6">
-      <c r="C55" s="9">
-        <v>180050</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="E55" s="6">
-        <v>18</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:6">
-      <c r="C56" s="9">
-        <v>180051</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E56" s="6">
-        <v>18</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:6">
-      <c r="C57" s="9">
-        <v>180052</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="E57" s="6">
-        <v>18</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:6">
-      <c r="C58" s="9">
-        <v>180053</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E58" s="6">
-        <v>18</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:6">
-      <c r="C59" s="9">
-        <v>180054</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="E59" s="6">
-        <v>18</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:6">
-      <c r="C60" s="9">
-        <v>180055</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="E60" s="6">
-        <v>18</v>
-      </c>
-      <c r="F60" s="17" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:6">
-      <c r="C61" s="9">
-        <v>180056</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E61" s="6">
-        <v>18</v>
-      </c>
-      <c r="F61" s="17" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:6">
-      <c r="C62" s="9">
-        <v>180057</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>149</v>
-      </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
-      <c r="F62" s="17" t="s">
-        <v>194</v>
+      <c r="F62" s="20" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
-      <c r="C63" s="9">
+      <c r="C63" s="10">
         <v>180058</v>
       </c>
-      <c r="D63" s="12" t="s">
-        <v>195</v>
+      <c r="D63" s="13" t="s">
+        <v>209</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
-      <c r="F63" s="17" t="s">
-        <v>196</v>
+      <c r="F63" s="20" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
-      <c r="C64" s="9">
+      <c r="C64" s="10">
         <v>180059</v>
       </c>
-      <c r="D64" s="10" t="s">
-        <v>197</v>
+      <c r="D64" s="11" t="s">
+        <v>211</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
-      <c r="F64" s="17" t="s">
-        <v>198</v>
+      <c r="F64" s="20" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
-      <c r="C65" s="9">
+      <c r="C65" s="10">
         <v>180060</v>
       </c>
-      <c r="D65" s="11" t="s">
-        <v>199</v>
+      <c r="D65" s="12" t="s">
+        <v>213</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
-      <c r="F65" s="17" t="s">
-        <v>200</v>
+      <c r="F65" s="20" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
-      <c r="C66" s="9">
+      <c r="C66" s="10">
         <v>180061</v>
       </c>
-      <c r="D66" s="10" t="s">
-        <v>201</v>
+      <c r="D66" s="11" t="s">
+        <v>215</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
-      <c r="F66" s="17" t="s">
-        <v>202</v>
+      <c r="F66" s="20" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
-      <c r="C67" s="9">
+      <c r="C67" s="10">
         <v>180062</v>
       </c>
-      <c r="D67" s="13" t="s">
-        <v>203</v>
+      <c r="D67" s="14" t="s">
+        <v>217</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
-      <c r="F67" s="17" t="s">
-        <v>204</v>
+      <c r="F67" s="20" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
-      <c r="C68" s="9">
+      <c r="C68" s="10">
         <v>180063</v>
       </c>
-      <c r="D68" s="10" t="s">
-        <v>205</v>
+      <c r="D68" s="11" t="s">
+        <v>219</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
-      <c r="F68" s="17" t="s">
-        <v>206</v>
+      <c r="F68" s="20" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
-      <c r="C69" s="9">
+      <c r="C69" s="10">
         <v>180064</v>
       </c>
-      <c r="D69" s="10" t="s">
-        <v>207</v>
+      <c r="D69" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
-      <c r="F69" s="17" t="s">
-        <v>208</v>
+      <c r="F69" s="20" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
-      <c r="C70" s="9">
+      <c r="C70" s="10">
         <v>180065</v>
       </c>
-      <c r="D70" s="10" t="s">
-        <v>209</v>
+      <c r="D70" s="11" t="s">
+        <v>223</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
-      <c r="F70" s="17" t="s">
-        <v>210</v>
+      <c r="F70" s="20" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
-      <c r="C71" s="9">
+      <c r="C71" s="10">
         <v>180066</v>
       </c>
-      <c r="D71" s="11" t="s">
-        <v>211</v>
+      <c r="D71" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
-      <c r="F71" s="17" t="s">
-        <v>212</v>
+      <c r="F71" s="20" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
-      <c r="C72" s="9">
+      <c r="C72" s="10">
         <v>180067</v>
       </c>
-      <c r="D72" s="10" t="s">
-        <v>207</v>
+      <c r="D72" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
-      <c r="F72" s="17" t="s">
-        <v>213</v>
+      <c r="F72" s="20" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
-      <c r="C73" s="9">
+      <c r="C73" s="10">
         <v>180068</v>
       </c>
-      <c r="D73" s="10" t="s">
-        <v>214</v>
+      <c r="D73" s="11" t="s">
+        <v>228</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
-      <c r="F73" s="17" t="s">
-        <v>215</v>
+      <c r="F73" s="20" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
-      <c r="C74" s="9">
+      <c r="C74" s="10">
         <v>180069</v>
       </c>
-      <c r="D74" s="10" t="s">
-        <v>216</v>
+      <c r="D74" s="11" t="s">
+        <v>230</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
-      <c r="F74" s="17" t="s">
-        <v>217</v>
+      <c r="F74" s="20" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
-      <c r="C75" s="9">
+      <c r="C75" s="10">
         <v>180070</v>
       </c>
-      <c r="D75" s="10" t="s">
-        <v>218</v>
+      <c r="D75" s="11" t="s">
+        <v>232</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
-      <c r="F75" s="17" t="s">
-        <v>219</v>
+      <c r="F75" s="20" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
-      <c r="C76" s="9">
+      <c r="C76" s="10">
         <v>180071</v>
       </c>
-      <c r="D76" s="12" t="s">
-        <v>220</v>
+      <c r="D76" s="13" t="s">
+        <v>234</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
-      <c r="F76" s="17" t="s">
-        <v>221</v>
+      <c r="F76" s="20" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
-      <c r="C77" s="9">
+      <c r="C77" s="10">
         <v>180072</v>
       </c>
-      <c r="D77" s="11" t="s">
-        <v>222</v>
+      <c r="D77" s="12" t="s">
+        <v>236</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
-      <c r="F77" s="17" t="s">
-        <v>223</v>
+      <c r="F77" s="20" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3729,7 +4088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:F22"/>
@@ -3796,17 +4155,17 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C22" s="9"/>
+      <c r="C22" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3820,7 +4179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C1:F32"/>
@@ -3888,13 +4247,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>227</v>
+      <c r="F6" s="23" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3902,13 +4261,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>229</v>
+      <c r="F7" s="23" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3916,13 +4275,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>231</v>
+      <c r="F8" s="23" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3930,13 +4289,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>233</v>
+      <c r="F9" s="23" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3944,13 +4303,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="18" t="s">
-        <v>235</v>
+      <c r="F10" s="23" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3958,13 +4317,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>237</v>
+      <c r="F11" s="23" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3972,13 +4331,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>239</v>
+      <c r="F12" s="23" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3986,13 +4345,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="19" t="s">
-        <v>241</v>
+      <c r="F13" s="24" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4000,41 +4359,41 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="19" t="s">
-        <v>243</v>
+      <c r="F14" s="24" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F24" s="7"/>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F25" s="7"/>
+      <c r="F25" s="8"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F26" s="7"/>
+      <c r="F26" s="8"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F27" s="7"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F28" s="7"/>
+      <c r="F28" s="8"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F29" s="7"/>
+      <c r="F29" s="8"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F30" s="7"/>
+      <c r="F30" s="8"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F31" s="7"/>
+      <c r="F31" s="8"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F32" s="7"/>
+      <c r="F32" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4048,27 +4407,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
+  <dimension ref="C1:F32"/>
+  <sheetFormatPr defaultColWidth="12.25" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5833333333333" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.25" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="6" max="6" width="18.4166666666667" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="12.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -4082,7 +4442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
@@ -4096,7 +4456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
@@ -4110,132 +4470,200 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:7">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C6" s="5">
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="E6" s="1">
-        <v>5</v>
-      </c>
-      <c r="F6" s="6">
-        <v>40000001</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:7">
+        <v>6</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C7" s="5">
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="E7" s="1">
-        <v>5</v>
-      </c>
-      <c r="F7" s="6">
-        <v>40000002</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:7">
+        <v>6</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C8" s="5">
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="E8" s="1">
-        <v>5</v>
-      </c>
-      <c r="F8" s="6">
-        <v>40000003</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:7">
+        <v>6</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C9" s="5">
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="E9" s="1">
-        <v>5</v>
-      </c>
-      <c r="F9" s="6">
-        <v>40000004</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:7">
+        <v>6</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C10" s="5">
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="E10" s="1">
-        <v>5</v>
-      </c>
-      <c r="F10" s="6">
-        <v>40000005</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:7">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C11" s="5">
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="E11" s="1">
-        <v>5</v>
-      </c>
-      <c r="F11" s="6">
-        <v>40000006</v>
-      </c>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" customHeight="1" spans="1:7">
-      <c r="C12" s="5"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" customHeight="1" spans="1:7">
-      <c r="C13" s="5"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" customHeight="1" spans="1:7">
-      <c r="C14" s="5"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" customHeight="1" spans="1:7">
-      <c r="C15" s="5"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" customHeight="1" spans="1:7">
-      <c r="C16" s="5"/>
-      <c r="F16" s="7"/>
+        <v>6</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C12" s="5">
+        <v>50007</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E12" s="1">
+        <v>6</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C13" s="5">
+        <v>50008</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E13" s="1">
+        <v>6</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C14" s="5">
+        <v>50009</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="E14" s="1">
+        <v>6</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:6">
+      <c r="C15" s="5">
+        <v>50010</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E15" s="1">
+        <v>6</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:6">
+      <c r="C16" s="5">
+        <v>50011</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="E16" s="1">
+        <v>6</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="5"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="5"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="5"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="5"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" customHeight="1" spans="3:6">
-      <c r="C21" s="5"/>
-      <c r="F21" s="7"/>
+      <c r="C17" s="5">
+        <v>50012</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="E17" s="1">
+        <v>6</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F27" s="8"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F32" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -1878,7 +1878,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1917,9 +1917,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1934,9 +1931,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -2279,13 +2273,13 @@
       <c r="F2" s="2"/>
     </row>
     <row r="3" s="8" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -2293,13 +2287,13 @@
       </c>
     </row>
     <row r="4" s="8" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -2307,72 +2301,72 @@
       </c>
     </row>
     <row r="5" s="8" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="16" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="16">
+    <row r="6" s="8" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="8">
         <v>1</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="8">
         <v>5</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="16">
+      <c r="C7" s="8">
         <v>2</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="8">
         <v>5</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="16">
+      <c r="C8" s="8">
         <v>3</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="8">
         <v>5</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="16">
+      <c r="C9" s="8">
         <v>4</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="8">
         <v>5</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="18" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2386,7 +2380,7 @@
       <c r="E10" s="8">
         <v>6</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2400,7 +2394,7 @@
       <c r="E11" s="8">
         <v>6</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2414,12 +2408,12 @@
       <c r="E12" s="8">
         <v>6</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="19" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" s="16" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C22" s="18"/>
+    <row r="22" s="8" customFormat="1" customHeight="1" spans="3:3">
+      <c r="C22" s="17"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2499,7 +2493,7 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="20" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2513,7 +2507,7 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="20" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2527,7 +2521,7 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2541,7 +2535,7 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="20" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2555,7 +2549,7 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2569,7 +2563,7 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="21" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2583,7 +2577,7 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="20" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2597,7 +2591,7 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="20" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2611,7 +2605,7 @@
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2625,7 +2619,7 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2639,7 +2633,7 @@
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="20" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2653,7 +2647,7 @@
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="21" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2667,7 +2661,7 @@
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="20" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2681,7 +2675,7 @@
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="20" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2695,7 +2689,7 @@
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="20" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2709,7 +2703,7 @@
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="20" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2723,7 +2717,7 @@
       <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="20" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2737,7 +2731,7 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="21" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2751,7 +2745,7 @@
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="20" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2765,7 +2759,7 @@
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="F25" s="20" t="s">
         <v>64</v>
       </c>
     </row>
@@ -2779,7 +2773,7 @@
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="F26" s="20" t="s">
         <v>66</v>
       </c>
     </row>
@@ -2793,7 +2787,7 @@
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="20" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2807,7 +2801,7 @@
       <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="20" t="s">
         <v>70</v>
       </c>
     </row>
@@ -2821,7 +2815,7 @@
       <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="21" t="s">
         <v>72</v>
       </c>
     </row>
@@ -2835,7 +2829,7 @@
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F30" s="20" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2849,7 +2843,7 @@
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="21" t="s">
+      <c r="F31" s="20" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2863,7 +2857,7 @@
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="20" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2877,7 +2871,7 @@
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="20" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2891,7 +2885,7 @@
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="20" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2905,7 +2899,7 @@
       <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="22" t="s">
+      <c r="F35" s="21" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2919,7 +2913,7 @@
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F36" s="20" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2933,7 +2927,7 @@
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="21" t="s">
+      <c r="F37" s="20" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2947,7 +2941,7 @@
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="21" t="s">
+      <c r="F38" s="20" t="s">
         <v>90</v>
       </c>
     </row>
@@ -2961,7 +2955,7 @@
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="21" t="s">
+      <c r="F39" s="20" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2975,7 +2969,7 @@
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="21" t="s">
+      <c r="F40" s="20" t="s">
         <v>94</v>
       </c>
     </row>
@@ -2989,7 +2983,7 @@
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="22" t="s">
+      <c r="F41" s="21" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3078,7 +3072,7 @@
       <c r="E6" s="6">
         <v>18</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="19" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3092,7 +3086,7 @@
       <c r="E7" s="6">
         <v>18</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3106,7 +3100,7 @@
       <c r="E8" s="6">
         <v>18</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="19" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3120,7 +3114,7 @@
       <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3134,7 +3128,7 @@
       <c r="E10" s="6">
         <v>18</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="19" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3148,7 +3142,7 @@
       <c r="E11" s="6">
         <v>18</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="19" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3162,7 +3156,7 @@
       <c r="E12" s="6">
         <v>18</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="19" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3176,7 +3170,7 @@
       <c r="E13" s="6">
         <v>18</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="19" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3190,7 +3184,7 @@
       <c r="E14" s="6">
         <v>18</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="19" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3204,7 +3198,7 @@
       <c r="E15" s="6">
         <v>18</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="19" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3218,7 +3212,7 @@
       <c r="E16" s="6">
         <v>18</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="19" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3232,7 +3226,7 @@
       <c r="E17" s="6">
         <v>18</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="19" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3246,7 +3240,7 @@
       <c r="E18" s="6">
         <v>18</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="19" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3260,7 +3254,7 @@
       <c r="E19" s="6">
         <v>18</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="19" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3274,7 +3268,7 @@
       <c r="E20" s="6">
         <v>18</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="19" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3288,7 +3282,7 @@
       <c r="E21" s="6">
         <v>18</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="19" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3302,7 +3296,7 @@
       <c r="E22" s="6">
         <v>18</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="19" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3316,7 +3310,7 @@
       <c r="E23" s="6">
         <v>18</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="F23" s="19" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3330,7 +3324,7 @@
       <c r="E24" s="6">
         <v>18</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="19" t="s">
         <v>134</v>
       </c>
     </row>
@@ -3344,7 +3338,7 @@
       <c r="E25" s="6">
         <v>18</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="19" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3358,7 +3352,7 @@
       <c r="E26" s="6">
         <v>18</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="19" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3372,7 +3366,7 @@
       <c r="E27" s="6">
         <v>18</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="19" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3386,7 +3380,7 @@
       <c r="E28" s="6">
         <v>18</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="19" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3400,7 +3394,7 @@
       <c r="E29" s="6">
         <v>18</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="F29" s="19" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3414,7 +3408,7 @@
       <c r="E30" s="6">
         <v>18</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="19" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3428,7 +3422,7 @@
       <c r="E31" s="6">
         <v>18</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="F31" s="19" t="s">
         <v>148</v>
       </c>
     </row>
@@ -3442,7 +3436,7 @@
       <c r="E32" s="6">
         <v>18</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="19" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3456,7 +3450,7 @@
       <c r="E33" s="6">
         <v>18</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="19" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3470,7 +3464,7 @@
       <c r="E34" s="6">
         <v>18</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="19" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3484,7 +3478,7 @@
       <c r="E35" s="6">
         <v>18</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="F35" s="19" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3498,7 +3492,7 @@
       <c r="E36" s="6">
         <v>18</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="19" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3512,7 +3506,7 @@
       <c r="E37" s="6">
         <v>18</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="19" t="s">
         <v>160</v>
       </c>
     </row>
@@ -3526,7 +3520,7 @@
       <c r="E38" s="6">
         <v>18</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="19" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3540,7 +3534,7 @@
       <c r="E39" s="6">
         <v>18</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="19" t="s">
         <v>164</v>
       </c>
     </row>
@@ -3554,7 +3548,7 @@
       <c r="E40" s="6">
         <v>18</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="F40" s="19" t="s">
         <v>166</v>
       </c>
     </row>
@@ -3568,7 +3562,7 @@
       <c r="E41" s="6">
         <v>18</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="F41" s="19" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3582,7 +3576,7 @@
       <c r="E42" s="6">
         <v>18</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="19" t="s">
         <v>170</v>
       </c>
     </row>
@@ -3596,7 +3590,7 @@
       <c r="E43" s="6">
         <v>18</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="F43" s="19" t="s">
         <v>172</v>
       </c>
     </row>
@@ -3610,7 +3604,7 @@
       <c r="E44" s="6">
         <v>18</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="19" t="s">
         <v>174</v>
       </c>
     </row>
@@ -3624,7 +3618,7 @@
       <c r="E45" s="6">
         <v>18</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="F45" s="19" t="s">
         <v>176</v>
       </c>
     </row>
@@ -3638,7 +3632,7 @@
       <c r="E46" s="6">
         <v>18</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" s="19" t="s">
         <v>178</v>
       </c>
     </row>
@@ -3652,7 +3646,7 @@
       <c r="E47" s="6">
         <v>18</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="F47" s="19" t="s">
         <v>180</v>
       </c>
     </row>
@@ -3666,7 +3660,7 @@
       <c r="E48" s="6">
         <v>18</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="F48" s="19" t="s">
         <v>182</v>
       </c>
     </row>
@@ -3680,7 +3674,7 @@
       <c r="E49" s="6">
         <v>18</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="F49" s="19" t="s">
         <v>184</v>
       </c>
     </row>
@@ -3694,7 +3688,7 @@
       <c r="E50" s="6">
         <v>18</v>
       </c>
-      <c r="F50" s="20" t="s">
+      <c r="F50" s="19" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3708,7 +3702,7 @@
       <c r="E51" s="6">
         <v>18</v>
       </c>
-      <c r="F51" s="20" t="s">
+      <c r="F51" s="19" t="s">
         <v>188</v>
       </c>
     </row>
@@ -3722,7 +3716,7 @@
       <c r="E52" s="6">
         <v>18</v>
       </c>
-      <c r="F52" s="20" t="s">
+      <c r="F52" s="19" t="s">
         <v>190</v>
       </c>
     </row>
@@ -3736,7 +3730,7 @@
       <c r="E53" s="6">
         <v>18</v>
       </c>
-      <c r="F53" s="20" t="s">
+      <c r="F53" s="19" t="s">
         <v>191</v>
       </c>
     </row>
@@ -3750,7 +3744,7 @@
       <c r="E54" s="6">
         <v>18</v>
       </c>
-      <c r="F54" s="20" t="s">
+      <c r="F54" s="19" t="s">
         <v>193</v>
       </c>
     </row>
@@ -3764,7 +3758,7 @@
       <c r="E55" s="6">
         <v>18</v>
       </c>
-      <c r="F55" s="20" t="s">
+      <c r="F55" s="19" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3778,7 +3772,7 @@
       <c r="E56" s="6">
         <v>18</v>
       </c>
-      <c r="F56" s="20" t="s">
+      <c r="F56" s="19" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3792,7 +3786,7 @@
       <c r="E57" s="6">
         <v>18</v>
       </c>
-      <c r="F57" s="20" t="s">
+      <c r="F57" s="19" t="s">
         <v>199</v>
       </c>
     </row>
@@ -3806,7 +3800,7 @@
       <c r="E58" s="6">
         <v>18</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="F58" s="19" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3820,7 +3814,7 @@
       <c r="E59" s="6">
         <v>18</v>
       </c>
-      <c r="F59" s="20" t="s">
+      <c r="F59" s="19" t="s">
         <v>203</v>
       </c>
     </row>
@@ -3834,7 +3828,7 @@
       <c r="E60" s="6">
         <v>18</v>
       </c>
-      <c r="F60" s="20" t="s">
+      <c r="F60" s="19" t="s">
         <v>205</v>
       </c>
     </row>
@@ -3848,7 +3842,7 @@
       <c r="E61" s="6">
         <v>18</v>
       </c>
-      <c r="F61" s="20" t="s">
+      <c r="F61" s="19" t="s">
         <v>207</v>
       </c>
     </row>
@@ -3862,7 +3856,7 @@
       <c r="E62" s="6">
         <v>18</v>
       </c>
-      <c r="F62" s="20" t="s">
+      <c r="F62" s="19" t="s">
         <v>208</v>
       </c>
     </row>
@@ -3876,7 +3870,7 @@
       <c r="E63" s="6">
         <v>18</v>
       </c>
-      <c r="F63" s="20" t="s">
+      <c r="F63" s="19" t="s">
         <v>210</v>
       </c>
     </row>
@@ -3890,7 +3884,7 @@
       <c r="E64" s="6">
         <v>18</v>
       </c>
-      <c r="F64" s="20" t="s">
+      <c r="F64" s="19" t="s">
         <v>212</v>
       </c>
     </row>
@@ -3904,7 +3898,7 @@
       <c r="E65" s="6">
         <v>18</v>
       </c>
-      <c r="F65" s="20" t="s">
+      <c r="F65" s="19" t="s">
         <v>214</v>
       </c>
     </row>
@@ -3918,7 +3912,7 @@
       <c r="E66" s="6">
         <v>18</v>
       </c>
-      <c r="F66" s="20" t="s">
+      <c r="F66" s="19" t="s">
         <v>216</v>
       </c>
     </row>
@@ -3932,7 +3926,7 @@
       <c r="E67" s="6">
         <v>18</v>
       </c>
-      <c r="F67" s="20" t="s">
+      <c r="F67" s="19" t="s">
         <v>218</v>
       </c>
     </row>
@@ -3946,7 +3940,7 @@
       <c r="E68" s="6">
         <v>18</v>
       </c>
-      <c r="F68" s="20" t="s">
+      <c r="F68" s="19" t="s">
         <v>220</v>
       </c>
     </row>
@@ -3960,7 +3954,7 @@
       <c r="E69" s="6">
         <v>18</v>
       </c>
-      <c r="F69" s="20" t="s">
+      <c r="F69" s="19" t="s">
         <v>222</v>
       </c>
     </row>
@@ -3974,7 +3968,7 @@
       <c r="E70" s="6">
         <v>18</v>
       </c>
-      <c r="F70" s="20" t="s">
+      <c r="F70" s="19" t="s">
         <v>224</v>
       </c>
     </row>
@@ -3988,7 +3982,7 @@
       <c r="E71" s="6">
         <v>18</v>
       </c>
-      <c r="F71" s="20" t="s">
+      <c r="F71" s="19" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4002,7 +3996,7 @@
       <c r="E72" s="6">
         <v>18</v>
       </c>
-      <c r="F72" s="20" t="s">
+      <c r="F72" s="19" t="s">
         <v>227</v>
       </c>
     </row>
@@ -4016,7 +4010,7 @@
       <c r="E73" s="6">
         <v>18</v>
       </c>
-      <c r="F73" s="20" t="s">
+      <c r="F73" s="19" t="s">
         <v>229</v>
       </c>
     </row>
@@ -4030,7 +4024,7 @@
       <c r="E74" s="6">
         <v>18</v>
       </c>
-      <c r="F74" s="20" t="s">
+      <c r="F74" s="19" t="s">
         <v>231</v>
       </c>
     </row>
@@ -4044,7 +4038,7 @@
       <c r="E75" s="6">
         <v>18</v>
       </c>
-      <c r="F75" s="20" t="s">
+      <c r="F75" s="19" t="s">
         <v>233</v>
       </c>
     </row>
@@ -4058,7 +4052,7 @@
       <c r="E76" s="6">
         <v>18</v>
       </c>
-      <c r="F76" s="20" t="s">
+      <c r="F76" s="19" t="s">
         <v>235</v>
       </c>
     </row>
@@ -4072,7 +4066,7 @@
       <c r="E77" s="6">
         <v>18</v>
       </c>
-      <c r="F77" s="20" t="s">
+      <c r="F77" s="19" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4252,7 +4246,7 @@
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="18" t="s">
         <v>241</v>
       </c>
     </row>
@@ -4266,7 +4260,7 @@
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F7" s="18" t="s">
         <v>243</v>
       </c>
     </row>
@@ -4280,7 +4274,7 @@
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="18" t="s">
         <v>245</v>
       </c>
     </row>
@@ -4294,7 +4288,7 @@
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="18" t="s">
         <v>247</v>
       </c>
     </row>
@@ -4308,7 +4302,7 @@
       <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="18" t="s">
         <v>249</v>
       </c>
     </row>
@@ -4322,7 +4316,7 @@
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="18" t="s">
         <v>251</v>
       </c>
     </row>
@@ -4336,7 +4330,7 @@
       <c r="E12" s="1">
         <v>4</v>
       </c>
-      <c r="F12" s="23" t="s">
+      <c r="F12" s="18" t="s">
         <v>253</v>
       </c>
     </row>
@@ -4350,7 +4344,7 @@
       <c r="E13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="22" t="s">
         <v>255</v>
       </c>
     </row>
@@ -4364,7 +4358,7 @@
       <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="22" t="s">
         <v>257</v>
       </c>
     </row>
@@ -4480,7 +4474,7 @@
       <c r="E6" s="1">
         <v>6</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="19" t="s">
         <v>259</v>
       </c>
     </row>
@@ -4494,7 +4488,7 @@
       <c r="E7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19" t="s">
         <v>261</v>
       </c>
     </row>
@@ -4508,7 +4502,7 @@
       <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="19" t="s">
         <v>263</v>
       </c>
     </row>
@@ -4522,7 +4516,7 @@
       <c r="E9" s="1">
         <v>6</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>265</v>
       </c>
     </row>
@@ -4536,7 +4530,7 @@
       <c r="E10" s="1">
         <v>6</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="19" t="s">
         <v>267</v>
       </c>
     </row>
@@ -4550,7 +4544,7 @@
       <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="19" t="s">
         <v>269</v>
       </c>
     </row>
@@ -4564,7 +4558,7 @@
       <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="19" t="s">
         <v>271</v>
       </c>
     </row>
@@ -4578,7 +4572,7 @@
       <c r="E13" s="1">
         <v>6</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="19" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4592,7 +4586,7 @@
       <c r="E14" s="1">
         <v>6</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="19" t="s">
         <v>275</v>
       </c>
     </row>
@@ -4606,7 +4600,7 @@
       <c r="E15" s="1">
         <v>6</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="19" t="s">
         <v>277</v>
       </c>
     </row>
@@ -4620,7 +4614,7 @@
       <c r="E16" s="1">
         <v>6</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="19" t="s">
         <v>279</v>
       </c>
     </row>
@@ -4634,7 +4628,7 @@
       <c r="E17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="19" t="s">
         <v>281</v>
       </c>
     </row>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -4,15 +4,16 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
     <sheet name="普通装备" sheetId="1" r:id="rId2"/>
-    <sheet name="宠物" sheetId="9" r:id="rId3"/>
-    <sheet name="特殊装备" sheetId="7" r:id="rId4"/>
-    <sheet name="技能书" sheetId="8" r:id="rId5"/>
-    <sheet name="珍宝" sheetId="11" r:id="rId6"/>
+    <sheet name="传奇装备" sheetId="12" r:id="rId3"/>
+    <sheet name="宠物" sheetId="9" r:id="rId4"/>
+    <sheet name="特殊装备" sheetId="7" r:id="rId5"/>
+    <sheet name="技能书" sheetId="8" r:id="rId6"/>
+    <sheet name="珍宝" sheetId="11" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -148,25 +149,16 @@
       <text>
         <r>
           <rPr>
-            <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t xml:space="preserve">admin:
 1 普通道具
 2，装备
 3，技能书
-5，材料
-6，buff</t>
+6，buff
+</t>
         </r>
       </text>
     </comment>
@@ -370,8 +362,66 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 普通道具
+2，装备
+3，技能书
+5，材料
+6，buff</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+格式为</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="296">
   <si>
     <t>_id</t>
   </si>
@@ -662,6 +712,48 @@
   </si>
   <si>
     <t>210051,220051,230051</t>
+  </si>
+  <si>
+    <t>治愈</t>
+  </si>
+  <si>
+    <t>201001,201002,201003</t>
+  </si>
+  <si>
+    <t>财富</t>
+  </si>
+  <si>
+    <t>201004,201005,201006</t>
+  </si>
+  <si>
+    <t>修炼</t>
+  </si>
+  <si>
+    <t>201007,201008,201009</t>
+  </si>
+  <si>
+    <t>神速</t>
+  </si>
+  <si>
+    <t>201010,201011,201012</t>
+  </si>
+  <si>
+    <t>重击</t>
+  </si>
+  <si>
+    <t>201013,201014,201015</t>
+  </si>
+  <si>
+    <t>暴击</t>
+  </si>
+  <si>
+    <t>201016,201017,201018</t>
+  </si>
+  <si>
+    <t>天命</t>
+  </si>
+  <si>
+    <t>201019,201020,201021</t>
   </si>
   <si>
     <t>狼宝宝</t>
@@ -1413,12 +1505,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3003,23 +3095,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F77"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="C3:F41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.0833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="73.8333333333333" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F2" s="2"/>
-    </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C3" s="3" t="s">
         <v>0</v>
@@ -3048,7 +3134,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="5" s="1" customFormat="1" ht="11.5" spans="3:6">
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
@@ -3062,1013 +3148,190 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="10">
-        <v>180001</v>
-      </c>
-      <c r="D6" s="11" t="s">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="1">
+        <v>21001</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="6">
-        <v>18</v>
-      </c>
-      <c r="F6" s="19" t="s">
+      <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="10">
-        <v>180002</v>
-      </c>
-      <c r="D7" s="11" t="s">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C7" s="1">
+        <v>21002</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="6">
-        <v>18</v>
-      </c>
-      <c r="F7" s="19" t="s">
+      <c r="E7" s="1">
+        <v>2</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="10">
-        <v>180003</v>
-      </c>
-      <c r="D8" s="11" t="s">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C8" s="1">
+        <v>21003</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="6">
-        <v>18</v>
-      </c>
-      <c r="F8" s="19" t="s">
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="10">
-        <v>180004</v>
-      </c>
-      <c r="D9" s="11" t="s">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C9" s="1">
+        <v>21004</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="6">
-        <v>18</v>
-      </c>
-      <c r="F9" s="19" t="s">
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="20" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:6">
-      <c r="C10" s="10">
-        <v>180005</v>
-      </c>
-      <c r="D10" s="11" t="s">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C10" s="1">
+        <v>21005</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="6">
-        <v>18</v>
-      </c>
-      <c r="F10" s="19" t="s">
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:6">
-      <c r="C11" s="10">
-        <v>180006</v>
-      </c>
-      <c r="D11" s="12" t="s">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C11" s="1">
+        <v>21006</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="6">
-        <v>18</v>
-      </c>
-      <c r="F11" s="19" t="s">
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:6">
-      <c r="C12" s="10">
-        <v>180007</v>
-      </c>
-      <c r="D12" s="11" t="s">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C12" s="1">
+        <v>21007</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E12" s="6">
-        <v>18</v>
-      </c>
-      <c r="F12" s="19" t="s">
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:6">
-      <c r="C13" s="10">
-        <v>180008</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E13" s="6">
-        <v>18</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:6">
-      <c r="C14" s="10">
-        <v>180009</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" s="6">
-        <v>18</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:6">
-      <c r="C15" s="10">
-        <v>180010</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="6">
-        <v>18</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:6">
-      <c r="C16" s="10">
-        <v>180011</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" s="6">
-        <v>18</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="10">
-        <v>180012</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" s="6">
-        <v>18</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="10">
-        <v>180013</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" s="6">
-        <v>18</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="10">
-        <v>180014</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" s="6">
-        <v>18</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="10">
-        <v>180015</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="E20" s="6">
-        <v>18</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:6">
-      <c r="C21" s="10">
-        <v>180016</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" s="6">
-        <v>18</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:6">
-      <c r="C22" s="10">
-        <v>180017</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="6">
-        <v>18</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:6">
-      <c r="C23" s="10">
-        <v>180018</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="E23" s="6">
-        <v>18</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:6">
-      <c r="C24" s="10">
-        <v>180019</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" s="6">
-        <v>18</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:6">
-      <c r="C25" s="10">
-        <v>180020</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" s="6">
-        <v>18</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:6">
-      <c r="C26" s="10">
-        <v>180021</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26" s="6">
-        <v>18</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:6">
-      <c r="C27" s="10">
-        <v>180022</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="6">
-        <v>18</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:6">
-      <c r="C28" s="10">
-        <v>180023</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E28" s="6">
-        <v>18</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:6">
-      <c r="C29" s="10">
-        <v>180024</v>
-      </c>
-      <c r="D29" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="E29" s="6">
-        <v>18</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:6">
-      <c r="C30" s="10">
-        <v>180025</v>
-      </c>
-      <c r="D30" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="E30" s="6">
-        <v>18</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:6">
-      <c r="C31" s="10">
-        <v>180026</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="E31" s="6">
-        <v>18</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:6">
-      <c r="C32" s="10">
-        <v>180027</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="E32" s="6">
-        <v>18</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:6">
-      <c r="C33" s="10">
-        <v>180028</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="E33" s="6">
-        <v>18</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:6">
-      <c r="C34" s="10">
-        <v>180029</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="E34" s="6">
-        <v>18</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:6">
-      <c r="C35" s="10">
-        <v>180030</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="E35" s="6">
-        <v>18</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:6">
-      <c r="C36" s="10">
-        <v>180031</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="E36" s="6">
-        <v>18</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:6">
-      <c r="C37" s="10">
-        <v>180032</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="E37" s="6">
-        <v>18</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:6">
-      <c r="C38" s="10">
-        <v>180033</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E38" s="6">
-        <v>18</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:6">
-      <c r="C39" s="10">
-        <v>180034</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E39" s="6">
-        <v>18</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:6">
-      <c r="C40" s="10">
-        <v>180035</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E40" s="6">
-        <v>18</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:6">
-      <c r="C41" s="10">
-        <v>180036</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" s="6">
-        <v>18</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:6">
-      <c r="C42" s="10">
-        <v>180037</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="E42" s="6">
-        <v>18</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:6">
-      <c r="C43" s="10">
-        <v>180038</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E43" s="6">
-        <v>18</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:6">
-      <c r="C44" s="10">
-        <v>180039</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E44" s="6">
-        <v>18</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:6">
-      <c r="C45" s="10">
-        <v>180040</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="E45" s="6">
-        <v>18</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:6">
-      <c r="C46" s="10">
-        <v>180041</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="E46" s="6">
-        <v>18</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:6">
-      <c r="C47" s="10">
-        <v>180042</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="E47" s="6">
-        <v>18</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:6">
-      <c r="C48" s="10">
-        <v>180043</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="E48" s="6">
-        <v>18</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:6">
-      <c r="C49" s="10">
-        <v>180044</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="E49" s="6">
-        <v>18</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:6">
-      <c r="C50" s="10">
-        <v>180045</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="E50" s="6">
-        <v>18</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:6">
-      <c r="C51" s="10">
-        <v>180046</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="E51" s="6">
-        <v>18</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:6">
-      <c r="C52" s="10">
-        <v>180047</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="E52" s="6">
-        <v>18</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:6">
-      <c r="C53" s="10">
-        <v>180048</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E53" s="6">
-        <v>18</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:6">
-      <c r="C54" s="10">
-        <v>180049</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E54" s="6">
-        <v>18</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:6">
-      <c r="C55" s="10">
-        <v>180050</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="E55" s="6">
-        <v>18</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:6">
-      <c r="C56" s="10">
-        <v>180051</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="E56" s="6">
-        <v>18</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:6">
-      <c r="C57" s="10">
-        <v>180052</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="E57" s="6">
-        <v>18</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:6">
-      <c r="C58" s="10">
-        <v>180053</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="E58" s="6">
-        <v>18</v>
-      </c>
-      <c r="F58" s="19" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:6">
-      <c r="C59" s="10">
-        <v>180054</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="E59" s="6">
-        <v>18</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:6">
-      <c r="C60" s="10">
-        <v>180055</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="E60" s="6">
-        <v>18</v>
-      </c>
-      <c r="F60" s="19" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:6">
-      <c r="C61" s="10">
-        <v>180056</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="E61" s="6">
-        <v>18</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:6">
-      <c r="C62" s="10">
-        <v>180057</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E62" s="6">
-        <v>18</v>
-      </c>
-      <c r="F62" s="19" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:6">
-      <c r="C63" s="10">
-        <v>180058</v>
-      </c>
-      <c r="D63" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="E63" s="6">
-        <v>18</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:6">
-      <c r="C64" s="10">
-        <v>180059</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="E64" s="6">
-        <v>18</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:6">
-      <c r="C65" s="10">
-        <v>180060</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>213</v>
-      </c>
-      <c r="E65" s="6">
-        <v>18</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:6">
-      <c r="C66" s="10">
-        <v>180061</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="E66" s="6">
-        <v>18</v>
-      </c>
-      <c r="F66" s="19" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:6">
-      <c r="C67" s="10">
-        <v>180062</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="E67" s="6">
-        <v>18</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:6">
-      <c r="C68" s="10">
-        <v>180063</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="E68" s="6">
-        <v>18</v>
-      </c>
-      <c r="F68" s="19" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:6">
-      <c r="C69" s="10">
-        <v>180064</v>
-      </c>
-      <c r="D69" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="E69" s="6">
-        <v>18</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:6">
-      <c r="C70" s="10">
-        <v>180065</v>
-      </c>
-      <c r="D70" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E70" s="6">
-        <v>18</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:6">
-      <c r="C71" s="10">
-        <v>180066</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="E71" s="6">
-        <v>18</v>
-      </c>
-      <c r="F71" s="19" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:6">
-      <c r="C72" s="10">
-        <v>180067</v>
-      </c>
-      <c r="D72" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="E72" s="6">
-        <v>18</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:6">
-      <c r="C73" s="10">
-        <v>180068</v>
-      </c>
-      <c r="D73" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="E73" s="6">
-        <v>18</v>
-      </c>
-      <c r="F73" s="19" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:6">
-      <c r="C74" s="10">
-        <v>180069</v>
-      </c>
-      <c r="D74" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E74" s="6">
-        <v>18</v>
-      </c>
-      <c r="F74" s="19" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:6">
-      <c r="C75" s="10">
-        <v>180070</v>
-      </c>
-      <c r="D75" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E75" s="6">
-        <v>18</v>
-      </c>
-      <c r="F75" s="19" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:6">
-      <c r="C76" s="10">
-        <v>180071</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="E76" s="6">
-        <v>18</v>
-      </c>
-      <c r="F76" s="19" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:6">
-      <c r="C77" s="10">
-        <v>180072</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="E77" s="6">
-        <v>18</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>237</v>
-      </c>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F14" s="15"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F15" s="15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F16" s="15"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F18" s="15"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F19" s="15"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F20" s="15"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F21" s="15"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F22" s="15"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F24" s="15"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F25" s="15"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F26" s="15"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F27" s="15"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F28" s="15"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F30" s="15"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F31" s="15"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F32" s="15"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F33" s="15"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F34" s="15"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F37" s="15"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F38" s="15"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F39" s="15"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F40" s="15"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F41" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4085,7 +3348,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F22"/>
+  <dimension ref="C1:F77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -4145,21 +3408,1012 @@
       </c>
     </row>
     <row r="6" s="6" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="6">
-        <v>30001</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="10">
+        <v>180001</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="6">
+        <v>18</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:6">
+      <c r="C7" s="10">
+        <v>180002</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="6">
+        <v>18</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:6">
+      <c r="C8" s="10">
+        <v>180003</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E8" s="6">
+        <v>18</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:6">
+      <c r="C9" s="10">
+        <v>180004</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="6">
+        <v>18</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:6">
+      <c r="C10" s="10">
+        <v>180005</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="6">
+        <v>18</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:6">
+      <c r="C11" s="10">
+        <v>180006</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="6">
+        <v>18</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:6">
+      <c r="C12" s="10">
+        <v>180007</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" s="6">
+        <v>18</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:6">
+      <c r="C13" s="10">
+        <v>180008</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="6">
+        <v>18</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:6">
+      <c r="C14" s="10">
+        <v>180009</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="6">
+        <v>18</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:6">
+      <c r="C15" s="10">
+        <v>180010</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E15" s="6">
+        <v>18</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:6">
+      <c r="C16" s="10">
+        <v>180011</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="6">
+        <v>18</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:6">
+      <c r="C17" s="10">
+        <v>180012</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E17" s="6">
+        <v>18</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:6">
+      <c r="C18" s="10">
+        <v>180013</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="6">
+        <v>18</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:6">
+      <c r="C19" s="10">
+        <v>180014</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" s="6">
+        <v>18</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:6">
+      <c r="C20" s="10">
+        <v>180015</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="E20" s="6">
+        <v>18</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:6">
+      <c r="C21" s="10">
+        <v>180016</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="6">
+        <v>18</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:6">
+      <c r="C22" s="10">
+        <v>180017</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E22" s="6">
+        <v>18</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:6">
+      <c r="C23" s="10">
+        <v>180018</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" s="6">
+        <v>18</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:6">
+      <c r="C24" s="10">
+        <v>180019</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E24" s="6">
+        <v>18</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:6">
+      <c r="C25" s="10">
+        <v>180020</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" s="6">
+        <v>18</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:6">
+      <c r="C26" s="10">
+        <v>180021</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" s="6">
+        <v>18</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:6">
+      <c r="C27" s="10">
+        <v>180022</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="6">
+        <v>18</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:6">
+      <c r="C28" s="10">
+        <v>180023</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E28" s="6">
+        <v>18</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:6">
+      <c r="C29" s="10">
+        <v>180024</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="E29" s="6">
+        <v>18</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:6">
+      <c r="C30" s="10">
+        <v>180025</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" s="6">
+        <v>18</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:6">
+      <c r="C31" s="10">
+        <v>180026</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E31" s="6">
+        <v>18</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:6">
+      <c r="C32" s="10">
+        <v>180027</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E32" s="6">
+        <v>18</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:6">
+      <c r="C33" s="10">
+        <v>180028</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="E33" s="6">
+        <v>18</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:6">
+      <c r="C34" s="10">
+        <v>180029</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="6">
+        <v>18</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:6">
+      <c r="C35" s="10">
+        <v>180030</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" s="6">
+        <v>18</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:6">
+      <c r="C36" s="10">
+        <v>180031</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" s="6">
+        <v>18</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:6">
+      <c r="C37" s="10">
+        <v>180032</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" s="6">
+        <v>18</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:6">
+      <c r="C38" s="10">
+        <v>180033</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="E38" s="6">
+        <v>18</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:6">
+      <c r="C39" s="10">
+        <v>180034</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" s="6">
+        <v>18</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:6">
+      <c r="C40" s="10">
+        <v>180035</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E40" s="6">
+        <v>18</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:6">
+      <c r="C41" s="10">
+        <v>180036</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" s="6">
+        <v>18</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:6">
+      <c r="C42" s="10">
+        <v>180037</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E42" s="6">
+        <v>18</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:6">
+      <c r="C43" s="10">
+        <v>180038</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" s="6">
+        <v>18</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:6">
+      <c r="C44" s="10">
+        <v>180039</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E44" s="6">
+        <v>18</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:6">
+      <c r="C45" s="10">
+        <v>180040</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="E45" s="6">
+        <v>18</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:6">
+      <c r="C46" s="10">
+        <v>180041</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E46" s="6">
+        <v>18</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:6">
+      <c r="C47" s="10">
+        <v>180042</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" s="6">
+        <v>18</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:6">
+      <c r="C48" s="10">
+        <v>180043</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="6">
+        <v>18</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:6">
+      <c r="C49" s="10">
+        <v>180044</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="E49" s="6">
+        <v>18</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:6">
+      <c r="C50" s="10">
+        <v>180045</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E50" s="6">
+        <v>18</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:6">
+      <c r="C51" s="10">
+        <v>180046</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E51" s="6">
+        <v>18</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:6">
+      <c r="C52" s="10">
+        <v>180047</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E52" s="6">
+        <v>18</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:6">
+      <c r="C53" s="10">
+        <v>180048</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="E53" s="6">
+        <v>18</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:6">
+      <c r="C54" s="10">
+        <v>180049</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E54" s="6">
+        <v>18</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:6">
+      <c r="C55" s="10">
+        <v>180050</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E55" s="6">
+        <v>18</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:6">
+      <c r="C56" s="10">
+        <v>180051</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E56" s="6">
+        <v>18</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:6">
+      <c r="C57" s="10">
+        <v>180052</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E57" s="6">
+        <v>18</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:6">
+      <c r="C58" s="10">
+        <v>180053</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E58" s="6">
+        <v>18</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:6">
+      <c r="C59" s="10">
+        <v>180054</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E59" s="6">
+        <v>18</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:6">
+      <c r="C60" s="10">
+        <v>180055</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="E60" s="6">
+        <v>18</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:6">
+      <c r="C61" s="10">
+        <v>180056</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="E61" s="6">
+        <v>18</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:6">
+      <c r="C62" s="10">
+        <v>180057</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="E62" s="6">
+        <v>18</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:6">
+      <c r="C63" s="10">
+        <v>180058</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="E63" s="6">
+        <v>18</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:6">
+      <c r="C64" s="10">
+        <v>180059</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E64" s="6">
+        <v>18</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:6">
+      <c r="C65" s="10">
+        <v>180060</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="E65" s="6">
+        <v>18</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:6">
+      <c r="C66" s="10">
+        <v>180061</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E66" s="6">
+        <v>18</v>
+      </c>
+      <c r="F66" s="19" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:6">
+      <c r="C67" s="10">
+        <v>180062</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E67" s="6">
+        <v>18</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:6">
+      <c r="C68" s="10">
+        <v>180063</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E68" s="6">
+        <v>18</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:6">
+      <c r="C69" s="10">
+        <v>180064</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E69" s="6">
+        <v>18</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:6">
+      <c r="C70" s="10">
+        <v>180065</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E70" s="6">
+        <v>18</v>
+      </c>
+      <c r="F70" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="E6" s="6">
-        <v>3</v>
-      </c>
-      <c r="F6" s="6" t="s">
+    </row>
+    <row r="71" customHeight="1" spans="3:6">
+      <c r="C71" s="10">
+        <v>180066</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C22" s="10"/>
+      <c r="E71" s="6">
+        <v>18</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:6">
+      <c r="C72" s="10">
+        <v>180067</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="E72" s="6">
+        <v>18</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:6">
+      <c r="C73" s="10">
+        <v>180068</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="E73" s="6">
+        <v>18</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:6">
+      <c r="C74" s="10">
+        <v>180069</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="E74" s="6">
+        <v>18</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:6">
+      <c r="C75" s="10">
+        <v>180070</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="E75" s="6">
+        <v>18</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:6">
+      <c r="C76" s="10">
+        <v>180071</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="E76" s="6">
+        <v>18</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:6">
+      <c r="C77" s="10">
+        <v>180072</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="E77" s="6">
+        <v>18</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>251</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4176,16 +4430,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F32"/>
-  <sheetFormatPr defaultColWidth="12.25" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="C1:F22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="12.25" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5833333333333" style="1" customWidth="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="8.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.4166666666667" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="12.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.0833333333333" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4236,158 +4489,22 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="5">
-        <v>40001</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="E6" s="1">
-        <v>4</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C7" s="5">
-        <v>40002</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="E7" s="1">
-        <v>4</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C8" s="5">
-        <v>40003</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E8" s="1">
-        <v>4</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C9" s="5">
-        <v>40004</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="E9" s="1">
-        <v>4</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C10" s="5">
-        <v>40005</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="E10" s="1">
-        <v>4</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C11" s="5">
-        <v>40006</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E11" s="1">
-        <v>4</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C12" s="5">
-        <v>40007</v>
-      </c>
-      <c r="D12" s="1" t="s">
+    <row r="6" s="6" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="6">
+        <v>30001</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E12" s="1">
-        <v>4</v>
-      </c>
-      <c r="F12" s="18" t="s">
+      <c r="E6" s="6">
+        <v>3</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C13" s="5">
-        <v>40008</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E13" s="1">
-        <v>4</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:6">
-      <c r="C14" s="5">
-        <v>40009</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E14" s="1">
-        <v>4</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F25" s="8"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F27" s="8"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F28" s="8"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F29" s="8"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F31" s="8"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F32" s="8"/>
+    <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
+      <c r="C22" s="10"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4466,16 +4583,244 @@
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C6" s="5">
+        <v>40001</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C7" s="5">
+        <v>40002</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C8" s="5">
+        <v>40003</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="1">
+        <v>4</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C9" s="5">
+        <v>40004</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="E9" s="1">
+        <v>4</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C10" s="5">
+        <v>40005</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E10" s="1">
+        <v>4</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C11" s="5">
+        <v>40006</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E11" s="1">
+        <v>4</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C12" s="5">
+        <v>40007</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C13" s="5">
+        <v>40008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:6">
+      <c r="C14" s="5">
+        <v>40009</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F27" s="8"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F29" s="8"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F30" s="8"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="6:6">
+      <c r="F32" s="8"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C2:C5" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C2)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C1:F32"/>
+  <sheetFormatPr defaultColWidth="12.25" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="12.25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.4166666666667" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="12.25" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="5">
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4483,13 +4828,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4497,13 +4842,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4511,13 +4856,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4525,13 +4870,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4539,13 +4884,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4553,13 +4898,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4567,13 +4912,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4581,13 +4926,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -4595,13 +4940,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -4609,13 +4954,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -4623,13 +4968,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -421,7 +421,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="308">
   <si>
     <t>_id</t>
   </si>
@@ -1309,6 +1309,42 @@
   </si>
   <si>
     <t>40000012</t>
+  </si>
+  <si>
+    <t>骨弓</t>
+  </si>
+  <si>
+    <t>40000013</t>
+  </si>
+  <si>
+    <t>骨杖</t>
+  </si>
+  <si>
+    <t>40000014</t>
+  </si>
+  <si>
+    <t>骨龙核心</t>
+  </si>
+  <si>
+    <t>40000015</t>
+  </si>
+  <si>
+    <t>獠牙</t>
+  </si>
+  <si>
+    <t>40000016</t>
+  </si>
+  <si>
+    <t>图腾</t>
+  </si>
+  <si>
+    <t>40000017</t>
+  </si>
+  <si>
+    <t>酋长重锤</t>
+  </si>
+  <si>
+    <t>40000018</t>
   </si>
 </sst>
 </file>
@@ -1505,12 +1541,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4977,6 +5013,90 @@
         <v>295</v>
       </c>
     </row>
+    <row r="18" customHeight="1" spans="3:6">
+      <c r="C18" s="5">
+        <v>50013</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E18" s="1">
+        <v>6</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:6">
+      <c r="C19" s="5">
+        <v>50014</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="E19" s="1">
+        <v>6</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:6">
+      <c r="C20" s="5">
+        <v>50015</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="E20" s="1">
+        <v>6</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:6">
+      <c r="C21" s="5">
+        <v>50016</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E21" s="1">
+        <v>6</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:6">
+      <c r="C22" s="5">
+        <v>50017</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E22" s="1">
+        <v>6</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:6">
+      <c r="C23" s="5">
+        <v>50018</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="E23" s="1">
+        <v>6</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>307</v>
+      </c>
+    </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F24" s="8"/>
     </row>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="6"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -421,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="318">
   <si>
     <t>_id</t>
   </si>
@@ -496,6 +501,36 @@
   </si>
   <si>
     <t>40000003,40000006,40000009,40000012</t>
+  </si>
+  <si>
+    <t>神兵符1</t>
+  </si>
+  <si>
+    <t>5015</t>
+  </si>
+  <si>
+    <t>神兵符2</t>
+  </si>
+  <si>
+    <t>5016</t>
+  </si>
+  <si>
+    <t>神兵符3</t>
+  </si>
+  <si>
+    <t>5017</t>
+  </si>
+  <si>
+    <t>神兵符4</t>
+  </si>
+  <si>
+    <t>5018</t>
+  </si>
+  <si>
+    <t>神兵符5</t>
+  </si>
+  <si>
+    <t>5019</t>
   </si>
   <si>
     <t>1级链头</t>
@@ -2540,7 +2575,77 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" s="8" customFormat="1" customHeight="1" spans="3:3">
+    <row r="16" customHeight="1" spans="3:6">
+      <c r="C16" s="8">
+        <v>11</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="8">
+        <v>5</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:6">
+      <c r="C17" s="8">
+        <v>12</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="8">
+        <v>5</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:6">
+      <c r="C18" s="8">
+        <v>13</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="8">
+        <v>5</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:6">
+      <c r="C19" s="8">
+        <v>14</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="8">
+        <v>5</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:6">
+      <c r="C20" s="8">
+        <v>15</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="8">
+        <v>5</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" s="8" customFormat="1" customHeight="1" spans="3:6">
       <c r="C22" s="17"/>
     </row>
   </sheetData>
@@ -2616,13 +2721,13 @@
         <v>20001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -2630,13 +2735,13 @@
         <v>20002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -2644,13 +2749,13 @@
         <v>20003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -2658,13 +2763,13 @@
         <v>20004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -2672,13 +2777,13 @@
         <v>20005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -2686,13 +2791,13 @@
         <v>20006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -2700,13 +2805,13 @@
         <v>20007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -2714,13 +2819,13 @@
         <v>20008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -2728,13 +2833,13 @@
         <v>20009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -2742,13 +2847,13 @@
         <v>20010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -2756,13 +2861,13 @@
         <v>20011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -2770,13 +2875,13 @@
         <v>20012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -2784,13 +2889,13 @@
         <v>20013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -2798,13 +2903,13 @@
         <v>20014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -2812,13 +2917,13 @@
         <v>20015</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -2826,13 +2931,13 @@
         <v>20016</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -2840,13 +2945,13 @@
         <v>20017</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -2854,13 +2959,13 @@
         <v>20018</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -2868,13 +2973,13 @@
         <v>20019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -2882,13 +2987,13 @@
         <v>20020</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -2896,13 +3001,13 @@
         <v>20021</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -2910,13 +3015,13 @@
         <v>20022</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -2924,13 +3029,13 @@
         <v>20023</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -2938,13 +3043,13 @@
         <v>20024</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -2952,13 +3057,13 @@
         <v>20025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -2966,13 +3071,13 @@
         <v>20026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -2980,13 +3085,13 @@
         <v>20027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -2994,13 +3099,13 @@
         <v>20028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -3008,13 +3113,13 @@
         <v>20029</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -3022,13 +3127,13 @@
         <v>20030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -3036,13 +3141,13 @@
         <v>20031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -3050,13 +3155,13 @@
         <v>20032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -3064,13 +3169,13 @@
         <v>20033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -3078,13 +3183,13 @@
         <v>20034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -3092,13 +3197,13 @@
         <v>20035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -3106,13 +3211,13 @@
         <v>20036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -3189,13 +3294,13 @@
         <v>21001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3203,13 +3308,13 @@
         <v>21002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3217,13 +3322,13 @@
         <v>21003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3231,13 +3336,13 @@
         <v>21004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3245,13 +3350,13 @@
         <v>21005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3259,13 +3364,13 @@
         <v>21006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3273,13 +3378,13 @@
         <v>21007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -3448,13 +3553,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -3462,13 +3567,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -3476,13 +3581,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -3490,13 +3595,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -3504,13 +3609,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -3518,13 +3623,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -3532,13 +3637,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -3546,13 +3651,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -3560,13 +3665,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -3574,13 +3679,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -3588,13 +3693,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -3602,13 +3707,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -3616,13 +3721,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -3630,13 +3735,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -3644,13 +3749,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -3658,13 +3763,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -3672,13 +3777,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -3686,13 +3791,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -3700,13 +3805,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -3714,13 +3819,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -3728,13 +3833,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -3742,13 +3847,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -3756,13 +3861,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -3770,13 +3875,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -3784,13 +3889,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -3798,13 +3903,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -3812,13 +3917,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -3826,13 +3931,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -3840,13 +3945,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -3854,13 +3959,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -3868,13 +3973,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -3882,13 +3987,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -3896,13 +4001,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -3910,13 +4015,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -3924,13 +4029,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -3938,13 +4043,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -3952,13 +4057,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -3966,13 +4071,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -3980,13 +4085,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -3994,13 +4099,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -4008,13 +4113,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -4022,13 +4127,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -4036,13 +4141,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -4050,13 +4155,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -4064,13 +4169,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -4078,13 +4183,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -4092,13 +4197,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -4106,13 +4211,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -4120,13 +4225,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -4134,13 +4239,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -4148,13 +4253,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -4162,13 +4267,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -4176,13 +4281,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -4190,13 +4295,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -4204,13 +4309,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -4218,13 +4323,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -4232,13 +4337,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -4246,13 +4351,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -4260,13 +4365,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -4274,13 +4379,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -4288,13 +4393,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -4302,13 +4407,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -4316,13 +4421,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -4330,13 +4435,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -4344,13 +4449,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -4358,13 +4463,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -4372,13 +4477,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -4386,13 +4491,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -4400,13 +4505,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -4414,13 +4519,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -4428,13 +4533,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -4442,13 +4547,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -4530,13 +4635,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -4622,13 +4727,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4636,13 +4741,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4650,13 +4755,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4664,13 +4769,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4678,13 +4783,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4692,13 +4797,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4706,13 +4811,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4720,13 +4825,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4734,13 +4839,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -4850,13 +4955,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4864,13 +4969,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4878,13 +4983,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4892,13 +4997,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4906,13 +5011,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4920,13 +5025,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4934,13 +5039,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4948,13 +5053,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4962,13 +5067,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -4976,13 +5081,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -4990,13 +5095,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5004,13 +5109,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5018,13 +5123,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -5032,13 +5137,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -5046,13 +5151,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -5060,13 +5165,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -5074,13 +5179,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -5088,13 +5193,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="320">
   <si>
     <t>_id</t>
   </si>
@@ -789,6 +789,12 @@
   </si>
   <si>
     <t>201019,201020,201021</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>贪婪</t>
   </si>
   <si>
     <t>狼宝宝</t>
@@ -3236,7 +3242,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F41"/>
+  <dimension ref="A3:F41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -3247,7 +3253,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -3261,7 +3267,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
@@ -3275,7 +3281,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="11.5" spans="3:6">
+    <row r="5" s="1" customFormat="1" ht="11.5" spans="1:6">
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
@@ -3289,7 +3295,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C6" s="1">
         <v>21001</v>
       </c>
@@ -3303,7 +3309,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C7" s="1">
         <v>21002</v>
       </c>
@@ -3317,7 +3323,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C8" s="1">
         <v>21003</v>
       </c>
@@ -3331,7 +3337,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C9" s="1">
         <v>21004</v>
       </c>
@@ -3345,7 +3351,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C10" s="1">
         <v>21005</v>
       </c>
@@ -3359,7 +3365,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C11" s="1">
         <v>21006</v>
       </c>
@@ -3373,7 +3379,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C12" s="1">
         <v>21007</v>
       </c>
@@ -3387,64 +3393,91 @@
         <v>120</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="1">
+        <v>21008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
       <c r="F13" s="15"/>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="C14" s="1">
+        <v>21009</v>
+      </c>
       <c r="F14" s="15"/>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="C15" s="1">
+        <v>21010</v>
+      </c>
       <c r="F15" s="15"/>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="C16" s="1">
+        <v>21011</v>
+      </c>
       <c r="F16" s="15"/>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C17" s="1">
+        <v>21012</v>
+      </c>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F18" s="15"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F19" s="15"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F20" s="15"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F21" s="15"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F22" s="15"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F23" s="2"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F24" s="15"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F25" s="15"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F26" s="15"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F27" s="15"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F28" s="15"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F30" s="15"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F31" s="15"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="6:6">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F32" s="15"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -3553,13 +3586,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -3567,13 +3600,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -3581,13 +3614,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -3595,13 +3628,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -3609,13 +3642,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -3623,13 +3656,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -3637,13 +3670,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -3651,13 +3684,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -3665,13 +3698,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -3679,13 +3712,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -3693,13 +3726,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -3707,13 +3740,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -3721,13 +3754,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -3735,13 +3768,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -3749,13 +3782,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -3763,13 +3796,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -3777,13 +3810,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -3791,13 +3824,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -3805,13 +3838,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -3819,13 +3852,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -3833,13 +3866,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -3847,13 +3880,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -3861,13 +3894,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -3875,13 +3908,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -3889,13 +3922,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -3903,13 +3936,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -3917,13 +3950,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -3931,13 +3964,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -3945,13 +3978,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -3959,13 +3992,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -3973,13 +4006,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -3987,13 +4020,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -4001,13 +4034,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -4015,13 +4048,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -4029,13 +4062,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -4043,13 +4076,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -4057,13 +4090,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -4071,13 +4104,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -4085,13 +4118,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -4099,13 +4132,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -4113,13 +4146,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -4127,13 +4160,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -4141,13 +4174,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -4155,13 +4188,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -4169,13 +4202,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -4183,13 +4216,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -4197,13 +4230,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -4211,13 +4244,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -4225,13 +4258,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -4239,13 +4272,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -4253,13 +4286,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -4267,13 +4300,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -4281,13 +4314,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -4295,13 +4328,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -4309,13 +4342,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -4323,13 +4356,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -4337,13 +4370,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -4351,13 +4384,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -4365,13 +4398,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -4379,13 +4412,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -4393,13 +4426,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -4407,13 +4440,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -4421,13 +4454,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -4435,13 +4468,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -4449,13 +4482,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -4463,13 +4496,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -4477,13 +4510,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -4491,13 +4524,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -4505,13 +4538,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -4519,13 +4552,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -4533,13 +4566,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -4547,13 +4580,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -4635,13 +4668,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -4727,13 +4760,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4741,13 +4774,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4755,13 +4788,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4769,13 +4802,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4783,13 +4816,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4797,13 +4830,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4811,13 +4844,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4825,13 +4858,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4839,13 +4872,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -4955,13 +4988,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4969,13 +5002,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4983,13 +5016,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4997,13 +5030,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5011,13 +5044,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5025,13 +5058,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5039,13 +5072,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5053,13 +5086,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5067,13 +5100,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -5081,13 +5114,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -5095,13 +5128,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5109,13 +5142,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5123,13 +5156,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -5137,13 +5170,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -5151,13 +5184,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -5165,13 +5198,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -5179,13 +5212,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -5193,13 +5226,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="320">
   <si>
     <t>_id</t>
   </si>
@@ -788,13 +788,13 @@
     <t>天命</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>贪婪</t>
+  </si>
+  <si>
     <t>201019,201020,201021</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>贪婪</t>
   </si>
   <si>
     <t>狼宝宝</t>
@@ -3390,26 +3390,28 @@
         <v>2</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C13" s="1">
         <v>21008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="15"/>
+      <c r="F13" s="20" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C14" s="1">

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="356">
   <si>
     <t>_id</t>
   </si>
@@ -747,6 +747,114 @@
   </si>
   <si>
     <t>210051,220051,230051</t>
+  </si>
+  <si>
+    <t>60级链头</t>
+  </si>
+  <si>
+    <t>210063,220063,230063,210064,220064,230064</t>
+  </si>
+  <si>
+    <t>60级手镯</t>
+  </si>
+  <si>
+    <t>210065,220065,230065</t>
+  </si>
+  <si>
+    <t>60级戒指</t>
+  </si>
+  <si>
+    <t>210066,220066,230066</t>
+  </si>
+  <si>
+    <t>60级腰鞋</t>
+  </si>
+  <si>
+    <t>210067,220067,230067,210068,220068,230068</t>
+  </si>
+  <si>
+    <t>60级衣服</t>
+  </si>
+  <si>
+    <t>210062,220062,230062</t>
+  </si>
+  <si>
+    <t>60级武器</t>
+  </si>
+  <si>
+    <t>210061,220061,230061</t>
+  </si>
+  <si>
+    <t>70级链头</t>
+  </si>
+  <si>
+    <t>210073,220073,230073,210074,220074,230074</t>
+  </si>
+  <si>
+    <t>70级手镯</t>
+  </si>
+  <si>
+    <t>210075,220075,230075</t>
+  </si>
+  <si>
+    <t>70级戒指</t>
+  </si>
+  <si>
+    <t>210076,220076,230076</t>
+  </si>
+  <si>
+    <t>70级腰鞋</t>
+  </si>
+  <si>
+    <t>210077,220077,230077,210078,220078,230078</t>
+  </si>
+  <si>
+    <t>70级衣服</t>
+  </si>
+  <si>
+    <t>210072,220072,230072</t>
+  </si>
+  <si>
+    <t>70级武器</t>
+  </si>
+  <si>
+    <t>210071,220071,230071</t>
+  </si>
+  <si>
+    <t>80级链头</t>
+  </si>
+  <si>
+    <t>210083,220083,230083,210084,220084,230084</t>
+  </si>
+  <si>
+    <t>80级手镯</t>
+  </si>
+  <si>
+    <t>210085,220085,230085</t>
+  </si>
+  <si>
+    <t>80级戒指</t>
+  </si>
+  <si>
+    <t>210086,220086,230086</t>
+  </si>
+  <si>
+    <t>80级腰鞋</t>
+  </si>
+  <si>
+    <t>210087,220087,230087,210088,220088,230088</t>
+  </si>
+  <si>
+    <t>80级衣服</t>
+  </si>
+  <si>
+    <t>210082,220082,230082</t>
+  </si>
+  <si>
+    <t>80级武器</t>
+  </si>
+  <si>
+    <t>210081,220081,230081</t>
   </si>
   <si>
     <t>治愈</t>
@@ -2669,7 +2777,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F41"/>
+  <dimension ref="C3:F59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -3224,6 +3332,258 @@
       </c>
       <c r="F41" s="21" t="s">
         <v>106</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:6">
+      <c r="C42" s="1">
+        <v>20037</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:6">
+      <c r="C43" s="1">
+        <v>20038</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:6">
+      <c r="C44" s="1">
+        <v>20039</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" s="1">
+        <v>2</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:6">
+      <c r="C45" s="1">
+        <v>20040</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:6">
+      <c r="C46" s="1">
+        <v>20041</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E46" s="1">
+        <v>2</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:6">
+      <c r="C47" s="1">
+        <v>20042</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E47" s="1">
+        <v>2</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:6">
+      <c r="C48" s="1">
+        <v>20043</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E48" s="1">
+        <v>2</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:6">
+      <c r="C49" s="1">
+        <v>20044</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E49" s="1">
+        <v>2</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:6">
+      <c r="C50" s="1">
+        <v>20045</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E50" s="1">
+        <v>2</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:6">
+      <c r="C51" s="1">
+        <v>20046</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" s="1">
+        <v>2</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:6">
+      <c r="C52" s="1">
+        <v>20047</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E52" s="1">
+        <v>2</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:6">
+      <c r="C53" s="1">
+        <v>20048</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E53" s="1">
+        <v>2</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:6">
+      <c r="C54" s="1">
+        <v>20049</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E54" s="1">
+        <v>2</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:6">
+      <c r="C55" s="1">
+        <v>20050</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E55" s="1">
+        <v>2</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:6">
+      <c r="C56" s="1">
+        <v>20051</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E56" s="1">
+        <v>2</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:6">
+      <c r="C57" s="1">
+        <v>20052</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E57" s="1">
+        <v>2</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:6">
+      <c r="C58" s="1">
+        <v>20053</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E58" s="1">
+        <v>2</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:6">
+      <c r="C59" s="1">
+        <v>20054</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E59" s="1">
+        <v>2</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3300,13 +3660,13 @@
         <v>21001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3314,13 +3674,13 @@
         <v>21002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3328,13 +3688,13 @@
         <v>21003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3342,13 +3702,13 @@
         <v>21004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3356,13 +3716,13 @@
         <v>21005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3370,13 +3730,13 @@
         <v>21006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3384,33 +3744,33 @@
         <v>21007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="C13" s="1">
         <v>21008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3588,13 +3948,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>124</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -3602,13 +3962,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -3616,13 +3976,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -3630,13 +3990,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>130</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -3644,13 +4004,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -3658,13 +4018,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -3672,13 +4032,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -3686,13 +4046,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -3700,13 +4060,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -3714,13 +4074,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -3728,13 +4088,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -3742,13 +4102,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -3756,13 +4116,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -3770,13 +4130,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -3784,13 +4144,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -3798,13 +4158,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -3812,13 +4172,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -3826,13 +4186,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -3840,13 +4200,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -3854,13 +4214,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -3868,13 +4228,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -3882,13 +4242,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -3896,13 +4256,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -3910,13 +4270,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -3924,13 +4284,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -3938,13 +4298,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -3952,13 +4312,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -3966,13 +4326,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -3980,13 +4340,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -3994,13 +4354,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -4008,13 +4368,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -4022,13 +4382,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -4036,13 +4396,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -4050,13 +4410,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -4064,13 +4424,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -4078,13 +4438,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -4092,13 +4452,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="13" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -4106,13 +4466,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -4120,13 +4480,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -4134,13 +4494,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -4148,13 +4508,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -4162,13 +4522,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -4176,13 +4536,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -4190,13 +4550,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -4204,13 +4564,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -4218,13 +4578,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -4232,13 +4592,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -4246,13 +4606,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -4260,13 +4620,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -4274,13 +4634,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -4288,13 +4648,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -4302,13 +4662,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -4316,13 +4676,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -4330,13 +4690,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -4344,13 +4704,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -4358,13 +4718,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -4372,13 +4732,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -4386,13 +4746,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -4400,13 +4760,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -4414,13 +4774,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -4428,13 +4788,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -4442,13 +4802,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -4456,13 +4816,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -4470,13 +4830,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -4484,13 +4844,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>250</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -4498,13 +4858,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -4512,13 +4872,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -4526,13 +4886,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -4540,13 +4900,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -4554,13 +4914,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -4568,13 +4928,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -4582,13 +4942,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -4670,13 +5030,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -4762,13 +5122,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4776,13 +5136,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4790,13 +5150,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4804,13 +5164,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4818,13 +5178,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4832,13 +5192,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4846,13 +5206,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4860,13 +5220,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4874,13 +5234,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -4990,13 +5350,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5004,13 +5364,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5018,13 +5378,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5032,13 +5392,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5046,13 +5406,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5060,13 +5420,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5074,13 +5434,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5088,13 +5448,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5102,13 +5462,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -5116,13 +5476,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -5130,13 +5490,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5144,13 +5504,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5158,13 +5518,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -5172,13 +5532,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -5186,13 +5546,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -5200,13 +5560,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -5214,13 +5574,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -5228,13 +5588,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="362">
   <si>
     <t>_id</t>
   </si>
@@ -1494,6 +1494,24 @@
   </si>
   <si>
     <t>40000018</t>
+  </si>
+  <si>
+    <t>‌血花露‌</t>
+  </si>
+  <si>
+    <t>40000019</t>
+  </si>
+  <si>
+    <t>火甲虫</t>
+  </si>
+  <si>
+    <t>40000020</t>
+  </si>
+  <si>
+    <t>炎魔火髓</t>
+  </si>
+  <si>
+    <t>40000021</t>
   </si>
 </sst>
 </file>
@@ -5598,13 +5616,46 @@
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F24" s="8"/>
+      <c r="C24" s="5">
+        <v>50019</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E24" s="1">
+        <v>6</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>357</v>
+      </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F25" s="8"/>
+      <c r="C25" s="5">
+        <v>50020</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F26" s="8"/>
+      <c r="C26" s="5">
+        <v>50021</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E26" s="1">
+        <v>6</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F27" s="8"/>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="6"/>
+    <workbookView windowWidth="25600" windowHeight="11480" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="380">
   <si>
     <t>_id</t>
   </si>
@@ -1512,6 +1512,77 @@
   </si>
   <si>
     <t>40000021</t>
+  </si>
+  <si>
+    <t>‌冰蝎爪</t>
+  </si>
+  <si>
+    <t>40000022</t>
+  </si>
+  <si>
+    <t>龙龟蛋</t>
+  </si>
+  <si>
+    <t>40000023</t>
+  </si>
+  <si>
+    <t>冰兽魔核</t>
+  </si>
+  <si>
+    <t>40000024</t>
+  </si>
+  <si>
+    <t>鬼面毒囊</t>
+  </si>
+  <si>
+    <t>40000025</t>
+  </si>
+  <si>
+    <t>巨蜥毒牙</t>
+  </si>
+  <si>
+    <t>40000026</t>
+  </si>
+  <si>
+    <t>暗影徽记</t>
+  </si>
+  <si>
+    <t>40000027</t>
+  </si>
+  <si>
+    <t>巨熊掌</t>
+  </si>
+  <si>
+    <t>40000028</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>‌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF333333"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>狂暴牛角</t>
+    </r>
+  </si>
+  <si>
+    <t>40000029</t>
+  </si>
+  <si>
+    <t>亲卫令牌</t>
+  </si>
+  <si>
+    <t>40000030</t>
   </si>
 </sst>
 </file>
@@ -1524,7 +1595,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1557,6 +1628,12 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2043,137 +2120,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2192,6 +2269,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2209,7 +2287,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2222,7 +2300,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -2553,168 +2631,168 @@
   <dimension ref="C1:F22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9" style="8"/>
-    <col min="3" max="3" width="8.75" style="8" customWidth="1"/>
-    <col min="4" max="4" width="15" style="8" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="8" customWidth="1"/>
+    <col min="1" max="2" width="9" style="9"/>
+    <col min="3" max="3" width="8.75" style="9" customWidth="1"/>
+    <col min="4" max="4" width="15" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="9" customWidth="1"/>
     <col min="6" max="6" width="30.75" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="8"/>
+    <col min="7" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="1" customHeight="1" spans="3:6">
+    <row r="1" s="9" customFormat="1" customHeight="1" spans="3:6">
       <c r="F1" s="2"/>
     </row>
-    <row r="2" s="8" customFormat="1" customHeight="1" spans="3:6">
+    <row r="2" s="9" customFormat="1" customHeight="1" spans="3:6">
       <c r="F2" s="2"/>
     </row>
-    <row r="3" s="8" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C3" s="16" t="s">
+    <row r="3" s="9" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C4" s="16" t="s">
+    <row r="4" s="9" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="17" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="8" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C5" s="16" t="s">
+    <row r="5" s="9" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="17" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="8" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="8">
+    <row r="6" s="9" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="9">
         <v>1</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="9">
         <v>5</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="8">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="9">
+        <v>2</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="9">
         <v>5</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="8">
+      <c r="C8" s="9">
         <v>3</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="9">
         <v>5</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="19" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <v>4</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="9">
         <v>5</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
-      <c r="C10" s="8">
+      <c r="C10" s="9">
         <v>5</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="9">
         <v>6</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="20" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
-      <c r="C11" s="8">
+      <c r="C11" s="9">
         <v>6</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="9">
         <v>6</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
-      <c r="C12" s="8">
+      <c r="C12" s="9">
         <v>7</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="9">
         <v>6</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="20" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
-      <c r="C16" s="8">
+      <c r="C16" s="9">
         <v>11</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="9">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="s">
@@ -2722,13 +2800,13 @@
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="8">
+      <c r="C17" s="9">
         <v>12</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="9">
         <v>5</v>
       </c>
       <c r="F17" s="2" t="s">
@@ -2736,13 +2814,13 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <v>13</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="9">
         <v>5</v>
       </c>
       <c r="F18" s="2" t="s">
@@ -2750,13 +2828,13 @@
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <v>14</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="9">
         <v>5</v>
       </c>
       <c r="F19" s="2" t="s">
@@ -2764,21 +2842,21 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="8">
+      <c r="C20" s="9">
         <v>15</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="9">
         <v>5</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" s="8" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C22" s="17"/>
+    <row r="22" s="9" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C22" s="18"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2858,7 +2936,7 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2872,7 +2950,7 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="21" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2886,7 +2964,7 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="21" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2900,7 +2978,7 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="21" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2914,7 +2992,7 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="21" t="s">
         <v>44</v>
       </c>
     </row>
@@ -2928,7 +3006,7 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="22" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2942,7 +3020,7 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="21" t="s">
         <v>48</v>
       </c>
     </row>
@@ -2956,7 +3034,7 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="21" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2970,7 +3048,7 @@
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="21" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2984,7 +3062,7 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="21" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2998,7 +3076,7 @@
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="21" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3012,7 +3090,7 @@
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="22" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3026,7 +3104,7 @@
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="21" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3040,7 +3118,7 @@
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="21" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3054,7 +3132,7 @@
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F20" s="21" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3068,7 +3146,7 @@
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="21" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3082,7 +3160,7 @@
       <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="F22" s="21" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3096,7 +3174,7 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="22" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3110,7 +3188,7 @@
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="21" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3124,7 +3202,7 @@
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="F25" s="21" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3138,7 +3216,7 @@
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="21" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3152,7 +3230,7 @@
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="21" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3166,7 +3244,7 @@
       <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="F28" s="21" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3180,7 +3258,7 @@
       <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="22" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3194,7 +3272,7 @@
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="21" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3208,7 +3286,7 @@
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="F31" s="21" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3222,7 +3300,7 @@
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="F32" s="21" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3236,7 +3314,7 @@
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="21" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3250,7 +3328,7 @@
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="F34" s="21" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3264,7 +3342,7 @@
       <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="21" t="s">
+      <c r="F35" s="22" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3278,7 +3356,7 @@
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="21" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3292,7 +3370,7 @@
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="21" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3306,7 +3384,7 @@
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="F38" s="21" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3320,7 +3398,7 @@
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="21" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3334,7 +3412,7 @@
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="F40" s="21" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3348,7 +3426,7 @@
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="21" t="s">
+      <c r="F41" s="22" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3362,7 +3440,7 @@
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="21" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3376,7 +3454,7 @@
       <c r="E43" s="1">
         <v>2</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="F43" s="21" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3390,7 +3468,7 @@
       <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="21" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3404,7 +3482,7 @@
       <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="F45" s="21" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3418,7 +3496,7 @@
       <c r="E46" s="1">
         <v>2</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" s="21" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3432,7 +3510,7 @@
       <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F47" s="22" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3446,7 +3524,7 @@
       <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="F48" s="21" t="s">
+      <c r="F48" s="22" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3460,7 +3538,7 @@
       <c r="E49" s="1">
         <v>2</v>
       </c>
-      <c r="F49" s="21" t="s">
+      <c r="F49" s="22" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3474,7 +3552,7 @@
       <c r="E50" s="1">
         <v>2</v>
       </c>
-      <c r="F50" s="21" t="s">
+      <c r="F50" s="22" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3488,7 +3566,7 @@
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="21" t="s">
+      <c r="F51" s="22" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3502,7 +3580,7 @@
       <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F52" s="21" t="s">
+      <c r="F52" s="22" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3516,7 +3594,7 @@
       <c r="E53" s="1">
         <v>2</v>
       </c>
-      <c r="F53" s="21" t="s">
+      <c r="F53" s="22" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3530,7 +3608,7 @@
       <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="21" t="s">
+      <c r="F54" s="22" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3544,7 +3622,7 @@
       <c r="E55" s="1">
         <v>2</v>
       </c>
-      <c r="F55" s="21" t="s">
+      <c r="F55" s="22" t="s">
         <v>134</v>
       </c>
     </row>
@@ -3558,7 +3636,7 @@
       <c r="E56" s="1">
         <v>2</v>
       </c>
-      <c r="F56" s="21" t="s">
+      <c r="F56" s="22" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3572,7 +3650,7 @@
       <c r="E57" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="21" t="s">
+      <c r="F57" s="22" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3586,7 +3664,7 @@
       <c r="E58" s="1">
         <v>2</v>
       </c>
-      <c r="F58" s="21" t="s">
+      <c r="F58" s="22" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3600,7 +3678,7 @@
       <c r="E59" s="1">
         <v>2</v>
       </c>
-      <c r="F59" s="21" t="s">
+      <c r="F59" s="22" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3683,7 +3761,7 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="21" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3697,7 +3775,7 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="21" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3711,7 +3789,7 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="21" t="s">
         <v>148</v>
       </c>
     </row>
@@ -3725,7 +3803,7 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="21" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3739,7 +3817,7 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="21" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3753,7 +3831,7 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="21" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3767,7 +3845,7 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="21" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3787,7 +3865,7 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="21" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3795,19 +3873,19 @@
       <c r="C14" s="1">
         <v>21009</v>
       </c>
-      <c r="F14" s="15"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C15" s="1">
         <v>21010</v>
       </c>
-      <c r="F15" s="15"/>
+      <c r="F15" s="16"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="C16" s="1">
         <v>21011</v>
       </c>
-      <c r="F16" s="15"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C17" s="1">
@@ -3816,73 +3894,73 @@
       <c r="F17" s="2"/>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F18" s="15"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F19" s="15"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F20" s="15"/>
+      <c r="F20" s="16"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F21" s="15"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F22" s="15"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F23" s="2"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F24" s="15"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F25" s="15"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F26" s="15"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F27" s="15"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F28" s="15"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F29" s="2"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F30" s="15"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F31" s="15"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F32" s="15"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F33" s="15"/>
+      <c r="F33" s="16"/>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F34" s="15"/>
+      <c r="F34" s="16"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="6:6">
       <c r="F35" s="2"/>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F36" s="15"/>
+      <c r="F36" s="16"/>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F37" s="15"/>
+      <c r="F37" s="16"/>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F38" s="15"/>
+      <c r="F38" s="16"/>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F39" s="15"/>
+      <c r="F39" s="16"/>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F40" s="15"/>
+      <c r="F40" s="16"/>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="6:6">
       <c r="F41" s="2"/>
@@ -3962,1010 +4040,1010 @@
       </c>
     </row>
     <row r="6" s="6" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="10">
+      <c r="C6" s="11">
         <v>180001</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="12" t="s">
         <v>159</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="20" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="10">
+      <c r="C7" s="11">
         <v>180002</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>161</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="20" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="10">
+      <c r="C8" s="11">
         <v>180003</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="12" t="s">
         <v>163</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="20" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="10">
+      <c r="C9" s="11">
         <v>180004</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="12" t="s">
         <v>165</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="20" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <v>180005</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="12" t="s">
         <v>167</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="20" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
-      <c r="C11" s="10">
+      <c r="C11" s="11">
         <v>180006</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="13" t="s">
         <v>169</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
-      <c r="C12" s="10">
+      <c r="C12" s="11">
         <v>180007</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="12" t="s">
         <v>171</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="20" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
-      <c r="C13" s="10">
+      <c r="C13" s="11">
         <v>180008</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>173</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="20" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
-      <c r="C14" s="10">
+      <c r="C14" s="11">
         <v>180009</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>175</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="20" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
-      <c r="C15" s="10">
+      <c r="C15" s="11">
         <v>180010</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>177</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="20" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
-      <c r="C16" s="10">
+      <c r="C16" s="11">
         <v>180011</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="12" t="s">
         <v>179</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="10">
+      <c r="C17" s="11">
         <v>180012</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="13" t="s">
         <v>181</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="20" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="10">
+      <c r="C18" s="11">
         <v>180013</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="14" t="s">
         <v>183</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="20" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="10">
+      <c r="C19" s="11">
         <v>180014</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="12" t="s">
         <v>185</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="20" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="10">
+      <c r="C20" s="11">
         <v>180015</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="12" t="s">
         <v>187</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="20" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
-      <c r="C21" s="10">
+      <c r="C21" s="11">
         <v>180016</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="12" t="s">
         <v>189</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="20" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
-      <c r="C22" s="10">
+      <c r="C22" s="11">
         <v>180017</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="12" t="s">
         <v>191</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="20" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
-      <c r="C23" s="10">
+      <c r="C23" s="11">
         <v>180018</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="13" t="s">
         <v>193</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="20" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
-      <c r="C24" s="10">
+      <c r="C24" s="11">
         <v>180019</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="12" t="s">
         <v>195</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="20" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
-      <c r="C25" s="10">
+      <c r="C25" s="11">
         <v>180020</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="12" t="s">
         <v>197</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="20" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
-      <c r="C26" s="10">
+      <c r="C26" s="11">
         <v>180021</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="12" t="s">
         <v>199</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
-      <c r="F26" s="19" t="s">
+      <c r="F26" s="20" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
-      <c r="C27" s="10">
+      <c r="C27" s="11">
         <v>180022</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="12" t="s">
         <v>201</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="20" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
-      <c r="C28" s="10">
+      <c r="C28" s="11">
         <v>180023</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="14" t="s">
         <v>203</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
-      <c r="F28" s="19" t="s">
+      <c r="F28" s="20" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
-      <c r="C29" s="10">
+      <c r="C29" s="11">
         <v>180024</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>205</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
-      <c r="F29" s="19" t="s">
+      <c r="F29" s="20" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
-      <c r="C30" s="10">
+      <c r="C30" s="11">
         <v>180025</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="12" t="s">
         <v>207</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="20" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
-      <c r="C31" s="10">
+      <c r="C31" s="11">
         <v>180026</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="12" t="s">
         <v>209</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="20" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
-      <c r="C32" s="10">
+      <c r="C32" s="11">
         <v>180027</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="15" t="s">
         <v>211</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="20" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
-      <c r="C33" s="10">
+      <c r="C33" s="11">
         <v>180028</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="12" t="s">
         <v>213</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="F33" s="20" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
-      <c r="C34" s="10">
+      <c r="C34" s="11">
         <v>180029</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="15" t="s">
         <v>215</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="F34" s="20" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
-      <c r="C35" s="10">
+      <c r="C35" s="11">
         <v>180030</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="13" t="s">
         <v>217</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
-      <c r="F35" s="19" t="s">
+      <c r="F35" s="20" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
-      <c r="C36" s="10">
+      <c r="C36" s="11">
         <v>180031</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="12" t="s">
         <v>219</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
-      <c r="F36" s="19" t="s">
+      <c r="F36" s="20" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
-      <c r="C37" s="10">
+      <c r="C37" s="11">
         <v>180032</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="12" t="s">
         <v>221</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="20" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
-      <c r="C38" s="10">
+      <c r="C38" s="11">
         <v>180033</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="12" t="s">
         <v>223</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="20" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
-      <c r="C39" s="10">
+      <c r="C39" s="11">
         <v>180034</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="12" t="s">
         <v>225</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="20" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
-      <c r="C40" s="10">
+      <c r="C40" s="11">
         <v>180035</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="12" t="s">
         <v>227</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="F40" s="20" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
-      <c r="C41" s="10">
+      <c r="C41" s="11">
         <v>180036</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="13" t="s">
         <v>229</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
-      <c r="F41" s="19" t="s">
+      <c r="F41" s="20" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
-      <c r="C42" s="10">
+      <c r="C42" s="11">
         <v>180037</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="14" t="s">
         <v>231</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
-      <c r="F42" s="19" t="s">
+      <c r="F42" s="20" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
-      <c r="C43" s="10">
+      <c r="C43" s="11">
         <v>180038</v>
       </c>
-      <c r="D43" s="11" t="s">
+      <c r="D43" s="12" t="s">
         <v>233</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
-      <c r="F43" s="19" t="s">
+      <c r="F43" s="20" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
-      <c r="C44" s="10">
+      <c r="C44" s="11">
         <v>180039</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="14" t="s">
         <v>235</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
-      <c r="F44" s="19" t="s">
+      <c r="F44" s="20" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
-      <c r="C45" s="10">
+      <c r="C45" s="11">
         <v>180040</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" s="12" t="s">
         <v>237</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
-      <c r="F45" s="19" t="s">
+      <c r="F45" s="20" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
-      <c r="C46" s="10">
+      <c r="C46" s="11">
         <v>180041</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="15" t="s">
         <v>239</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
-      <c r="F46" s="19" t="s">
+      <c r="F46" s="20" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
-      <c r="C47" s="10">
+      <c r="C47" s="11">
         <v>180042</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="14" t="s">
         <v>241</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
-      <c r="F47" s="19" t="s">
+      <c r="F47" s="20" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
-      <c r="C48" s="10">
+      <c r="C48" s="11">
         <v>180043</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="12" t="s">
         <v>243</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="F48" s="20" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
-      <c r="C49" s="10">
+      <c r="C49" s="11">
         <v>180044</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="12" t="s">
         <v>245</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="F49" s="20" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
-      <c r="C50" s="10">
+      <c r="C50" s="11">
         <v>180045</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="12" t="s">
         <v>247</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
-      <c r="F50" s="19" t="s">
+      <c r="F50" s="20" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
-      <c r="C51" s="10">
+      <c r="C51" s="11">
         <v>180046</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="15" t="s">
         <v>249</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="F51" s="20" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
-      <c r="C52" s="10">
+      <c r="C52" s="11">
         <v>180047</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="12" t="s">
         <v>251</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
-      <c r="F52" s="19" t="s">
+      <c r="F52" s="20" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
-      <c r="C53" s="10">
+      <c r="C53" s="11">
         <v>180048</v>
       </c>
-      <c r="D53" s="12" t="s">
+      <c r="D53" s="13" t="s">
         <v>245</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
-      <c r="F53" s="19" t="s">
+      <c r="F53" s="20" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
-      <c r="C54" s="10">
+      <c r="C54" s="11">
         <v>180049</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="12" t="s">
         <v>254</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
-      <c r="F54" s="19" t="s">
+      <c r="F54" s="20" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
-      <c r="C55" s="10">
+      <c r="C55" s="11">
         <v>180050</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="12" t="s">
         <v>256</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
-      <c r="F55" s="19" t="s">
+      <c r="F55" s="20" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
-      <c r="C56" s="10">
+      <c r="C56" s="11">
         <v>180051</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="12" t="s">
         <v>258</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
-      <c r="F56" s="19" t="s">
+      <c r="F56" s="20" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
-      <c r="C57" s="10">
+      <c r="C57" s="11">
         <v>180052</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="12" t="s">
         <v>260</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
-      <c r="F57" s="19" t="s">
+      <c r="F57" s="20" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
-      <c r="C58" s="10">
+      <c r="C58" s="11">
         <v>180053</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D58" s="12" t="s">
         <v>262</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
-      <c r="F58" s="19" t="s">
+      <c r="F58" s="20" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
-      <c r="C59" s="10">
+      <c r="C59" s="11">
         <v>180054</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D59" s="13" t="s">
         <v>264</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
-      <c r="F59" s="19" t="s">
+      <c r="F59" s="20" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
-      <c r="C60" s="10">
+      <c r="C60" s="11">
         <v>180055</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D60" s="12" t="s">
         <v>266</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
-      <c r="F60" s="19" t="s">
+      <c r="F60" s="20" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
-      <c r="C61" s="10">
+      <c r="C61" s="11">
         <v>180056</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D61" s="12" t="s">
         <v>268</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
-      <c r="F61" s="19" t="s">
+      <c r="F61" s="20" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
-      <c r="C62" s="10">
+      <c r="C62" s="11">
         <v>180057</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="12" t="s">
         <v>225</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
-      <c r="F62" s="19" t="s">
+      <c r="F62" s="20" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
-      <c r="C63" s="10">
+      <c r="C63" s="11">
         <v>180058</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="14" t="s">
         <v>271</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
-      <c r="F63" s="19" t="s">
+      <c r="F63" s="20" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
-      <c r="C64" s="10">
+      <c r="C64" s="11">
         <v>180059</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="12" t="s">
         <v>273</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
-      <c r="F64" s="19" t="s">
+      <c r="F64" s="20" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
-      <c r="C65" s="10">
+      <c r="C65" s="11">
         <v>180060</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="13" t="s">
         <v>275</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
-      <c r="F65" s="19" t="s">
+      <c r="F65" s="20" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
-      <c r="C66" s="10">
+      <c r="C66" s="11">
         <v>180061</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="12" t="s">
         <v>277</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
-      <c r="F66" s="19" t="s">
+      <c r="F66" s="20" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
-      <c r="C67" s="10">
+      <c r="C67" s="11">
         <v>180062</v>
       </c>
-      <c r="D67" s="14" t="s">
+      <c r="D67" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
-      <c r="F67" s="19" t="s">
+      <c r="F67" s="20" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
-      <c r="C68" s="10">
+      <c r="C68" s="11">
         <v>180063</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="12" t="s">
         <v>281</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
-      <c r="F68" s="19" t="s">
+      <c r="F68" s="20" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
-      <c r="C69" s="10">
+      <c r="C69" s="11">
         <v>180064</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="12" t="s">
         <v>283</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
-      <c r="F69" s="19" t="s">
+      <c r="F69" s="20" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
-      <c r="C70" s="10">
+      <c r="C70" s="11">
         <v>180065</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="12" t="s">
         <v>285</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
-      <c r="F70" s="19" t="s">
+      <c r="F70" s="20" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
-      <c r="C71" s="10">
+      <c r="C71" s="11">
         <v>180066</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="13" t="s">
         <v>287</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
-      <c r="F71" s="19" t="s">
+      <c r="F71" s="20" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
-      <c r="C72" s="10">
+      <c r="C72" s="11">
         <v>180067</v>
       </c>
-      <c r="D72" s="11" t="s">
+      <c r="D72" s="12" t="s">
         <v>283</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
-      <c r="F72" s="19" t="s">
+      <c r="F72" s="20" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
-      <c r="C73" s="10">
+      <c r="C73" s="11">
         <v>180068</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="12" t="s">
         <v>290</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
-      <c r="F73" s="19" t="s">
+      <c r="F73" s="20" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
-      <c r="C74" s="10">
+      <c r="C74" s="11">
         <v>180069</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="D74" s="12" t="s">
         <v>292</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
-      <c r="F74" s="19" t="s">
+      <c r="F74" s="20" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
-      <c r="C75" s="10">
+      <c r="C75" s="11">
         <v>180070</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="12" t="s">
         <v>294</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
-      <c r="F75" s="19" t="s">
+      <c r="F75" s="20" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
-      <c r="C76" s="10">
+      <c r="C76" s="11">
         <v>180071</v>
       </c>
-      <c r="D76" s="13" t="s">
+      <c r="D76" s="14" t="s">
         <v>296</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
-      <c r="F76" s="19" t="s">
+      <c r="F76" s="20" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
-      <c r="C77" s="10">
+      <c r="C77" s="11">
         <v>180072</v>
       </c>
-      <c r="D77" s="12" t="s">
+      <c r="D77" s="13" t="s">
         <v>298</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
-      <c r="F77" s="19" t="s">
+      <c r="F77" s="20" t="s">
         <v>299</v>
       </c>
     </row>
@@ -5058,7 +5136,7 @@
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
-      <c r="C22" s="10"/>
+      <c r="C22" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5145,7 +5223,7 @@
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>303</v>
       </c>
     </row>
@@ -5159,7 +5237,7 @@
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>305</v>
       </c>
     </row>
@@ -5173,7 +5251,7 @@
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="19" t="s">
         <v>307</v>
       </c>
     </row>
@@ -5187,7 +5265,7 @@
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>309</v>
       </c>
     </row>
@@ -5201,7 +5279,7 @@
       <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="19" t="s">
         <v>311</v>
       </c>
     </row>
@@ -5215,7 +5293,7 @@
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="19" t="s">
         <v>313</v>
       </c>
     </row>
@@ -5229,7 +5307,7 @@
       <c r="E12" s="1">
         <v>4</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="19" t="s">
         <v>315</v>
       </c>
     </row>
@@ -5243,7 +5321,7 @@
       <c r="E13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="23" t="s">
         <v>317</v>
       </c>
     </row>
@@ -5257,36 +5335,36 @@
       <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="23" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F24" s="8"/>
+      <c r="F24" s="9"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F25" s="8"/>
+      <c r="F25" s="9"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F26" s="8"/>
+      <c r="F26" s="9"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F27" s="8"/>
+      <c r="F27" s="9"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F28" s="8"/>
+      <c r="F28" s="9"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F29" s="8"/>
+      <c r="F29" s="9"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F30" s="8"/>
+      <c r="F30" s="9"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F31" s="8"/>
+      <c r="F31" s="9"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="6:6">
-      <c r="F32" s="8"/>
+      <c r="F32" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5303,7 +5381,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F32"/>
+  <dimension ref="C1:F35"/>
   <sheetFormatPr defaultColWidth="12.25" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.25" style="1" customWidth="1"/>
@@ -5373,7 +5451,7 @@
       <c r="E6" s="1">
         <v>6</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="20" t="s">
         <v>321</v>
       </c>
     </row>
@@ -5387,7 +5465,7 @@
       <c r="E7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="20" t="s">
         <v>323</v>
       </c>
     </row>
@@ -5401,7 +5479,7 @@
       <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="20" t="s">
         <v>325</v>
       </c>
     </row>
@@ -5415,7 +5493,7 @@
       <c r="E9" s="1">
         <v>6</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="20" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5429,7 +5507,7 @@
       <c r="E10" s="1">
         <v>6</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="20" t="s">
         <v>329</v>
       </c>
     </row>
@@ -5443,7 +5521,7 @@
       <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>331</v>
       </c>
     </row>
@@ -5457,7 +5535,7 @@
       <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="20" t="s">
         <v>333</v>
       </c>
     </row>
@@ -5471,7 +5549,7 @@
       <c r="E13" s="1">
         <v>6</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="20" t="s">
         <v>335</v>
       </c>
     </row>
@@ -5485,7 +5563,7 @@
       <c r="E14" s="1">
         <v>6</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="20" t="s">
         <v>337</v>
       </c>
     </row>
@@ -5499,7 +5577,7 @@
       <c r="E15" s="1">
         <v>6</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="20" t="s">
         <v>339</v>
       </c>
     </row>
@@ -5513,7 +5591,7 @@
       <c r="E16" s="1">
         <v>6</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20" t="s">
         <v>341</v>
       </c>
     </row>
@@ -5527,7 +5605,7 @@
       <c r="E17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="20" t="s">
         <v>343</v>
       </c>
     </row>
@@ -5541,7 +5619,7 @@
       <c r="E18" s="1">
         <v>6</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="20" t="s">
         <v>345</v>
       </c>
     </row>
@@ -5555,7 +5633,7 @@
       <c r="E19" s="1">
         <v>6</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="20" t="s">
         <v>347</v>
       </c>
     </row>
@@ -5569,7 +5647,7 @@
       <c r="E20" s="1">
         <v>6</v>
       </c>
-      <c r="F20" s="19" t="s">
+      <c r="F20" s="20" t="s">
         <v>349</v>
       </c>
     </row>
@@ -5583,7 +5661,7 @@
       <c r="E21" s="1">
         <v>6</v>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="20" t="s">
         <v>351</v>
       </c>
     </row>
@@ -5597,7 +5675,7 @@
       <c r="E22" s="1">
         <v>6</v>
       </c>
-      <c r="F22" s="19" t="s">
+      <c r="F22" s="20" t="s">
         <v>353</v>
       </c>
     </row>
@@ -5611,7 +5689,7 @@
       <c r="E23" s="1">
         <v>6</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="20" t="s">
         <v>355</v>
       </c>
     </row>
@@ -5625,7 +5703,7 @@
       <c r="E24" s="1">
         <v>6</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="F24" s="20" t="s">
         <v>357</v>
       </c>
     </row>
@@ -5639,7 +5717,7 @@
       <c r="E25" s="1">
         <v>6</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="20" t="s">
         <v>359</v>
       </c>
     </row>
@@ -5653,27 +5731,135 @@
       <c r="E26" s="1">
         <v>6</v>
       </c>
-      <c r="F26" s="19" t="s">
+      <c r="F26" s="20" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F27" s="8"/>
+      <c r="C27" s="5">
+        <v>50022</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E27" s="1">
+        <v>6</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F28" s="8"/>
+      <c r="C28" s="5">
+        <v>50023</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="E28" s="1">
+        <v>6</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>365</v>
+      </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F29" s="8"/>
+      <c r="C29" s="5">
+        <v>50024</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E29" s="1">
+        <v>6</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F30" s="8"/>
+      <c r="C30" s="5">
+        <v>50025</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="E30" s="1">
+        <v>6</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>369</v>
+      </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F31" s="8"/>
+      <c r="C31" s="5">
+        <v>50026</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="E31" s="1">
+        <v>6</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>371</v>
+      </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F32" s="8"/>
+      <c r="C32" s="5">
+        <v>50027</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="E32" s="1">
+        <v>6</v>
+      </c>
+      <c r="F32" s="20" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:6">
+      <c r="C33" s="5">
+        <v>50028</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E33" s="1">
+        <v>6</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:6">
+      <c r="C34" s="5">
+        <v>50029</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="E34" s="1">
+        <v>6</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:6">
+      <c r="C35" s="5">
+        <v>50030</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="E35" s="1">
+        <v>6</v>
+      </c>
+      <c r="F35" s="20" t="s">
+        <v>379</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480" activeTab="6"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="416">
   <si>
     <t>_id</t>
   </si>
@@ -855,6 +855,114 @@
   </si>
   <si>
     <t>210081,220081,230081</t>
+  </si>
+  <si>
+    <t>90级链头</t>
+  </si>
+  <si>
+    <t>210093,220093,230093,210094,220094,230094</t>
+  </si>
+  <si>
+    <t>90级手镯</t>
+  </si>
+  <si>
+    <t>210095,220095,230095</t>
+  </si>
+  <si>
+    <t>90级戒指</t>
+  </si>
+  <si>
+    <t>210096,220096,230096</t>
+  </si>
+  <si>
+    <t>90级腰鞋</t>
+  </si>
+  <si>
+    <t>210097,220097,230097,210098,220098,230098</t>
+  </si>
+  <si>
+    <t>90级衣服</t>
+  </si>
+  <si>
+    <t>210092,220092,230092</t>
+  </si>
+  <si>
+    <t>90级武器</t>
+  </si>
+  <si>
+    <t>210091,220091,230091</t>
+  </si>
+  <si>
+    <t>100级链头</t>
+  </si>
+  <si>
+    <t>2100103,2200103,2300103,2100104,2200104,2300104</t>
+  </si>
+  <si>
+    <t>100级手镯</t>
+  </si>
+  <si>
+    <t>2100105,2200105,2300105</t>
+  </si>
+  <si>
+    <t>100级戒指</t>
+  </si>
+  <si>
+    <t>2100106,2200106,2300106</t>
+  </si>
+  <si>
+    <t>100级腰鞋</t>
+  </si>
+  <si>
+    <t>2100107,2200107,2300107,2100108,2200108,2300108</t>
+  </si>
+  <si>
+    <t>100级衣服</t>
+  </si>
+  <si>
+    <t>2100102,2200102,2300102</t>
+  </si>
+  <si>
+    <t>100级武器</t>
+  </si>
+  <si>
+    <t>2100101,2200101,2300101</t>
+  </si>
+  <si>
+    <t>110级链头</t>
+  </si>
+  <si>
+    <t>2100113,2200113,2300113,2100114,2200114,2300114</t>
+  </si>
+  <si>
+    <t>110级手镯</t>
+  </si>
+  <si>
+    <t>2100115,2200115,2300115</t>
+  </si>
+  <si>
+    <t>110级戒指</t>
+  </si>
+  <si>
+    <t>2100116,2200116,2300116</t>
+  </si>
+  <si>
+    <t>110级腰鞋</t>
+  </si>
+  <si>
+    <t>2100117,2200117,2300117,2100118,2200118,2300118</t>
+  </si>
+  <si>
+    <t>110级衣服</t>
+  </si>
+  <si>
+    <t>2100112,2200112,2300112</t>
+  </si>
+  <si>
+    <t>110级武器</t>
+  </si>
+  <si>
+    <t>2100111,2200111,2300111</t>
   </si>
   <si>
     <t>治愈</t>
@@ -1785,12 +1893,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2873,7 +2981,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F59"/>
+  <dimension ref="C3:F77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -3680,6 +3788,258 @@
       </c>
       <c r="F59" s="22" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:6">
+      <c r="C60" s="1">
+        <v>20055</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E60" s="1">
+        <v>2</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:6">
+      <c r="C61" s="1">
+        <v>20056</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E61" s="1">
+        <v>2</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:6">
+      <c r="C62" s="1">
+        <v>20057</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E62" s="1">
+        <v>2</v>
+      </c>
+      <c r="F62" s="22" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:6">
+      <c r="C63" s="1">
+        <v>20058</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E63" s="1">
+        <v>2</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:6">
+      <c r="C64" s="1">
+        <v>20059</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E64" s="1">
+        <v>2</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:6">
+      <c r="C65" s="1">
+        <v>20060</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E65" s="1">
+        <v>2</v>
+      </c>
+      <c r="F65" s="22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:6">
+      <c r="C66" s="1">
+        <v>20061</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E66" s="1">
+        <v>2</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:6">
+      <c r="C67" s="1">
+        <v>20062</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E67" s="1">
+        <v>2</v>
+      </c>
+      <c r="F67" s="22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:6">
+      <c r="C68" s="1">
+        <v>20063</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E68" s="1">
+        <v>2</v>
+      </c>
+      <c r="F68" s="22" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="3:6">
+      <c r="C69" s="1">
+        <v>20064</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E69" s="1">
+        <v>2</v>
+      </c>
+      <c r="F69" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="3:6">
+      <c r="C70" s="1">
+        <v>20065</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E70" s="1">
+        <v>2</v>
+      </c>
+      <c r="F70" s="22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:6">
+      <c r="C71" s="1">
+        <v>20066</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E71" s="1">
+        <v>2</v>
+      </c>
+      <c r="F71" s="22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:6">
+      <c r="C72" s="1">
+        <v>20067</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E72" s="1">
+        <v>2</v>
+      </c>
+      <c r="F72" s="22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:6">
+      <c r="C73" s="1">
+        <v>20068</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E73" s="1">
+        <v>2</v>
+      </c>
+      <c r="F73" s="22" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:6">
+      <c r="C74" s="1">
+        <v>20069</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E74" s="1">
+        <v>2</v>
+      </c>
+      <c r="F74" s="22" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:6">
+      <c r="C75" s="1">
+        <v>20070</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E75" s="1">
+        <v>2</v>
+      </c>
+      <c r="F75" s="22" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:6">
+      <c r="C76" s="1">
+        <v>20071</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E76" s="1">
+        <v>2</v>
+      </c>
+      <c r="F76" s="22" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:6">
+      <c r="C77" s="1">
+        <v>20072</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E77" s="1">
+        <v>2</v>
+      </c>
+      <c r="F77" s="22" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3756,13 +4116,13 @@
         <v>21001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>143</v>
+        <v>179</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>144</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3770,13 +4130,13 @@
         <v>21002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3784,13 +4144,13 @@
         <v>21003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>147</v>
+        <v>183</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3798,13 +4158,13 @@
         <v>21004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3812,13 +4172,13 @@
         <v>21005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3826,13 +4186,13 @@
         <v>21006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -3840,33 +4200,33 @@
         <v>21007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="C13" s="1">
         <v>21008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>158</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -4044,13 +4404,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -4058,13 +4418,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -4072,13 +4432,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -4086,13 +4446,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -4100,13 +4460,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>167</v>
+        <v>203</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>168</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -4114,13 +4474,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>170</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -4128,13 +4488,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>172</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -4142,13 +4502,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4156,13 +4516,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>175</v>
+        <v>211</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>176</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -4170,13 +4530,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>178</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -4184,13 +4544,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>179</v>
+        <v>215</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>180</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -4198,13 +4558,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>181</v>
+        <v>217</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>182</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -4212,13 +4572,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>184</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -4226,13 +4586,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>185</v>
+        <v>221</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>186</v>
+        <v>222</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -4240,13 +4600,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>188</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -4254,13 +4614,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>189</v>
+        <v>225</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>190</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -4268,13 +4628,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>191</v>
+        <v>227</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -4282,13 +4642,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -4296,13 +4656,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -4310,13 +4670,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -4324,13 +4684,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -4338,13 +4698,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -4352,13 +4712,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -4366,13 +4726,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -4380,13 +4740,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -4394,13 +4754,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -4408,13 +4768,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -4422,13 +4782,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -4436,13 +4796,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -4450,13 +4810,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -4464,13 +4824,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -4478,13 +4838,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -4492,13 +4852,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -4506,13 +4866,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -4520,13 +4880,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -4534,13 +4894,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -4548,13 +4908,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -4562,13 +4922,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -4576,13 +4936,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -4590,13 +4950,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -4604,13 +4964,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -4618,13 +4978,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>242</v>
+        <v>278</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -4632,13 +4992,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>243</v>
+        <v>279</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>244</v>
+        <v>280</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -4646,13 +5006,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>246</v>
+        <v>282</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -4660,13 +5020,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>247</v>
+        <v>283</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>248</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -4674,13 +5034,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>250</v>
+        <v>286</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -4688,13 +5048,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>251</v>
+        <v>287</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>252</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -4702,13 +5062,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>245</v>
+        <v>281</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -4716,13 +5076,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>254</v>
+        <v>290</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>255</v>
+        <v>291</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -4730,13 +5090,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -4744,13 +5104,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>258</v>
+        <v>294</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>259</v>
+        <v>295</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -4758,13 +5118,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>260</v>
+        <v>296</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>261</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -4772,13 +5132,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -4786,13 +5146,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>265</v>
+        <v>301</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -4800,13 +5160,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>267</v>
+        <v>303</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -4814,13 +5174,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -4828,13 +5188,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>270</v>
+        <v>306</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -4842,13 +5202,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>271</v>
+        <v>307</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>272</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -4856,13 +5216,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>273</v>
+        <v>309</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>274</v>
+        <v>310</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -4870,13 +5230,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>276</v>
+        <v>312</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -4884,13 +5244,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -4898,13 +5258,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -4912,13 +5272,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>282</v>
+        <v>318</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -4926,13 +5286,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>284</v>
+        <v>320</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -4940,13 +5300,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>286</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -4954,13 +5314,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>287</v>
+        <v>323</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -4968,13 +5328,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>283</v>
+        <v>319</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>289</v>
+        <v>325</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -4982,13 +5342,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>291</v>
+        <v>327</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -4996,13 +5356,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>292</v>
+        <v>328</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5010,13 +5370,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>295</v>
+        <v>331</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5024,13 +5384,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>297</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -5038,13 +5398,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>298</v>
+        <v>334</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>299</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -5126,13 +5486,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>300</v>
+        <v>336</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>301</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -5218,13 +5578,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>303</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5232,13 +5592,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>304</v>
+        <v>340</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>305</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5246,13 +5606,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>306</v>
+        <v>342</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>307</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5260,13 +5620,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>308</v>
+        <v>344</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>309</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5274,13 +5634,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>311</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5288,13 +5648,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>312</v>
+        <v>348</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>313</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5302,13 +5662,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>315</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5316,13 +5676,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>317</v>
+        <v>353</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5330,13 +5690,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -5446,13 +5806,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>320</v>
+        <v>356</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5460,13 +5820,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5474,13 +5834,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>325</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5488,13 +5848,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>326</v>
+        <v>362</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>327</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5502,13 +5862,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>329</v>
+        <v>365</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5516,13 +5876,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>331</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5530,13 +5890,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>332</v>
+        <v>368</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>333</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5544,13 +5904,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>334</v>
+        <v>370</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>335</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5558,13 +5918,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>336</v>
+        <v>372</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -5572,13 +5932,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>338</v>
+        <v>374</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>339</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -5586,13 +5946,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>341</v>
+        <v>377</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5600,13 +5960,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>343</v>
+        <v>379</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5614,13 +5974,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>344</v>
+        <v>380</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>345</v>
+        <v>381</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -5628,13 +5988,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>347</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -5642,13 +6002,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>349</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -5656,13 +6016,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>350</v>
+        <v>386</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>351</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -5670,13 +6030,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>352</v>
+        <v>388</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>353</v>
+        <v>389</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -5684,13 +6044,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>354</v>
+        <v>390</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>355</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5698,13 +6058,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>357</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5712,13 +6072,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5726,13 +6086,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5740,13 +6100,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>363</v>
+        <v>399</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5754,13 +6114,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>364</v>
+        <v>400</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>365</v>
+        <v>401</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5768,13 +6128,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>366</v>
+        <v>402</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>367</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5782,13 +6142,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>369</v>
+        <v>405</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5796,13 +6156,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5810,13 +6170,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>373</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -5824,13 +6184,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -5838,13 +6198,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -5852,13 +6212,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>379</v>
+        <v>415</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="417">
   <si>
     <t>_id</t>
   </si>
@@ -1001,16 +1001,19 @@
     <t>201016,201017,201018</t>
   </si>
   <si>
+    <t>致命</t>
+  </si>
+  <si>
+    <t>201019,201020,201021</t>
+  </si>
+  <si>
     <t>天命</t>
   </si>
   <si>
+    <t>201022,201023,201024</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>贪婪</t>
-  </si>
-  <si>
-    <t>201019,201020,201021</t>
   </si>
   <si>
     <t>狼宝宝</t>
@@ -1893,12 +1896,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4206,16 +4209,10 @@
         <v>2</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A13" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C13" s="1">
         <v>21008</v>
       </c>
@@ -4230,72 +4227,96 @@
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="C14" s="1">
         <v>21009</v>
       </c>
       <c r="F14" s="16"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="C15" s="1">
         <v>21010</v>
       </c>
       <c r="F15" s="16"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="C16" s="1">
         <v>21011</v>
       </c>
       <c r="F16" s="16"/>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="A17" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="C17" s="1">
         <v>21012</v>
       </c>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F18" s="16"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F19" s="16"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F20" s="16"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F21" s="16"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F22" s="16"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F23" s="2"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F24" s="16"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F25" s="16"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F26" s="16"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F27" s="16"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F28" s="16"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F30" s="16"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F31" s="16"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="F32" s="16"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -4404,13 +4425,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -4418,13 +4439,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -4432,13 +4453,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -4446,13 +4467,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -4460,13 +4481,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -4474,13 +4495,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -4488,13 +4509,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -4502,13 +4523,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4516,13 +4537,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -4530,13 +4551,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -4544,13 +4565,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -4558,13 +4579,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -4572,13 +4593,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -4586,13 +4607,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -4600,13 +4621,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -4614,13 +4635,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -4628,13 +4649,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -4642,13 +4663,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -4656,13 +4677,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -4670,13 +4691,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -4684,13 +4705,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -4698,13 +4719,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -4712,13 +4733,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -4726,13 +4747,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -4740,13 +4761,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -4754,13 +4775,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -4768,13 +4789,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -4782,13 +4803,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -4796,13 +4817,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -4810,13 +4831,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -4824,13 +4845,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -4838,13 +4859,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -4852,13 +4873,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -4866,13 +4887,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -4880,13 +4901,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -4894,13 +4915,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -4908,13 +4929,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -4922,13 +4943,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -4936,13 +4957,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -4950,13 +4971,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -4964,13 +4985,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -4978,13 +4999,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -4992,13 +5013,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5006,13 +5027,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5020,13 +5041,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5034,13 +5055,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5048,13 +5069,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5062,13 +5083,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5076,13 +5097,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5090,13 +5111,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5104,13 +5125,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="20" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5118,13 +5139,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="20" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5132,13 +5153,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5146,13 +5167,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5160,13 +5181,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="20" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5174,13 +5195,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5188,13 +5209,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5202,13 +5223,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5216,13 +5237,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="20" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5230,13 +5251,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5244,13 +5265,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="20" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5258,13 +5279,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5272,13 +5293,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="20" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5286,13 +5307,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="20" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5300,13 +5321,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5314,13 +5335,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="20" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5328,13 +5349,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="20" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5342,13 +5363,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="20" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5356,13 +5377,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="20" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5370,13 +5391,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="20" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5384,13 +5405,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="20" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -5398,13 +5419,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -5486,13 +5507,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -5578,13 +5599,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5592,13 +5613,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5606,13 +5627,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5620,13 +5641,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5634,13 +5655,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5648,13 +5669,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5662,13 +5683,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5676,13 +5697,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5690,13 +5711,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -5806,13 +5827,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5820,13 +5841,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5834,13 +5855,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5848,13 +5869,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5862,13 +5883,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5876,13 +5897,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5890,13 +5911,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5904,13 +5925,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5918,13 +5939,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -5932,13 +5953,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -5946,13 +5967,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5960,13 +5981,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5974,13 +5995,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -5988,13 +6009,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
       <c r="F19" s="20" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6002,13 +6023,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6016,13 +6037,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
       <c r="F21" s="20" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6030,13 +6051,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6044,13 +6065,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="20" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6058,13 +6079,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6072,13 +6093,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6086,13 +6107,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6100,13 +6121,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6114,13 +6135,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6128,13 +6149,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6142,13 +6163,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6156,13 +6177,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6170,13 +6191,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6184,13 +6205,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6198,13 +6219,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6212,13 +6233,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="433">
   <si>
     <t>_id</t>
   </si>
@@ -531,6 +531,54 @@
   </si>
   <si>
     <t>5019</t>
+  </si>
+  <si>
+    <t>魂环1</t>
+  </si>
+  <si>
+    <t>8001</t>
+  </si>
+  <si>
+    <t>魂环2</t>
+  </si>
+  <si>
+    <t>8002</t>
+  </si>
+  <si>
+    <t>魂环3</t>
+  </si>
+  <si>
+    <t>8003</t>
+  </si>
+  <si>
+    <t>魂环4</t>
+  </si>
+  <si>
+    <t>8004</t>
+  </si>
+  <si>
+    <t>魂环5</t>
+  </si>
+  <si>
+    <t>8005</t>
+  </si>
+  <si>
+    <t>魂环6</t>
+  </si>
+  <si>
+    <t>8006</t>
+  </si>
+  <si>
+    <t>魂环7</t>
+  </si>
+  <si>
+    <t>8007</t>
+  </si>
+  <si>
+    <t>魂环8</t>
+  </si>
+  <si>
+    <t>8008</t>
   </si>
   <si>
     <t>1级链头</t>
@@ -1706,7 +1754,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1748,6 +1796,25 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -2231,137 +2298,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2401,20 +2468,36 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
@@ -2739,235 +2822,347 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="C1:F33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9" style="9"/>
-    <col min="3" max="3" width="8.75" style="9" customWidth="1"/>
-    <col min="4" max="4" width="15" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="9" customWidth="1"/>
-    <col min="6" max="6" width="30.75" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="9"/>
+    <col min="1" max="2" width="9" style="17"/>
+    <col min="3" max="3" width="8.75" style="17" customWidth="1"/>
+    <col min="4" max="4" width="15" style="17" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="17" customWidth="1"/>
+    <col min="6" max="6" width="30.75" style="18" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" s="9" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" s="9" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C3" s="17" t="s">
+    <row r="1" s="17" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F1" s="18"/>
+    </row>
+    <row r="2" s="17" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F2" s="18"/>
+    </row>
+    <row r="3" s="17" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="9" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C4" s="17" t="s">
+    <row r="4" s="17" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="9" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C5" s="17" t="s">
+    <row r="5" s="17" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="20" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="9" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="9">
+    <row r="6" s="17" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="17">
         <v>1</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="17">
         <v>5</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="9">
-        <v>2</v>
-      </c>
-      <c r="D7" s="9" t="s">
+      <c r="C7" s="17">
+        <v>2</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="17">
         <v>5</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="24" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="9">
+      <c r="C8" s="17">
         <v>3</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="17">
         <v>5</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="9">
+      <c r="C9" s="17">
         <v>4</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="17">
         <v>5</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="24" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
-      <c r="C10" s="9">
+      <c r="C10" s="17">
         <v>5</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="17">
         <v>6</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="25" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
-      <c r="C11" s="9">
+      <c r="C11" s="17">
         <v>6</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="17">
         <v>6</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="25" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
-      <c r="C12" s="9">
+      <c r="C12" s="17">
         <v>7</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="17">
         <v>6</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="25" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
-      <c r="C16" s="9">
+      <c r="C16" s="17">
         <v>11</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="17">
         <v>5</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="18" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="9">
+      <c r="C17" s="17">
         <v>12</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="17">
         <v>5</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="9">
+      <c r="C18" s="17">
         <v>13</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="17">
         <v>5</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="18" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="9">
+      <c r="C19" s="17">
         <v>14</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="17">
         <v>5</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="9">
+      <c r="C20" s="17">
         <v>15</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="17">
         <v>5</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" s="9" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C22" s="18"/>
+    <row r="22" s="17" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C22" s="22"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:6">
+      <c r="C26" s="17">
+        <v>21</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="17">
+        <v>5</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:6">
+      <c r="C27" s="17">
+        <v>22</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="17">
+        <v>5</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:6">
+      <c r="C28" s="17">
+        <v>23</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="17">
+        <v>5</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:6">
+      <c r="C29" s="17">
+        <v>24</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="17">
+        <v>5</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:6">
+      <c r="C30" s="17">
+        <v>25</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="17">
+        <v>5</v>
+      </c>
+      <c r="F30" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:6">
+      <c r="C31" s="17">
+        <v>26</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="17">
+        <v>5</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:6">
+      <c r="C32" s="17">
+        <v>27</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="17">
+        <v>5</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:6">
+      <c r="C33" s="17">
+        <v>28</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="17">
+        <v>5</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3042,13 +3237,13 @@
         <v>20001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>36</v>
+      <c r="F6" s="27" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -3056,13 +3251,13 @@
         <v>20002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>38</v>
+      <c r="F7" s="27" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -3070,13 +3265,13 @@
         <v>20003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="21" t="s">
-        <v>40</v>
+      <c r="F8" s="27" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -3084,13 +3279,13 @@
         <v>20004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>42</v>
+      <c r="F9" s="27" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -3098,13 +3293,13 @@
         <v>20005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="21" t="s">
-        <v>44</v>
+      <c r="F10" s="27" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -3112,13 +3307,13 @@
         <v>20006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="22" t="s">
-        <v>46</v>
+      <c r="F11" s="28" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -3126,13 +3321,13 @@
         <v>20007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>48</v>
+      <c r="F12" s="27" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -3140,13 +3335,13 @@
         <v>20008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>50</v>
+      <c r="F13" s="27" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -3154,13 +3349,13 @@
         <v>20009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>52</v>
+      <c r="F14" s="27" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -3168,13 +3363,13 @@
         <v>20010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="21" t="s">
-        <v>54</v>
+      <c r="F15" s="27" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -3182,13 +3377,13 @@
         <v>20011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="21" t="s">
-        <v>56</v>
+      <c r="F16" s="27" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -3196,13 +3391,13 @@
         <v>20012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="22" t="s">
-        <v>58</v>
+      <c r="F17" s="28" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -3210,13 +3405,13 @@
         <v>20013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>60</v>
+      <c r="F18" s="27" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -3224,13 +3419,13 @@
         <v>20014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>62</v>
+      <c r="F19" s="27" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -3238,13 +3433,13 @@
         <v>20015</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="21" t="s">
-        <v>64</v>
+      <c r="F20" s="27" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -3252,13 +3447,13 @@
         <v>20016</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>66</v>
+      <c r="F21" s="27" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -3266,13 +3461,13 @@
         <v>20017</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="21" t="s">
-        <v>68</v>
+      <c r="F22" s="27" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -3280,13 +3475,13 @@
         <v>20018</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="22" t="s">
-        <v>70</v>
+      <c r="F23" s="28" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -3294,13 +3489,13 @@
         <v>20019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="21" t="s">
-        <v>72</v>
+      <c r="F24" s="27" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -3308,13 +3503,13 @@
         <v>20020</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="21" t="s">
-        <v>74</v>
+      <c r="F25" s="27" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -3322,13 +3517,13 @@
         <v>20021</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="21" t="s">
-        <v>76</v>
+      <c r="F26" s="27" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -3336,13 +3531,13 @@
         <v>20022</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="21" t="s">
-        <v>78</v>
+      <c r="F27" s="27" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -3350,13 +3545,13 @@
         <v>20023</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="21" t="s">
-        <v>80</v>
+      <c r="F28" s="27" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -3364,13 +3559,13 @@
         <v>20024</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="22" t="s">
-        <v>82</v>
+      <c r="F29" s="28" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -3378,13 +3573,13 @@
         <v>20025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>84</v>
+      <c r="F30" s="27" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -3392,13 +3587,13 @@
         <v>20026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="21" t="s">
-        <v>86</v>
+      <c r="F31" s="27" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -3406,13 +3601,13 @@
         <v>20027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="21" t="s">
-        <v>88</v>
+      <c r="F32" s="27" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -3420,13 +3615,13 @@
         <v>20028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="21" t="s">
-        <v>90</v>
+      <c r="F33" s="27" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -3434,13 +3629,13 @@
         <v>20029</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="21" t="s">
-        <v>92</v>
+      <c r="F34" s="27" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -3448,13 +3643,13 @@
         <v>20030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="22" t="s">
-        <v>94</v>
+      <c r="F35" s="28" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -3462,13 +3657,13 @@
         <v>20031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="21" t="s">
-        <v>96</v>
+      <c r="F36" s="27" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -3476,13 +3671,13 @@
         <v>20032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="21" t="s">
-        <v>98</v>
+      <c r="F37" s="27" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -3490,13 +3685,13 @@
         <v>20033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="21" t="s">
-        <v>100</v>
+      <c r="F38" s="27" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -3504,13 +3699,13 @@
         <v>20034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="21" t="s">
-        <v>102</v>
+      <c r="F39" s="27" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -3518,13 +3713,13 @@
         <v>20035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="21" t="s">
-        <v>104</v>
+      <c r="F40" s="27" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -3532,13 +3727,13 @@
         <v>20036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="22" t="s">
-        <v>106</v>
+      <c r="F41" s="28" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -3546,13 +3741,13 @@
         <v>20037</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="21" t="s">
-        <v>108</v>
+      <c r="F42" s="27" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -3560,13 +3755,13 @@
         <v>20038</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
-      <c r="F43" s="21" t="s">
-        <v>110</v>
+      <c r="F43" s="27" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -3574,13 +3769,13 @@
         <v>20039</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="F44" s="21" t="s">
-        <v>112</v>
+      <c r="F44" s="27" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -3588,13 +3783,13 @@
         <v>20040</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="F45" s="21" t="s">
-        <v>114</v>
+      <c r="F45" s="27" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -3602,13 +3797,13 @@
         <v>20041</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
-      <c r="F46" s="21" t="s">
-        <v>116</v>
+      <c r="F46" s="27" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -3616,13 +3811,13 @@
         <v>20042</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="22" t="s">
-        <v>118</v>
+      <c r="F47" s="28" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -3630,13 +3825,13 @@
         <v>20043</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="F48" s="22" t="s">
-        <v>120</v>
+      <c r="F48" s="28" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -3644,13 +3839,13 @@
         <v>20044</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
-      <c r="F49" s="22" t="s">
-        <v>122</v>
+      <c r="F49" s="28" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -3658,13 +3853,13 @@
         <v>20045</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
-      <c r="F50" s="22" t="s">
-        <v>124</v>
+      <c r="F50" s="28" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -3672,13 +3867,13 @@
         <v>20046</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="22" t="s">
-        <v>126</v>
+      <c r="F51" s="28" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -3686,13 +3881,13 @@
         <v>20047</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F52" s="22" t="s">
-        <v>128</v>
+      <c r="F52" s="28" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -3700,13 +3895,13 @@
         <v>20048</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
-      <c r="F53" s="22" t="s">
-        <v>130</v>
+      <c r="F53" s="28" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -3714,13 +3909,13 @@
         <v>20049</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="22" t="s">
-        <v>132</v>
+      <c r="F54" s="28" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -3728,13 +3923,13 @@
         <v>20050</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
-      <c r="F55" s="22" t="s">
-        <v>134</v>
+      <c r="F55" s="28" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -3742,13 +3937,13 @@
         <v>20051</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
-      <c r="F56" s="22" t="s">
-        <v>136</v>
+      <c r="F56" s="28" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -3756,13 +3951,13 @@
         <v>20052</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="22" t="s">
-        <v>138</v>
+      <c r="F57" s="28" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -3770,13 +3965,13 @@
         <v>20053</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
-      <c r="F58" s="22" t="s">
-        <v>140</v>
+      <c r="F58" s="28" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -3784,13 +3979,13 @@
         <v>20054</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
-      <c r="F59" s="22" t="s">
-        <v>142</v>
+      <c r="F59" s="28" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -3798,13 +3993,13 @@
         <v>20055</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
-      <c r="F60" s="22" t="s">
-        <v>144</v>
+      <c r="F60" s="28" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -3812,13 +4007,13 @@
         <v>20056</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
-      <c r="F61" s="22" t="s">
-        <v>146</v>
+      <c r="F61" s="28" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -3826,13 +4021,13 @@
         <v>20057</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
-      <c r="F62" s="22" t="s">
-        <v>148</v>
+      <c r="F62" s="28" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -3840,13 +4035,13 @@
         <v>20058</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="22" t="s">
-        <v>150</v>
+      <c r="F63" s="28" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -3854,13 +4049,13 @@
         <v>20059</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
-      <c r="F64" s="22" t="s">
-        <v>152</v>
+      <c r="F64" s="28" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -3868,13 +4063,13 @@
         <v>20060</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
-      <c r="F65" s="22" t="s">
-        <v>154</v>
+      <c r="F65" s="28" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -3882,13 +4077,13 @@
         <v>20061</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
-      <c r="F66" s="22" t="s">
-        <v>156</v>
+      <c r="F66" s="28" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -3896,13 +4091,13 @@
         <v>20062</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
-      <c r="F67" s="22" t="s">
-        <v>158</v>
+      <c r="F67" s="28" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -3910,13 +4105,13 @@
         <v>20063</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
-      <c r="F68" s="22" t="s">
-        <v>160</v>
+      <c r="F68" s="28" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -3924,13 +4119,13 @@
         <v>20064</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
-      <c r="F69" s="22" t="s">
-        <v>162</v>
+      <c r="F69" s="28" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -3938,13 +4133,13 @@
         <v>20065</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
-      <c r="F70" s="22" t="s">
-        <v>164</v>
+      <c r="F70" s="28" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -3952,13 +4147,13 @@
         <v>20066</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
-      <c r="F71" s="22" t="s">
-        <v>166</v>
+      <c r="F71" s="28" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -3966,13 +4161,13 @@
         <v>20067</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
-      <c r="F72" s="22" t="s">
-        <v>168</v>
+      <c r="F72" s="28" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -3980,13 +4175,13 @@
         <v>20068</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
-      <c r="F73" s="22" t="s">
-        <v>170</v>
+      <c r="F73" s="28" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -3994,13 +4189,13 @@
         <v>20069</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
-      <c r="F74" s="22" t="s">
-        <v>172</v>
+      <c r="F74" s="28" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -4008,13 +4203,13 @@
         <v>20070</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
-      <c r="F75" s="22" t="s">
-        <v>174</v>
+      <c r="F75" s="28" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -4022,13 +4217,13 @@
         <v>20071</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
       </c>
-      <c r="F76" s="22" t="s">
-        <v>176</v>
+      <c r="F76" s="28" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -4036,13 +4231,13 @@
         <v>20072</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
-      <c r="F77" s="22" t="s">
-        <v>178</v>
+      <c r="F77" s="28" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -4119,13 +4314,13 @@
         <v>21001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>180</v>
+      <c r="F6" s="27" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -4133,13 +4328,13 @@
         <v>21002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>182</v>
+      <c r="F7" s="27" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -4147,13 +4342,13 @@
         <v>21003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="21" t="s">
-        <v>184</v>
+      <c r="F8" s="27" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -4161,13 +4356,13 @@
         <v>21004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>186</v>
+      <c r="F9" s="27" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -4175,13 +4370,13 @@
         <v>21005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="21" t="s">
-        <v>188</v>
+      <c r="F10" s="27" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -4189,13 +4384,13 @@
         <v>21006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>190</v>
+      <c r="F11" s="27" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -4203,13 +4398,13 @@
         <v>21007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>192</v>
+      <c r="F12" s="27" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:6">
@@ -4217,21 +4412,21 @@
         <v>21008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>194</v>
+      <c r="F13" s="27" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C14" s="1">
         <v>21009</v>
@@ -4240,10 +4435,10 @@
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C15" s="1">
         <v>21010</v>
@@ -4252,10 +4447,10 @@
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C16" s="1">
         <v>21011</v>
@@ -4264,10 +4459,10 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C17" s="1">
         <v>21012</v>
@@ -4425,13 +4620,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>197</v>
+      <c r="F6" s="29" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -4439,13 +4634,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>199</v>
+      <c r="F7" s="29" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -4453,13 +4648,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>201</v>
+      <c r="F8" s="29" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -4467,13 +4662,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>203</v>
+      <c r="F9" s="29" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -4481,13 +4676,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>205</v>
+      <c r="F10" s="29" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -4495,13 +4690,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>207</v>
+      <c r="F11" s="29" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -4509,13 +4704,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>209</v>
+      <c r="F12" s="29" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -4523,13 +4718,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>211</v>
+      <c r="F13" s="29" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4537,13 +4732,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
-      <c r="F14" s="20" t="s">
-        <v>213</v>
+      <c r="F14" s="29" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -4551,13 +4746,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>215</v>
+      <c r="F15" s="29" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -4565,13 +4760,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
-      <c r="F16" s="20" t="s">
-        <v>217</v>
+      <c r="F16" s="29" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -4579,13 +4774,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
-      <c r="F17" s="20" t="s">
-        <v>219</v>
+      <c r="F17" s="29" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -4593,13 +4788,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>221</v>
+      <c r="F18" s="29" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -4607,13 +4802,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
-      <c r="F19" s="20" t="s">
-        <v>223</v>
+      <c r="F19" s="29" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -4621,13 +4816,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>225</v>
+      <c r="F20" s="29" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -4635,13 +4830,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
-      <c r="F21" s="20" t="s">
-        <v>227</v>
+      <c r="F21" s="29" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -4649,13 +4844,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
-      <c r="F22" s="20" t="s">
-        <v>229</v>
+      <c r="F22" s="29" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -4663,13 +4858,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>231</v>
+      <c r="F23" s="29" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -4677,13 +4872,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
-      <c r="F24" s="20" t="s">
-        <v>233</v>
+      <c r="F24" s="29" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -4691,13 +4886,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
-      <c r="F25" s="20" t="s">
-        <v>235</v>
+      <c r="F25" s="29" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -4705,13 +4900,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
-      <c r="F26" s="20" t="s">
-        <v>237</v>
+      <c r="F26" s="29" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -4719,13 +4914,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
-      <c r="F27" s="20" t="s">
-        <v>239</v>
+      <c r="F27" s="29" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -4733,13 +4928,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
-      <c r="F28" s="20" t="s">
-        <v>241</v>
+      <c r="F28" s="29" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -4747,13 +4942,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
-      <c r="F29" s="20" t="s">
-        <v>243</v>
+      <c r="F29" s="29" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -4761,13 +4956,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>245</v>
+      <c r="F30" s="29" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -4775,13 +4970,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
-      <c r="F31" s="20" t="s">
-        <v>247</v>
+      <c r="F31" s="29" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -4789,13 +4984,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>249</v>
+      <c r="F32" s="29" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -4803,13 +4998,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
-      <c r="F33" s="20" t="s">
-        <v>251</v>
+      <c r="F33" s="29" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -4817,13 +5012,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
-      <c r="F34" s="20" t="s">
-        <v>253</v>
+      <c r="F34" s="29" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -4831,13 +5026,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
-      <c r="F35" s="20" t="s">
-        <v>255</v>
+      <c r="F35" s="29" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -4845,13 +5040,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
-      <c r="F36" s="20" t="s">
-        <v>257</v>
+      <c r="F36" s="29" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -4859,13 +5054,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
-      <c r="F37" s="20" t="s">
-        <v>259</v>
+      <c r="F37" s="29" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -4873,13 +5068,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
-      <c r="F38" s="20" t="s">
-        <v>261</v>
+      <c r="F38" s="29" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -4887,13 +5082,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
-      <c r="F39" s="20" t="s">
-        <v>263</v>
+      <c r="F39" s="29" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -4901,13 +5096,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
-      <c r="F40" s="20" t="s">
-        <v>265</v>
+      <c r="F40" s="29" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -4915,13 +5110,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
-      <c r="F41" s="20" t="s">
-        <v>267</v>
+      <c r="F41" s="29" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -4929,13 +5124,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
-      <c r="F42" s="20" t="s">
-        <v>269</v>
+      <c r="F42" s="29" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -4943,13 +5138,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
-      <c r="F43" s="20" t="s">
-        <v>271</v>
+      <c r="F43" s="29" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -4957,13 +5152,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
-      <c r="F44" s="20" t="s">
-        <v>273</v>
+      <c r="F44" s="29" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -4971,13 +5166,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
-      <c r="F45" s="20" t="s">
-        <v>275</v>
+      <c r="F45" s="29" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -4985,13 +5180,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
-      <c r="F46" s="20" t="s">
-        <v>277</v>
+      <c r="F46" s="29" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -4999,13 +5194,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
-      <c r="F47" s="20" t="s">
-        <v>279</v>
+      <c r="F47" s="29" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -5013,13 +5208,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
-      <c r="F48" s="20" t="s">
-        <v>281</v>
+      <c r="F48" s="29" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5027,13 +5222,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
-      <c r="F49" s="20" t="s">
-        <v>283</v>
+      <c r="F49" s="29" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5041,13 +5236,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
-      <c r="F50" s="20" t="s">
-        <v>285</v>
+      <c r="F50" s="29" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5055,13 +5250,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
-      <c r="F51" s="20" t="s">
-        <v>287</v>
+      <c r="F51" s="29" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5069,13 +5264,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
-      <c r="F52" s="20" t="s">
-        <v>289</v>
+      <c r="F52" s="29" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5083,13 +5278,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
-      <c r="F53" s="20" t="s">
-        <v>290</v>
+      <c r="F53" s="29" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5097,13 +5292,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
-      <c r="F54" s="20" t="s">
-        <v>292</v>
+      <c r="F54" s="29" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5111,13 +5306,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
-      <c r="F55" s="20" t="s">
-        <v>294</v>
+      <c r="F55" s="29" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5125,13 +5320,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
-      <c r="F56" s="20" t="s">
-        <v>296</v>
+      <c r="F56" s="29" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5139,13 +5334,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
-      <c r="F57" s="20" t="s">
-        <v>298</v>
+      <c r="F57" s="29" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5153,13 +5348,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
-      <c r="F58" s="20" t="s">
-        <v>300</v>
+      <c r="F58" s="29" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5167,13 +5362,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
-      <c r="F59" s="20" t="s">
-        <v>302</v>
+      <c r="F59" s="29" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5181,13 +5376,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
-      <c r="F60" s="20" t="s">
-        <v>304</v>
+      <c r="F60" s="29" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5195,13 +5390,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
-      <c r="F61" s="20" t="s">
-        <v>306</v>
+      <c r="F61" s="29" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5209,13 +5404,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
-      <c r="F62" s="20" t="s">
-        <v>307</v>
+      <c r="F62" s="29" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5223,13 +5418,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
-      <c r="F63" s="20" t="s">
-        <v>309</v>
+      <c r="F63" s="29" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5237,13 +5432,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
-      <c r="F64" s="20" t="s">
-        <v>311</v>
+      <c r="F64" s="29" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5251,13 +5446,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
-      <c r="F65" s="20" t="s">
-        <v>313</v>
+      <c r="F65" s="29" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5265,13 +5460,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
-      <c r="F66" s="20" t="s">
-        <v>315</v>
+      <c r="F66" s="29" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5279,13 +5474,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
-      <c r="F67" s="20" t="s">
-        <v>317</v>
+      <c r="F67" s="29" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5293,13 +5488,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
-      <c r="F68" s="20" t="s">
-        <v>319</v>
+      <c r="F68" s="29" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5307,13 +5502,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
-      <c r="F69" s="20" t="s">
-        <v>321</v>
+      <c r="F69" s="29" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5321,13 +5516,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
-      <c r="F70" s="20" t="s">
-        <v>323</v>
+      <c r="F70" s="29" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5335,13 +5530,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
-      <c r="F71" s="20" t="s">
-        <v>325</v>
+      <c r="F71" s="29" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5349,13 +5544,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
-      <c r="F72" s="20" t="s">
-        <v>326</v>
+      <c r="F72" s="29" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5363,13 +5558,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
-      <c r="F73" s="20" t="s">
-        <v>328</v>
+      <c r="F73" s="29" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5377,13 +5572,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
-      <c r="F74" s="20" t="s">
-        <v>330</v>
+      <c r="F74" s="29" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5391,13 +5586,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
-      <c r="F75" s="20" t="s">
-        <v>332</v>
+      <c r="F75" s="29" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5405,13 +5600,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
-      <c r="F76" s="20" t="s">
-        <v>334</v>
+      <c r="F76" s="29" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -5419,13 +5614,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
-      <c r="F77" s="20" t="s">
-        <v>336</v>
+      <c r="F77" s="29" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -5507,13 +5702,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -5599,13 +5794,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>340</v>
+      <c r="F6" s="30" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5613,13 +5808,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>342</v>
+      <c r="F7" s="30" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5627,13 +5822,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>344</v>
+      <c r="F8" s="30" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5641,13 +5836,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>346</v>
+      <c r="F9" s="30" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5655,13 +5850,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="19" t="s">
-        <v>348</v>
+      <c r="F10" s="30" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5669,13 +5864,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>350</v>
+      <c r="F11" s="30" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5683,13 +5878,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
-      <c r="F12" s="19" t="s">
-        <v>352</v>
+      <c r="F12" s="30" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5697,13 +5892,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="23" t="s">
-        <v>354</v>
+      <c r="F13" s="31" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5711,13 +5906,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="23" t="s">
-        <v>356</v>
+      <c r="F14" s="31" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -5827,13 +6022,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>358</v>
+      <c r="F6" s="29" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5841,13 +6036,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>360</v>
+      <c r="F7" s="29" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5855,13 +6050,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>362</v>
+      <c r="F8" s="29" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5869,13 +6064,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
-      <c r="F9" s="20" t="s">
-        <v>364</v>
+      <c r="F9" s="29" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5883,13 +6078,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
-      <c r="F10" s="20" t="s">
-        <v>366</v>
+      <c r="F10" s="29" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5897,13 +6092,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>368</v>
+      <c r="F11" s="29" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5911,13 +6106,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>370</v>
+      <c r="F12" s="29" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5925,13 +6120,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>372</v>
+      <c r="F13" s="29" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5939,13 +6134,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
-      <c r="F14" s="20" t="s">
-        <v>374</v>
+      <c r="F14" s="29" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -5953,13 +6148,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>376</v>
+      <c r="F15" s="29" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -5967,13 +6162,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
-      <c r="F16" s="20" t="s">
-        <v>378</v>
+      <c r="F16" s="29" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -5981,13 +6176,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="20" t="s">
-        <v>380</v>
+      <c r="F17" s="29" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -5995,13 +6190,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>382</v>
+      <c r="F18" s="29" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -6009,13 +6204,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
-      <c r="F19" s="20" t="s">
-        <v>384</v>
+      <c r="F19" s="29" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6023,13 +6218,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>386</v>
+      <c r="F20" s="29" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6037,13 +6232,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
-      <c r="F21" s="20" t="s">
-        <v>388</v>
+      <c r="F21" s="29" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6051,13 +6246,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
-      <c r="F22" s="20" t="s">
-        <v>390</v>
+      <c r="F22" s="29" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6065,13 +6260,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
-      <c r="F23" s="20" t="s">
-        <v>392</v>
+      <c r="F23" s="29" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6079,13 +6274,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
-      <c r="F24" s="20" t="s">
-        <v>394</v>
+      <c r="F24" s="29" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6093,13 +6288,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
-      <c r="F25" s="20" t="s">
-        <v>396</v>
+      <c r="F25" s="29" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6107,13 +6302,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
-      <c r="F26" s="20" t="s">
-        <v>398</v>
+      <c r="F26" s="29" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6121,13 +6316,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
-      <c r="F27" s="20" t="s">
-        <v>400</v>
+      <c r="F27" s="29" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6135,13 +6330,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
-      <c r="F28" s="20" t="s">
-        <v>402</v>
+      <c r="F28" s="29" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6149,13 +6344,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
-      <c r="F29" s="20" t="s">
-        <v>404</v>
+      <c r="F29" s="29" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6163,13 +6358,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
-      <c r="F30" s="20" t="s">
-        <v>406</v>
+      <c r="F30" s="29" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6177,13 +6372,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
-      <c r="F31" s="20" t="s">
-        <v>408</v>
+      <c r="F31" s="29" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6191,13 +6386,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>410</v>
+      <c r="F32" s="29" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6205,13 +6400,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
-      <c r="F33" s="20" t="s">
-        <v>412</v>
+      <c r="F33" s="29" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6219,13 +6414,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
-      <c r="F34" s="20" t="s">
-        <v>414</v>
+      <c r="F34" s="29" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6233,13 +6428,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
-      <c r="F35" s="20" t="s">
-        <v>416</v>
+      <c r="F35" s="29" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="437">
   <si>
     <t>_id</t>
   </si>
@@ -1059,6 +1059,18 @@
   </si>
   <si>
     <t>201022,201023,201024</t>
+  </si>
+  <si>
+    <t>福运</t>
+  </si>
+  <si>
+    <t>201025,201026,201027</t>
+  </si>
+  <si>
+    <t>寻宝</t>
+  </si>
+  <si>
+    <t>201028,201029,201030</t>
   </si>
   <si>
     <t>#</t>
@@ -1754,7 +1766,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1797,6 +1809,12 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2298,137 +2316,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2469,26 +2487,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
@@ -2825,342 +2846,342 @@
   <dimension ref="C1:F33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="9" style="17"/>
-    <col min="3" max="3" width="8.75" style="17" customWidth="1"/>
-    <col min="4" max="4" width="15" style="17" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="17" customWidth="1"/>
-    <col min="6" max="6" width="30.75" style="18" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="17"/>
+    <col min="1" max="2" width="9" style="18"/>
+    <col min="3" max="3" width="8.75" style="18" customWidth="1"/>
+    <col min="4" max="4" width="15" style="18" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="18" customWidth="1"/>
+    <col min="6" max="6" width="30.75" style="19" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" s="17" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F1" s="18"/>
-    </row>
-    <row r="2" s="17" customFormat="1" customHeight="1" spans="3:6">
-      <c r="F2" s="18"/>
-    </row>
-    <row r="3" s="17" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C3" s="19" t="s">
+    <row r="1" s="18" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" s="18" customFormat="1" customHeight="1" spans="3:6">
+      <c r="F2" s="19"/>
+    </row>
+    <row r="3" s="18" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="17" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C4" s="19" t="s">
+    <row r="4" s="18" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="17" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C5" s="19" t="s">
+    <row r="5" s="18" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="21" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="17" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C6" s="17">
+    <row r="6" s="18" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C6" s="18">
         <v>1</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="18">
         <v>5</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
-      <c r="C7" s="17">
-        <v>2</v>
-      </c>
-      <c r="D7" s="17" t="s">
+      <c r="C7" s="18">
+        <v>2</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <v>5</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <v>3</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <v>5</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="25" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
-      <c r="C9" s="17">
+      <c r="C9" s="18">
         <v>4</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="18">
         <v>5</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="25" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <v>5</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="18">
         <v>6</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
-      <c r="C11" s="17">
+      <c r="C11" s="18">
         <v>6</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="18">
         <v>6</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="26" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <v>7</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="18">
         <v>6</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="26" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
-      <c r="C16" s="17">
+      <c r="C16" s="18">
         <v>11</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="18">
         <v>5</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="19" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="17">
+      <c r="C17" s="18">
         <v>12</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="18">
         <v>5</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="19" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="17">
+      <c r="C18" s="18">
         <v>13</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="18">
         <v>5</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="F18" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="17">
+      <c r="C19" s="18">
         <v>14</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="18">
         <v>5</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="17">
+      <c r="C20" s="18">
         <v>15</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="18">
         <v>5</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F20" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" s="17" customFormat="1" customHeight="1" spans="3:6">
-      <c r="C22" s="22"/>
+    <row r="22" s="18" customFormat="1" customHeight="1" spans="3:6">
+      <c r="C22" s="23"/>
     </row>
     <row r="26" customHeight="1" spans="3:6">
-      <c r="C26" s="17">
+      <c r="C26" s="18">
         <v>21</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="18">
         <v>5</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="27" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
-      <c r="C27" s="17">
+      <c r="C27" s="18">
         <v>22</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="18">
         <v>5</v>
       </c>
-      <c r="F27" s="26" t="s">
+      <c r="F27" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
-      <c r="C28" s="17">
+      <c r="C28" s="18">
         <v>23</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="18">
         <v>5</v>
       </c>
-      <c r="F28" s="26" t="s">
+      <c r="F28" s="27" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
-      <c r="C29" s="17">
+      <c r="C29" s="18">
         <v>24</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="18">
         <v>5</v>
       </c>
-      <c r="F29" s="26" t="s">
+      <c r="F29" s="27" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
-      <c r="C30" s="17">
+      <c r="C30" s="18">
         <v>25</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="18">
         <v>5</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="27" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
-      <c r="C31" s="17">
+      <c r="C31" s="18">
         <v>26</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="18">
         <v>5</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="27" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
-      <c r="C32" s="17">
+      <c r="C32" s="18">
         <v>27</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="18">
         <v>5</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="F32" s="27" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
-      <c r="C33" s="17">
+      <c r="C33" s="18">
         <v>28</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="18">
         <v>5</v>
       </c>
-      <c r="F33" s="26" t="s">
+      <c r="F33" s="27" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3242,7 +3263,7 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="28" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3256,7 +3277,7 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="28" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3270,7 +3291,7 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="28" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3284,7 +3305,7 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="28" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3298,7 +3319,7 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="28" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3312,7 +3333,7 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="29" t="s">
         <v>62</v>
       </c>
     </row>
@@ -3326,7 +3347,7 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="28" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3340,7 +3361,7 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="28" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3354,7 +3375,7 @@
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="28" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3368,7 +3389,7 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="28" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3382,7 +3403,7 @@
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="28" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3396,7 +3417,7 @@
       <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="F17" s="29" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3410,7 +3431,7 @@
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="28" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3424,7 +3445,7 @@
       <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="28" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3438,7 +3459,7 @@
       <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F20" s="28" t="s">
         <v>80</v>
       </c>
     </row>
@@ -3452,7 +3473,7 @@
       <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="27" t="s">
+      <c r="F21" s="28" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3466,7 +3487,7 @@
       <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="28" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3480,7 +3501,7 @@
       <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F23" s="29" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3494,7 +3515,7 @@
       <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="F24" s="28" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3508,7 +3529,7 @@
       <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="27" t="s">
+      <c r="F25" s="28" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3522,7 +3543,7 @@
       <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F26" s="28" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3536,7 +3557,7 @@
       <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="27" t="s">
+      <c r="F27" s="28" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3550,7 +3571,7 @@
       <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F28" s="28" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3564,7 +3585,7 @@
       <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="28" t="s">
+      <c r="F29" s="29" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3578,7 +3599,7 @@
       <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="28" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3592,7 +3613,7 @@
       <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="28" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3606,7 +3627,7 @@
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="28" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3620,7 +3641,7 @@
       <c r="E33" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="27" t="s">
+      <c r="F33" s="28" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3634,7 +3655,7 @@
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="28" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3648,7 +3669,7 @@
       <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="28" t="s">
+      <c r="F35" s="29" t="s">
         <v>110</v>
       </c>
     </row>
@@ -3662,7 +3683,7 @@
       <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="27" t="s">
+      <c r="F36" s="28" t="s">
         <v>112</v>
       </c>
     </row>
@@ -3676,7 +3697,7 @@
       <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="27" t="s">
+      <c r="F37" s="28" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3690,7 +3711,7 @@
       <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="27" t="s">
+      <c r="F38" s="28" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3704,7 +3725,7 @@
       <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="28" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3718,7 +3739,7 @@
       <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F40" s="27" t="s">
+      <c r="F40" s="28" t="s">
         <v>120</v>
       </c>
     </row>
@@ -3732,7 +3753,7 @@
       <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F41" s="28" t="s">
+      <c r="F41" s="29" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3746,7 +3767,7 @@
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="27" t="s">
+      <c r="F42" s="28" t="s">
         <v>124</v>
       </c>
     </row>
@@ -3760,7 +3781,7 @@
       <c r="E43" s="1">
         <v>2</v>
       </c>
-      <c r="F43" s="27" t="s">
+      <c r="F43" s="28" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3774,7 +3795,7 @@
       <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="F44" s="27" t="s">
+      <c r="F44" s="28" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3788,7 +3809,7 @@
       <c r="E45" s="1">
         <v>2</v>
       </c>
-      <c r="F45" s="27" t="s">
+      <c r="F45" s="28" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3802,7 +3823,7 @@
       <c r="E46" s="1">
         <v>2</v>
       </c>
-      <c r="F46" s="27" t="s">
+      <c r="F46" s="28" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3816,7 +3837,7 @@
       <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="28" t="s">
+      <c r="F47" s="29" t="s">
         <v>134</v>
       </c>
     </row>
@@ -3830,7 +3851,7 @@
       <c r="E48" s="1">
         <v>2</v>
       </c>
-      <c r="F48" s="28" t="s">
+      <c r="F48" s="29" t="s">
         <v>136</v>
       </c>
     </row>
@@ -3844,7 +3865,7 @@
       <c r="E49" s="1">
         <v>2</v>
       </c>
-      <c r="F49" s="28" t="s">
+      <c r="F49" s="29" t="s">
         <v>138</v>
       </c>
     </row>
@@ -3858,7 +3879,7 @@
       <c r="E50" s="1">
         <v>2</v>
       </c>
-      <c r="F50" s="28" t="s">
+      <c r="F50" s="29" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3872,7 +3893,7 @@
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="28" t="s">
+      <c r="F51" s="29" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3886,7 +3907,7 @@
       <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F52" s="28" t="s">
+      <c r="F52" s="29" t="s">
         <v>144</v>
       </c>
     </row>
@@ -3900,7 +3921,7 @@
       <c r="E53" s="1">
         <v>2</v>
       </c>
-      <c r="F53" s="28" t="s">
+      <c r="F53" s="29" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3914,7 +3935,7 @@
       <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="28" t="s">
+      <c r="F54" s="29" t="s">
         <v>148</v>
       </c>
     </row>
@@ -3928,7 +3949,7 @@
       <c r="E55" s="1">
         <v>2</v>
       </c>
-      <c r="F55" s="28" t="s">
+      <c r="F55" s="29" t="s">
         <v>150</v>
       </c>
     </row>
@@ -3942,7 +3963,7 @@
       <c r="E56" s="1">
         <v>2</v>
       </c>
-      <c r="F56" s="28" t="s">
+      <c r="F56" s="29" t="s">
         <v>152</v>
       </c>
     </row>
@@ -3956,7 +3977,7 @@
       <c r="E57" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="28" t="s">
+      <c r="F57" s="29" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3970,7 +3991,7 @@
       <c r="E58" s="1">
         <v>2</v>
       </c>
-      <c r="F58" s="28" t="s">
+      <c r="F58" s="29" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3984,7 +4005,7 @@
       <c r="E59" s="1">
         <v>2</v>
       </c>
-      <c r="F59" s="28" t="s">
+      <c r="F59" s="29" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3998,7 +4019,7 @@
       <c r="E60" s="1">
         <v>2</v>
       </c>
-      <c r="F60" s="28" t="s">
+      <c r="F60" s="29" t="s">
         <v>160</v>
       </c>
     </row>
@@ -4012,7 +4033,7 @@
       <c r="E61" s="1">
         <v>2</v>
       </c>
-      <c r="F61" s="28" t="s">
+      <c r="F61" s="29" t="s">
         <v>162</v>
       </c>
     </row>
@@ -4026,7 +4047,7 @@
       <c r="E62" s="1">
         <v>2</v>
       </c>
-      <c r="F62" s="28" t="s">
+      <c r="F62" s="29" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4040,7 +4061,7 @@
       <c r="E63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="28" t="s">
+      <c r="F63" s="29" t="s">
         <v>166</v>
       </c>
     </row>
@@ -4054,7 +4075,7 @@
       <c r="E64" s="1">
         <v>2</v>
       </c>
-      <c r="F64" s="28" t="s">
+      <c r="F64" s="29" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4068,7 +4089,7 @@
       <c r="E65" s="1">
         <v>2</v>
       </c>
-      <c r="F65" s="28" t="s">
+      <c r="F65" s="29" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4082,7 +4103,7 @@
       <c r="E66" s="1">
         <v>2</v>
       </c>
-      <c r="F66" s="28" t="s">
+      <c r="F66" s="29" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4096,7 +4117,7 @@
       <c r="E67" s="1">
         <v>2</v>
       </c>
-      <c r="F67" s="28" t="s">
+      <c r="F67" s="29" t="s">
         <v>174</v>
       </c>
     </row>
@@ -4110,7 +4131,7 @@
       <c r="E68" s="1">
         <v>2</v>
       </c>
-      <c r="F68" s="28" t="s">
+      <c r="F68" s="29" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4124,7 +4145,7 @@
       <c r="E69" s="1">
         <v>2</v>
       </c>
-      <c r="F69" s="28" t="s">
+      <c r="F69" s="29" t="s">
         <v>178</v>
       </c>
     </row>
@@ -4138,7 +4159,7 @@
       <c r="E70" s="1">
         <v>2</v>
       </c>
-      <c r="F70" s="28" t="s">
+      <c r="F70" s="29" t="s">
         <v>180</v>
       </c>
     </row>
@@ -4152,7 +4173,7 @@
       <c r="E71" s="1">
         <v>2</v>
       </c>
-      <c r="F71" s="28" t="s">
+      <c r="F71" s="29" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4166,7 +4187,7 @@
       <c r="E72" s="1">
         <v>2</v>
       </c>
-      <c r="F72" s="28" t="s">
+      <c r="F72" s="29" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4180,7 +4201,7 @@
       <c r="E73" s="1">
         <v>2</v>
       </c>
-      <c r="F73" s="28" t="s">
+      <c r="F73" s="29" t="s">
         <v>186</v>
       </c>
     </row>
@@ -4194,7 +4215,7 @@
       <c r="E74" s="1">
         <v>2</v>
       </c>
-      <c r="F74" s="28" t="s">
+      <c r="F74" s="29" t="s">
         <v>188</v>
       </c>
     </row>
@@ -4208,7 +4229,7 @@
       <c r="E75" s="1">
         <v>2</v>
       </c>
-      <c r="F75" s="28" t="s">
+      <c r="F75" s="29" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4222,7 +4243,7 @@
       <c r="E76" s="1">
         <v>2</v>
       </c>
-      <c r="F76" s="28" t="s">
+      <c r="F76" s="29" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4236,7 +4257,7 @@
       <c r="E77" s="1">
         <v>2</v>
       </c>
-      <c r="F77" s="28" t="s">
+      <c r="F77" s="29" t="s">
         <v>194</v>
       </c>
     </row>
@@ -4319,7 +4340,7 @@
       <c r="E6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="28" t="s">
         <v>196</v>
       </c>
     </row>
@@ -4333,7 +4354,7 @@
       <c r="E7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="28" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4347,7 +4368,7 @@
       <c r="E8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="28" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4361,7 +4382,7 @@
       <c r="E9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="28" t="s">
         <v>202</v>
       </c>
     </row>
@@ -4375,7 +4396,7 @@
       <c r="E10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="28" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4389,7 +4410,7 @@
       <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="27" t="s">
+      <c r="F11" s="28" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4403,7 +4424,7 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="28" t="s">
         <v>208</v>
       </c>
     </row>
@@ -4417,40 +4438,44 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="28" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A14" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="C14" s="1">
         <v>21009</v>
       </c>
-      <c r="F14" s="16"/>
+      <c r="D14" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A15" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="C15" s="1">
         <v>21010</v>
       </c>
-      <c r="F15" s="16"/>
+      <c r="D15" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="1">
+        <v>2</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C16" s="1">
         <v>21011</v>
@@ -4459,10 +4484,10 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C17" s="1">
         <v>21012</v>
@@ -4620,13 +4645,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>213</v>
+      <c r="F6" s="30" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -4634,13 +4659,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>215</v>
+      <c r="F7" s="30" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -4648,13 +4673,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
-      <c r="F8" s="29" t="s">
-        <v>217</v>
+      <c r="F8" s="30" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -4662,13 +4687,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>219</v>
+      <c r="F9" s="30" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -4676,13 +4701,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
-      <c r="F10" s="29" t="s">
-        <v>221</v>
+      <c r="F10" s="30" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -4690,13 +4715,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
-      <c r="F11" s="29" t="s">
-        <v>223</v>
+      <c r="F11" s="30" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -4704,13 +4729,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
-      <c r="F12" s="29" t="s">
-        <v>225</v>
+      <c r="F12" s="30" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -4718,13 +4743,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
-      <c r="F13" s="29" t="s">
-        <v>227</v>
+      <c r="F13" s="30" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4732,13 +4757,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
-      <c r="F14" s="29" t="s">
-        <v>229</v>
+      <c r="F14" s="30" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -4746,13 +4771,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
-      <c r="F15" s="29" t="s">
-        <v>231</v>
+      <c r="F15" s="30" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -4760,13 +4785,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
-      <c r="F16" s="29" t="s">
-        <v>233</v>
+      <c r="F16" s="30" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -4774,13 +4799,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
-      <c r="F17" s="29" t="s">
-        <v>235</v>
+      <c r="F17" s="30" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -4788,13 +4813,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
-      <c r="F18" s="29" t="s">
-        <v>237</v>
+      <c r="F18" s="30" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -4802,13 +4827,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
-      <c r="F19" s="29" t="s">
-        <v>239</v>
+      <c r="F19" s="30" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -4816,13 +4841,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
-      <c r="F20" s="29" t="s">
-        <v>241</v>
+      <c r="F20" s="30" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -4830,13 +4855,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
-      <c r="F21" s="29" t="s">
-        <v>243</v>
+      <c r="F21" s="30" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -4844,13 +4869,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
-      <c r="F22" s="29" t="s">
-        <v>245</v>
+      <c r="F22" s="30" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -4858,13 +4883,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
-      <c r="F23" s="29" t="s">
-        <v>247</v>
+      <c r="F23" s="30" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -4872,13 +4897,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
-      <c r="F24" s="29" t="s">
-        <v>249</v>
+      <c r="F24" s="30" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -4886,13 +4911,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
-      <c r="F25" s="29" t="s">
-        <v>251</v>
+      <c r="F25" s="30" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -4900,13 +4925,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
-      <c r="F26" s="29" t="s">
-        <v>253</v>
+      <c r="F26" s="30" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -4914,13 +4939,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
-      <c r="F27" s="29" t="s">
-        <v>255</v>
+      <c r="F27" s="30" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -4928,13 +4953,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
-      <c r="F28" s="29" t="s">
-        <v>257</v>
+      <c r="F28" s="30" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -4942,13 +4967,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
-      <c r="F29" s="29" t="s">
-        <v>259</v>
+      <c r="F29" s="30" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -4956,13 +4981,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
-      <c r="F30" s="29" t="s">
-        <v>261</v>
+      <c r="F30" s="30" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -4970,13 +4995,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
-      <c r="F31" s="29" t="s">
-        <v>263</v>
+      <c r="F31" s="30" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -4984,13 +5009,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
-      <c r="F32" s="29" t="s">
-        <v>265</v>
+      <c r="F32" s="30" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -4998,13 +5023,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
-      <c r="F33" s="29" t="s">
-        <v>267</v>
+      <c r="F33" s="30" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -5012,13 +5037,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
-      <c r="F34" s="29" t="s">
-        <v>269</v>
+      <c r="F34" s="30" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -5026,13 +5051,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
-      <c r="F35" s="29" t="s">
-        <v>271</v>
+      <c r="F35" s="30" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -5040,13 +5065,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
-      <c r="F36" s="29" t="s">
-        <v>273</v>
+      <c r="F36" s="30" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -5054,13 +5079,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
-      <c r="F37" s="29" t="s">
-        <v>275</v>
+      <c r="F37" s="30" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -5068,13 +5093,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
-      <c r="F38" s="29" t="s">
-        <v>277</v>
+      <c r="F38" s="30" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -5082,13 +5107,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
-      <c r="F39" s="29" t="s">
-        <v>279</v>
+      <c r="F39" s="30" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -5096,13 +5121,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
-      <c r="F40" s="29" t="s">
-        <v>281</v>
+      <c r="F40" s="30" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -5110,13 +5135,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
-      <c r="F41" s="29" t="s">
-        <v>283</v>
+      <c r="F41" s="30" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -5124,13 +5149,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
-      <c r="F42" s="29" t="s">
-        <v>285</v>
+      <c r="F42" s="30" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -5138,13 +5163,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
-      <c r="F43" s="29" t="s">
-        <v>287</v>
+      <c r="F43" s="30" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -5152,13 +5177,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
-      <c r="F44" s="29" t="s">
-        <v>289</v>
+      <c r="F44" s="30" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -5166,13 +5191,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
-      <c r="F45" s="29" t="s">
-        <v>291</v>
+      <c r="F45" s="30" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -5180,13 +5205,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
-      <c r="F46" s="29" t="s">
-        <v>293</v>
+      <c r="F46" s="30" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -5194,13 +5219,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
-      <c r="F47" s="29" t="s">
-        <v>295</v>
+      <c r="F47" s="30" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -5208,13 +5233,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
-      <c r="F48" s="29" t="s">
-        <v>297</v>
+      <c r="F48" s="30" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5222,13 +5247,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
-      <c r="F49" s="29" t="s">
-        <v>299</v>
+      <c r="F49" s="30" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5236,13 +5261,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
-      <c r="F50" s="29" t="s">
-        <v>301</v>
+      <c r="F50" s="30" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5250,13 +5275,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
-      <c r="F51" s="29" t="s">
-        <v>303</v>
+      <c r="F51" s="30" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5264,13 +5289,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
-      <c r="F52" s="29" t="s">
-        <v>305</v>
+      <c r="F52" s="30" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5278,13 +5303,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
-      <c r="F53" s="29" t="s">
-        <v>306</v>
+      <c r="F53" s="30" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5292,13 +5317,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
-      <c r="F54" s="29" t="s">
-        <v>308</v>
+      <c r="F54" s="30" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5306,13 +5331,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
-      <c r="F55" s="29" t="s">
-        <v>310</v>
+      <c r="F55" s="30" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5320,13 +5345,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
-      <c r="F56" s="29" t="s">
-        <v>312</v>
+      <c r="F56" s="30" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5334,13 +5359,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
-      <c r="F57" s="29" t="s">
-        <v>314</v>
+      <c r="F57" s="30" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5348,13 +5373,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
-      <c r="F58" s="29" t="s">
-        <v>316</v>
+      <c r="F58" s="30" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5362,13 +5387,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
-      <c r="F59" s="29" t="s">
-        <v>318</v>
+      <c r="F59" s="30" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5376,13 +5401,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
-      <c r="F60" s="29" t="s">
-        <v>320</v>
+      <c r="F60" s="30" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5390,13 +5415,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
-      <c r="F61" s="29" t="s">
-        <v>322</v>
+      <c r="F61" s="30" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5404,13 +5429,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
-      <c r="F62" s="29" t="s">
-        <v>323</v>
+      <c r="F62" s="30" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5418,13 +5443,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
-      <c r="F63" s="29" t="s">
-        <v>325</v>
+      <c r="F63" s="30" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5432,13 +5457,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
-      <c r="F64" s="29" t="s">
-        <v>327</v>
+      <c r="F64" s="30" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5446,13 +5471,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
-      <c r="F65" s="29" t="s">
-        <v>329</v>
+      <c r="F65" s="30" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5460,13 +5485,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
-      <c r="F66" s="29" t="s">
-        <v>331</v>
+      <c r="F66" s="30" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5474,13 +5499,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
-      <c r="F67" s="29" t="s">
-        <v>333</v>
+      <c r="F67" s="30" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5488,13 +5513,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
-      <c r="F68" s="29" t="s">
-        <v>335</v>
+      <c r="F68" s="30" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5502,13 +5527,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
-      <c r="F69" s="29" t="s">
-        <v>337</v>
+      <c r="F69" s="30" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5516,13 +5541,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
-      <c r="F70" s="29" t="s">
-        <v>339</v>
+      <c r="F70" s="30" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5530,13 +5555,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
-      <c r="F71" s="29" t="s">
-        <v>341</v>
+      <c r="F71" s="30" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5544,13 +5569,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
-      <c r="F72" s="29" t="s">
-        <v>342</v>
+      <c r="F72" s="30" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5558,13 +5583,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
-      <c r="F73" s="29" t="s">
-        <v>344</v>
+      <c r="F73" s="30" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5572,13 +5597,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
-      <c r="F74" s="29" t="s">
-        <v>346</v>
+      <c r="F74" s="30" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5586,13 +5611,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
-      <c r="F75" s="29" t="s">
-        <v>348</v>
+      <c r="F75" s="30" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5600,13 +5625,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
-      <c r="F76" s="29" t="s">
-        <v>350</v>
+      <c r="F76" s="30" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -5614,13 +5639,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
-      <c r="F77" s="29" t="s">
-        <v>352</v>
+      <c r="F77" s="30" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -5702,13 +5727,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -5794,13 +5819,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>356</v>
+      <c r="F6" s="31" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5808,13 +5833,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
-      <c r="F7" s="30" t="s">
-        <v>358</v>
+      <c r="F7" s="31" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5822,13 +5847,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
-      <c r="F8" s="30" t="s">
-        <v>360</v>
+      <c r="F8" s="31" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5836,13 +5861,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="30" t="s">
-        <v>362</v>
+      <c r="F9" s="31" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5850,13 +5875,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
-      <c r="F10" s="30" t="s">
-        <v>364</v>
+      <c r="F10" s="31" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5864,13 +5889,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
-      <c r="F11" s="30" t="s">
-        <v>366</v>
+      <c r="F11" s="31" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5878,13 +5903,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
-      <c r="F12" s="30" t="s">
-        <v>368</v>
+      <c r="F12" s="31" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5892,13 +5917,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
-      <c r="F13" s="31" t="s">
-        <v>370</v>
+      <c r="F13" s="32" t="s">
+        <v>374</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5906,13 +5931,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
-      <c r="F14" s="31" t="s">
-        <v>372</v>
+      <c r="F14" s="32" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -6022,13 +6047,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>374</v>
+      <c r="F6" s="30" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6036,13 +6061,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
-      <c r="F7" s="29" t="s">
-        <v>376</v>
+      <c r="F7" s="30" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6050,13 +6075,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
-      <c r="F8" s="29" t="s">
-        <v>378</v>
+      <c r="F8" s="30" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6064,13 +6089,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>380</v>
+      <c r="F9" s="30" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6078,13 +6103,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
-      <c r="F10" s="29" t="s">
-        <v>382</v>
+      <c r="F10" s="30" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6092,13 +6117,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
-      <c r="F11" s="29" t="s">
-        <v>384</v>
+      <c r="F11" s="30" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6106,13 +6131,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="29" t="s">
-        <v>386</v>
+      <c r="F12" s="30" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6120,13 +6145,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
-      <c r="F13" s="29" t="s">
-        <v>388</v>
+      <c r="F13" s="30" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6134,13 +6159,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
-      <c r="F14" s="29" t="s">
-        <v>390</v>
+      <c r="F14" s="30" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -6148,13 +6173,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
-      <c r="F15" s="29" t="s">
-        <v>392</v>
+      <c r="F15" s="30" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -6162,13 +6187,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
-      <c r="F16" s="29" t="s">
-        <v>394</v>
+      <c r="F16" s="30" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -6176,13 +6201,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="29" t="s">
-        <v>396</v>
+      <c r="F17" s="30" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -6190,13 +6215,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
-      <c r="F18" s="29" t="s">
-        <v>398</v>
+      <c r="F18" s="30" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -6204,13 +6229,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
-      <c r="F19" s="29" t="s">
-        <v>400</v>
+      <c r="F19" s="30" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6218,13 +6243,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
-      <c r="F20" s="29" t="s">
-        <v>402</v>
+      <c r="F20" s="30" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6232,13 +6257,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
-      <c r="F21" s="29" t="s">
-        <v>404</v>
+      <c r="F21" s="30" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6246,13 +6271,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
-      <c r="F22" s="29" t="s">
-        <v>406</v>
+      <c r="F22" s="30" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6260,13 +6285,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
-      <c r="F23" s="29" t="s">
-        <v>408</v>
+      <c r="F23" s="30" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6274,13 +6299,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
-      <c r="F24" s="29" t="s">
-        <v>410</v>
+      <c r="F24" s="30" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6288,13 +6313,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
-      <c r="F25" s="29" t="s">
-        <v>412</v>
+      <c r="F25" s="30" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6302,13 +6327,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
-      <c r="F26" s="29" t="s">
-        <v>414</v>
+      <c r="F26" s="30" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6316,13 +6341,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
-      <c r="F27" s="29" t="s">
-        <v>416</v>
+      <c r="F27" s="30" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6330,13 +6355,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
-      <c r="F28" s="29" t="s">
-        <v>418</v>
+      <c r="F28" s="30" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6344,13 +6369,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
-      <c r="F29" s="29" t="s">
-        <v>420</v>
+      <c r="F29" s="30" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6358,13 +6383,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
-      <c r="F30" s="29" t="s">
-        <v>422</v>
+      <c r="F30" s="30" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6372,13 +6397,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
-      <c r="F31" s="29" t="s">
-        <v>424</v>
+      <c r="F31" s="30" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6386,13 +6411,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
-      <c r="F32" s="29" t="s">
-        <v>426</v>
+      <c r="F32" s="30" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6400,13 +6425,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
-      <c r="F33" s="29" t="s">
-        <v>428</v>
+      <c r="F33" s="30" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6414,13 +6439,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
-      <c r="F34" s="29" t="s">
-        <v>430</v>
+      <c r="F34" s="30" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6428,13 +6453,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
-      <c r="F35" s="29" t="s">
-        <v>432</v>
+      <c r="F35" s="30" t="s">
+        <v>436</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="452">
   <si>
     <t>_id</t>
   </si>
@@ -944,73 +944,73 @@
     <t>100级链头</t>
   </si>
   <si>
-    <t>2100103,2200103,2300103,2100104,2200104,2300104</t>
+    <t>210103,220103,230103,210104,220104,230104</t>
   </si>
   <si>
     <t>100级手镯</t>
   </si>
   <si>
-    <t>2100105,2200105,2300105</t>
+    <t>210105,220105,230105</t>
   </si>
   <si>
     <t>100级戒指</t>
   </si>
   <si>
-    <t>2100106,2200106,2300106</t>
+    <t>210106,220106,230106</t>
   </si>
   <si>
     <t>100级腰鞋</t>
   </si>
   <si>
-    <t>2100107,2200107,2300107,2100108,2200108,2300108</t>
+    <t>210107,220107,230107,210108,220108,230108</t>
   </si>
   <si>
     <t>100级衣服</t>
   </si>
   <si>
-    <t>2100102,2200102,2300102</t>
+    <t>210102,220102,230102</t>
   </si>
   <si>
     <t>100级武器</t>
   </si>
   <si>
-    <t>2100101,2200101,2300101</t>
+    <t>210101,220101,230101</t>
   </si>
   <si>
     <t>110级链头</t>
   </si>
   <si>
-    <t>2100113,2200113,2300113,2100114,2200114,2300114</t>
+    <t>210113,220113,230113,210114,220114,230114</t>
   </si>
   <si>
     <t>110级手镯</t>
   </si>
   <si>
-    <t>2100115,2200115,2300115</t>
+    <t>210115,220115,230115</t>
   </si>
   <si>
     <t>110级戒指</t>
   </si>
   <si>
-    <t>2100116,2200116,2300116</t>
+    <t>210116,220116,230116</t>
   </si>
   <si>
     <t>110级腰鞋</t>
   </si>
   <si>
-    <t>2100117,2200117,2300117,2100118,2200118,2300118</t>
+    <t>210117,220117,230117,210118,220118,230118</t>
   </si>
   <si>
     <t>110级衣服</t>
   </si>
   <si>
-    <t>2100112,2200112,2300112</t>
+    <t>210112,220112,230112</t>
   </si>
   <si>
     <t>110级武器</t>
   </si>
   <si>
-    <t>2100111,2200111,2300111</t>
+    <t>210111,220111,230111</t>
   </si>
   <si>
     <t>治愈</t>
@@ -1073,7 +1073,16 @@
     <t>201028,201029,201030</t>
   </si>
   <si>
-    <t>#</t>
+    <t>背刺</t>
+  </si>
+  <si>
+    <t>201031,201032,201033</t>
+  </si>
+  <si>
+    <t>斩杀</t>
+  </si>
+  <si>
+    <t>201034,201035,201036</t>
   </si>
   <si>
     <t>狼宝宝</t>
@@ -1754,6 +1763,42 @@
   </si>
   <si>
     <t>40000030</t>
+  </si>
+  <si>
+    <t>魔瞳</t>
+  </si>
+  <si>
+    <t>40000031</t>
+  </si>
+  <si>
+    <t>血镰刀</t>
+  </si>
+  <si>
+    <t>40000032</t>
+  </si>
+  <si>
+    <t>神秘法杖</t>
+  </si>
+  <si>
+    <t>40000033</t>
+  </si>
+  <si>
+    <t>犬牙</t>
+  </si>
+  <si>
+    <t>40000034</t>
+  </si>
+  <si>
+    <t>恶魔利爪</t>
+  </si>
+  <si>
+    <t>40000035</t>
+  </si>
+  <si>
+    <t>深渊巨刃</t>
+  </si>
+  <si>
+    <t>40000036</t>
   </si>
 </sst>
 </file>
@@ -4277,7 +4322,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:F41"/>
+  <dimension ref="C3:F41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -4288,7 +4333,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -4302,7 +4347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
@@ -4316,7 +4361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="11.5" spans="1:6">
+    <row r="5" s="1" customFormat="1" ht="11.5" spans="3:6">
       <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
@@ -4330,7 +4375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C6" s="1">
         <v>21001</v>
       </c>
@@ -4344,7 +4389,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C7" s="1">
         <v>21002</v>
       </c>
@@ -4358,7 +4403,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C8" s="1">
         <v>21003</v>
       </c>
@@ -4372,7 +4417,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C9" s="1">
         <v>21004</v>
       </c>
@@ -4386,7 +4431,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C10" s="1">
         <v>21005</v>
       </c>
@@ -4400,7 +4445,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C11" s="1">
         <v>21006</v>
       </c>
@@ -4414,7 +4459,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C12" s="1">
         <v>21007</v>
       </c>
@@ -4428,7 +4473,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C13" s="1">
         <v>21008</v>
       </c>
@@ -4442,7 +4487,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C14" s="1">
         <v>21009</v>
       </c>
@@ -4456,7 +4501,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C15" s="1">
         <v>21010</v>
       </c>
@@ -4470,73 +4515,77 @@
         <v>214</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A16" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>215</v>
-      </c>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C16" s="1">
         <v>21011</v>
       </c>
-      <c r="F16" s="16"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:6">
-      <c r="A17" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>215</v>
-      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="C17" s="1">
         <v>21012</v>
       </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:6">
+      <c r="D17" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F18" s="16"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F19" s="16"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F20" s="16"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F21" s="16"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F22" s="16"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F23" s="2"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F24" s="16"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F25" s="16"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F26" s="16"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F27" s="16"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F28" s="16"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F30" s="16"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F31" s="16"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:6">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
       <c r="F32" s="16"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -4645,13 +4694,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -4659,13 +4708,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -4673,13 +4722,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -4687,13 +4736,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -4701,13 +4750,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -4715,13 +4764,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -4729,13 +4778,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -4743,13 +4792,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4757,13 +4806,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -4771,13 +4820,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -4785,13 +4834,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -4799,13 +4848,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -4813,13 +4862,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -4827,13 +4876,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -4841,13 +4890,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -4855,13 +4904,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -4869,13 +4918,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -4883,13 +4932,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -4897,13 +4946,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -4911,13 +4960,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -4925,13 +4974,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -4939,13 +4988,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -4953,13 +5002,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -4967,13 +5016,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -4981,13 +5030,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -4995,13 +5044,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -5009,13 +5058,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -5023,13 +5072,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -5037,13 +5086,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -5051,13 +5100,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -5065,13 +5114,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -5079,13 +5128,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -5093,13 +5142,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -5107,13 +5156,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -5121,13 +5170,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -5135,13 +5184,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -5149,13 +5198,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -5163,13 +5212,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="30" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -5177,13 +5226,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -5191,13 +5240,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -5205,13 +5254,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -5219,13 +5268,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -5233,13 +5282,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5247,13 +5296,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5261,13 +5310,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5275,13 +5324,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5289,13 +5338,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5303,13 +5352,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5317,13 +5366,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5331,13 +5380,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5345,13 +5394,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5359,13 +5408,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5373,13 +5422,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5387,13 +5436,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5401,13 +5450,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5415,13 +5464,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5429,13 +5478,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5443,13 +5492,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5457,13 +5506,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="30" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5471,13 +5520,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="30" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5485,13 +5534,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5499,13 +5548,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5513,13 +5562,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5527,13 +5576,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5541,13 +5590,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5555,13 +5604,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5569,13 +5618,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5583,13 +5632,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="30" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5597,13 +5646,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="30" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5611,13 +5660,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="30" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5625,13 +5674,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -5639,13 +5688,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="30" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -5727,13 +5776,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -5819,13 +5868,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5833,13 +5882,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5847,13 +5896,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5861,13 +5910,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5875,13 +5924,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5889,13 +5938,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5903,13 +5952,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5917,13 +5966,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5931,13 +5980,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -5982,7 +6031,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F35"/>
+  <dimension ref="C1:F41"/>
   <sheetFormatPr defaultColWidth="12.25" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="12.25" style="1" customWidth="1"/>
@@ -6047,13 +6096,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6061,13 +6110,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6075,13 +6124,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6089,13 +6138,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6103,13 +6152,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6117,13 +6166,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6131,13 +6180,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6145,13 +6194,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6159,13 +6208,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -6173,13 +6222,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -6187,13 +6236,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -6201,13 +6250,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -6215,13 +6264,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -6229,13 +6278,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6243,13 +6292,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6257,13 +6306,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6271,13 +6320,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6285,13 +6334,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6299,13 +6348,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6313,13 +6362,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6327,13 +6376,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6341,13 +6390,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6355,13 +6404,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6369,13 +6418,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6383,13 +6432,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6397,13 +6446,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6411,13 +6460,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6425,13 +6474,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6439,13 +6488,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6453,13 +6502,97 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>436</v>
+        <v>439</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:6">
+      <c r="C36" s="5">
+        <v>50031</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E36" s="1">
+        <v>6</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:6">
+      <c r="C37" s="5">
+        <v>50032</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="E37" s="1">
+        <v>6</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:6">
+      <c r="C38" s="5">
+        <v>50033</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="E38" s="1">
+        <v>6</v>
+      </c>
+      <c r="F38" s="30" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:6">
+      <c r="C39" s="5">
+        <v>50034</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="E39" s="1">
+        <v>6</v>
+      </c>
+      <c r="F39" s="30" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:6">
+      <c r="C40" s="5">
+        <v>50035</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E40" s="1">
+        <v>6</v>
+      </c>
+      <c r="F40" s="30" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:6">
+      <c r="C41" s="5">
+        <v>50036</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="E41" s="1">
+        <v>6</v>
+      </c>
+      <c r="F41" s="30" t="s">
+        <v>451</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DropBaseConfig.xlsx
+++ b/Excel/DropBaseConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制通用" sheetId="10" r:id="rId1"/>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="462">
   <si>
     <t>_id</t>
   </si>
@@ -503,6 +503,24 @@
     <t>40000003,40000006,40000009,40000012</t>
   </si>
   <si>
+    <t>低级珍宝</t>
+  </si>
+  <si>
+    <t>40000001,40000004,40000007,40000010,40000013,40000016,40000019,40000022,40000025,40000028,40000031,40000034</t>
+  </si>
+  <si>
+    <t>中级珍宝</t>
+  </si>
+  <si>
+    <t>40000002,40000005,40000008,40000011,40000014,40000017,40000020,40000023,40000026,40000029,40000032,40000035</t>
+  </si>
+  <si>
+    <t>高级珍宝</t>
+  </si>
+  <si>
+    <t>40000003,40000006,40000009,40000012,40000015,40000018,40000021,40000024,40000027,40000030,40000033,40000036</t>
+  </si>
+  <si>
     <t>神兵符1</t>
   </si>
   <si>
@@ -533,6 +551,12 @@
     <t>5019</t>
   </si>
   <si>
+    <t>书页</t>
+  </si>
+  <si>
+    <t>5007</t>
+  </si>
+  <si>
     <t>魂环1</t>
   </si>
   <si>
@@ -579,6 +603,12 @@
   </si>
   <si>
     <t>8008</t>
+  </si>
+  <si>
+    <t>魂环</t>
+  </si>
+  <si>
+    <t>8001,8002,8003,8004,8005,8006,8007,8008</t>
   </si>
   <si>
     <t>1级链头</t>
@@ -2550,12 +2580,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2888,12 +2918,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:F33"/>
+  <dimension ref="C1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="18"/>
     <col min="3" max="3" width="8.75" style="18" customWidth="1"/>
-    <col min="4" max="4" width="15" style="18" customWidth="1"/>
+    <col min="4" max="4" width="17.8333333333333" style="18" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="18" customWidth="1"/>
     <col min="6" max="6" width="30.75" style="19" customWidth="1"/>
     <col min="7" max="16384" width="9" style="18"/>
@@ -3045,18 +3075,60 @@
         <v>24</v>
       </c>
     </row>
+    <row r="13" customHeight="1" spans="3:6">
+      <c r="C13" s="18">
+        <v>8</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="18">
+        <v>6</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:6">
+      <c r="C14" s="18">
+        <v>9</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="18">
+        <v>6</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:6">
+      <c r="C15" s="18">
+        <v>10</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="18">
+        <v>6</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
     <row r="16" customHeight="1" spans="3:6">
       <c r="C16" s="18">
         <v>11</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E16" s="18">
         <v>5</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -3064,13 +3136,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E17" s="18">
         <v>5</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -3078,13 +3150,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E18" s="18">
         <v>5</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -3092,13 +3164,13 @@
         <v>14</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E19" s="18">
         <v>5</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -3106,13 +3178,27 @@
         <v>15</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E20" s="18">
         <v>5</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:6">
+      <c r="C21" s="18">
+        <v>16</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="18">
+        <v>5</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="22" s="18" customFormat="1" customHeight="1" spans="3:6">
@@ -3123,13 +3209,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E26" s="18">
         <v>5</v>
       </c>
       <c r="F26" s="27" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -3137,13 +3223,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E27" s="18">
         <v>5</v>
       </c>
       <c r="F27" s="27" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -3151,13 +3237,13 @@
         <v>23</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E28" s="18">
         <v>5</v>
       </c>
       <c r="F28" s="27" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -3165,13 +3251,13 @@
         <v>24</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E29" s="18">
         <v>5</v>
       </c>
       <c r="F29" s="27" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -3179,13 +3265,13 @@
         <v>25</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E30" s="18">
         <v>5</v>
       </c>
       <c r="F30" s="27" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -3193,13 +3279,13 @@
         <v>26</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E31" s="18">
         <v>5</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -3207,13 +3293,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="E32" s="18">
         <v>5</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -3221,13 +3307,27 @@
         <v>28</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E33" s="18">
         <v>5</v>
       </c>
       <c r="F33" s="27" t="s">
-        <v>50</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:6">
+      <c r="C34" s="18">
+        <v>29</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="18">
+        <v>5</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3303,13 +3403,13 @@
         <v>20001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -3317,13 +3417,13 @@
         <v>20002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -3331,13 +3431,13 @@
         <v>20003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -3345,13 +3445,13 @@
         <v>20004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -3359,13 +3459,13 @@
         <v>20005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -3373,13 +3473,13 @@
         <v>20006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -3387,13 +3487,13 @@
         <v>20007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -3401,13 +3501,13 @@
         <v>20008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -3415,13 +3515,13 @@
         <v>20009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -3429,13 +3529,13 @@
         <v>20010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -3443,13 +3543,13 @@
         <v>20011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -3457,13 +3557,13 @@
         <v>20012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
       <c r="F17" s="29" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -3471,13 +3571,13 @@
         <v>20013</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -3485,13 +3585,13 @@
         <v>20014</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -3499,13 +3599,13 @@
         <v>20015</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -3513,13 +3613,13 @@
         <v>20016</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -3527,13 +3627,13 @@
         <v>20017</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -3541,13 +3641,13 @@
         <v>20018</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -3555,13 +3655,13 @@
         <v>20019</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -3569,13 +3669,13 @@
         <v>20020</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -3583,13 +3683,13 @@
         <v>20021</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -3597,13 +3697,13 @@
         <v>20022</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -3611,13 +3711,13 @@
         <v>20023</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -3625,13 +3725,13 @@
         <v>20024</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
       <c r="F29" s="29" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -3639,13 +3739,13 @@
         <v>20025</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -3653,13 +3753,13 @@
         <v>20026</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -3667,13 +3767,13 @@
         <v>20027</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -3681,13 +3781,13 @@
         <v>20028</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -3695,13 +3795,13 @@
         <v>20029</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -3709,13 +3809,13 @@
         <v>20030</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="F35" s="29" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -3723,13 +3823,13 @@
         <v>20031</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -3737,13 +3837,13 @@
         <v>20032</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E37" s="1">
         <v>2</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -3751,13 +3851,13 @@
         <v>20033</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -3765,13 +3865,13 @@
         <v>20034</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -3779,13 +3879,13 @@
         <v>20035</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -3793,13 +3893,13 @@
         <v>20036</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E41" s="1">
         <v>2</v>
       </c>
       <c r="F41" s="29" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -3807,13 +3907,13 @@
         <v>20037</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
       </c>
       <c r="F42" s="28" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -3821,13 +3921,13 @@
         <v>20038</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
       </c>
       <c r="F43" s="28" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -3835,13 +3935,13 @@
         <v>20039</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E44" s="1">
         <v>2</v>
       </c>
       <c r="F44" s="28" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -3849,13 +3949,13 @@
         <v>20040</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E45" s="1">
         <v>2</v>
       </c>
       <c r="F45" s="28" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -3863,13 +3963,13 @@
         <v>20041</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E46" s="1">
         <v>2</v>
       </c>
       <c r="F46" s="28" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -3877,13 +3977,13 @@
         <v>20042</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E47" s="1">
         <v>2</v>
       </c>
       <c r="F47" s="29" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -3891,13 +3991,13 @@
         <v>20043</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E48" s="1">
         <v>2</v>
       </c>
       <c r="F48" s="29" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -3905,13 +4005,13 @@
         <v>20044</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E49" s="1">
         <v>2</v>
       </c>
       <c r="F49" s="29" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -3919,13 +4019,13 @@
         <v>20045</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E50" s="1">
         <v>2</v>
       </c>
       <c r="F50" s="29" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -3933,13 +4033,13 @@
         <v>20046</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E51" s="1">
         <v>2</v>
       </c>
       <c r="F51" s="29" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -3947,13 +4047,13 @@
         <v>20047</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E52" s="1">
         <v>2</v>
       </c>
       <c r="F52" s="29" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -3961,13 +4061,13 @@
         <v>20048</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E53" s="1">
         <v>2</v>
       </c>
       <c r="F53" s="29" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -3975,13 +4075,13 @@
         <v>20049</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E54" s="1">
         <v>2</v>
       </c>
       <c r="F54" s="29" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -3989,13 +4089,13 @@
         <v>20050</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="E55" s="1">
         <v>2</v>
       </c>
       <c r="F55" s="29" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -4003,13 +4103,13 @@
         <v>20051</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="E56" s="1">
         <v>2</v>
       </c>
       <c r="F56" s="29" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -4017,13 +4117,13 @@
         <v>20052</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E57" s="1">
         <v>2</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -4031,13 +4131,13 @@
         <v>20053</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E58" s="1">
         <v>2</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -4045,13 +4145,13 @@
         <v>20054</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E59" s="1">
         <v>2</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -4059,13 +4159,13 @@
         <v>20055</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E60" s="1">
         <v>2</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -4073,13 +4173,13 @@
         <v>20056</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E61" s="1">
         <v>2</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -4087,13 +4187,13 @@
         <v>20057</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="E62" s="1">
         <v>2</v>
       </c>
       <c r="F62" s="29" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -4101,13 +4201,13 @@
         <v>20058</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E63" s="1">
         <v>2</v>
       </c>
       <c r="F63" s="29" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -4115,13 +4215,13 @@
         <v>20059</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E64" s="1">
         <v>2</v>
       </c>
       <c r="F64" s="29" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -4129,13 +4229,13 @@
         <v>20060</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E65" s="1">
         <v>2</v>
       </c>
       <c r="F65" s="29" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -4143,13 +4243,13 @@
         <v>20061</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E66" s="1">
         <v>2</v>
       </c>
       <c r="F66" s="29" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -4157,13 +4257,13 @@
         <v>20062</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="E67" s="1">
         <v>2</v>
       </c>
       <c r="F67" s="29" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -4171,13 +4271,13 @@
         <v>20063</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="E68" s="1">
         <v>2</v>
       </c>
       <c r="F68" s="29" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -4185,13 +4285,13 @@
         <v>20064</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E69" s="1">
         <v>2</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -4199,13 +4299,13 @@
         <v>20065</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="E70" s="1">
         <v>2</v>
       </c>
       <c r="F70" s="29" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -4213,13 +4313,13 @@
         <v>20066</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E71" s="1">
         <v>2</v>
       </c>
       <c r="F71" s="29" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -4227,13 +4327,13 @@
         <v>20067</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E72" s="1">
         <v>2</v>
       </c>
       <c r="F72" s="29" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -4241,13 +4341,13 @@
         <v>20068</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E73" s="1">
         <v>2</v>
       </c>
       <c r="F73" s="29" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -4255,13 +4355,13 @@
         <v>20069</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E74" s="1">
         <v>2</v>
       </c>
       <c r="F74" s="29" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -4269,13 +4369,13 @@
         <v>20070</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E75" s="1">
         <v>2</v>
       </c>
       <c r="F75" s="29" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -4283,13 +4383,13 @@
         <v>20071</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="E76" s="1">
         <v>2</v>
       </c>
       <c r="F76" s="29" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -4297,13 +4397,13 @@
         <v>20072</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E77" s="1">
         <v>2</v>
       </c>
       <c r="F77" s="29" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -4380,13 +4480,13 @@
         <v>21001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4394,13 +4494,13 @@
         <v>21002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4408,13 +4508,13 @@
         <v>21003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4422,13 +4522,13 @@
         <v>21004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4436,13 +4536,13 @@
         <v>21005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4450,13 +4550,13 @@
         <v>21006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4464,13 +4564,13 @@
         <v>21007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4478,13 +4578,13 @@
         <v>21008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4492,13 +4592,13 @@
         <v>21009</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4506,13 +4606,13 @@
         <v>21010</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4520,13 +4620,13 @@
         <v>21011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4534,13 +4634,13 @@
         <v>21012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -4694,13 +4794,13 @@
         <v>180001</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E6" s="6">
         <v>18</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:6">
@@ -4708,13 +4808,13 @@
         <v>180002</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E7" s="6">
         <v>18</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:6">
@@ -4722,13 +4822,13 @@
         <v>180003</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="E8" s="6">
         <v>18</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:6">
@@ -4736,13 +4836,13 @@
         <v>180004</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E9" s="6">
         <v>18</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:6">
@@ -4750,13 +4850,13 @@
         <v>180005</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="E10" s="6">
         <v>18</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:6">
@@ -4764,13 +4864,13 @@
         <v>180006</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E11" s="6">
         <v>18</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:6">
@@ -4778,13 +4878,13 @@
         <v>180007</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="E12" s="6">
         <v>18</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:6">
@@ -4792,13 +4892,13 @@
         <v>180008</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E13" s="6">
         <v>18</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -4806,13 +4906,13 @@
         <v>180009</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="E14" s="6">
         <v>18</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -4820,13 +4920,13 @@
         <v>180010</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="E15" s="6">
         <v>18</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -4834,13 +4934,13 @@
         <v>180011</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="E16" s="6">
         <v>18</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -4848,13 +4948,13 @@
         <v>180012</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="E17" s="6">
         <v>18</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -4862,13 +4962,13 @@
         <v>180013</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="E18" s="6">
         <v>18</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -4876,13 +4976,13 @@
         <v>180014</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="E19" s="6">
         <v>18</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -4890,13 +4990,13 @@
         <v>180015</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="E20" s="6">
         <v>18</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -4904,13 +5004,13 @@
         <v>180016</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="E21" s="6">
         <v>18</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -4918,13 +5018,13 @@
         <v>180017</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="E22" s="6">
         <v>18</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -4932,13 +5032,13 @@
         <v>180018</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="E23" s="6">
         <v>18</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="3:6">
@@ -4946,13 +5046,13 @@
         <v>180019</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="E24" s="6">
         <v>18</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:6">
@@ -4960,13 +5060,13 @@
         <v>180020</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="E25" s="6">
         <v>18</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:6">
@@ -4974,13 +5074,13 @@
         <v>180021</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="E26" s="6">
         <v>18</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:6">
@@ -4988,13 +5088,13 @@
         <v>180022</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E27" s="6">
         <v>18</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:6">
@@ -5002,13 +5102,13 @@
         <v>180023</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="3:6">
@@ -5016,13 +5116,13 @@
         <v>180024</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="E29" s="6">
         <v>18</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="3:6">
@@ -5030,13 +5130,13 @@
         <v>180025</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="E30" s="6">
         <v>18</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:6">
@@ -5044,13 +5144,13 @@
         <v>180026</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="E31" s="6">
         <v>18</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:6">
@@ -5058,13 +5158,13 @@
         <v>180027</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="E32" s="6">
         <v>18</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -5072,13 +5172,13 @@
         <v>180028</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="E33" s="6">
         <v>18</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -5086,13 +5186,13 @@
         <v>180029</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="E34" s="6">
         <v>18</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -5100,13 +5200,13 @@
         <v>180030</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="E35" s="6">
         <v>18</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -5114,13 +5214,13 @@
         <v>180031</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -5128,13 +5228,13 @@
         <v>180032</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="E37" s="6">
         <v>18</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -5142,13 +5242,13 @@
         <v>180033</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="E38" s="6">
         <v>18</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -5156,13 +5256,13 @@
         <v>180034</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E39" s="6">
         <v>18</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -5170,13 +5270,13 @@
         <v>180035</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="E40" s="6">
         <v>18</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -5184,13 +5284,13 @@
         <v>180036</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E41" s="6">
         <v>18</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:6">
@@ -5198,13 +5298,13 @@
         <v>180037</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="E42" s="6">
         <v>18</v>
       </c>
       <c r="F42" s="30" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:6">
@@ -5212,13 +5312,13 @@
         <v>180038</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E43" s="6">
         <v>18</v>
       </c>
       <c r="F43" s="30" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:6">
@@ -5226,13 +5326,13 @@
         <v>180039</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="E44" s="6">
         <v>18</v>
       </c>
       <c r="F44" s="30" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:6">
@@ -5240,13 +5340,13 @@
         <v>180040</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E45" s="6">
         <v>18</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="3:6">
@@ -5254,13 +5354,13 @@
         <v>180041</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="E46" s="6">
         <v>18</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="3:6">
@@ -5268,13 +5368,13 @@
         <v>180042</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="E47" s="6">
         <v>18</v>
       </c>
       <c r="F47" s="30" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:6">
@@ -5282,13 +5382,13 @@
         <v>180043</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="E48" s="6">
         <v>18</v>
       </c>
       <c r="F48" s="30" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:6">
@@ -5296,13 +5396,13 @@
         <v>180044</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="E49" s="6">
         <v>18</v>
       </c>
       <c r="F49" s="30" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:6">
@@ -5310,13 +5410,13 @@
         <v>180045</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="E50" s="6">
         <v>18</v>
       </c>
       <c r="F50" s="30" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:6">
@@ -5324,13 +5424,13 @@
         <v>180046</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="E51" s="6">
         <v>18</v>
       </c>
       <c r="F51" s="30" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:6">
@@ -5338,13 +5438,13 @@
         <v>180047</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="E52" s="6">
         <v>18</v>
       </c>
       <c r="F52" s="30" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:6">
@@ -5352,13 +5452,13 @@
         <v>180048</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="E53" s="6">
         <v>18</v>
       </c>
       <c r="F53" s="30" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:6">
@@ -5366,13 +5466,13 @@
         <v>180049</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E54" s="6">
         <v>18</v>
       </c>
       <c r="F54" s="30" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:6">
@@ -5380,13 +5480,13 @@
         <v>180050</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="E55" s="6">
         <v>18</v>
       </c>
       <c r="F55" s="30" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:6">
@@ -5394,13 +5494,13 @@
         <v>180051</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="E56" s="6">
         <v>18</v>
       </c>
       <c r="F56" s="30" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:6">
@@ -5408,13 +5508,13 @@
         <v>180052</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="E57" s="6">
         <v>18</v>
       </c>
       <c r="F57" s="30" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:6">
@@ -5422,13 +5522,13 @@
         <v>180053</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="E58" s="6">
         <v>18</v>
       </c>
       <c r="F58" s="30" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="3:6">
@@ -5436,13 +5536,13 @@
         <v>180054</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="E59" s="6">
         <v>18</v>
       </c>
       <c r="F59" s="30" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:6">
@@ -5450,13 +5550,13 @@
         <v>180055</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E60" s="6">
         <v>18</v>
       </c>
       <c r="F60" s="30" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:6">
@@ -5464,13 +5564,13 @@
         <v>180056</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="E61" s="6">
         <v>18</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:6">
@@ -5478,13 +5578,13 @@
         <v>180057</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E62" s="6">
         <v>18</v>
       </c>
       <c r="F62" s="30" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:6">
@@ -5492,13 +5592,13 @@
         <v>180058</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E63" s="6">
         <v>18</v>
       </c>
       <c r="F63" s="30" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:6">
@@ -5506,13 +5606,13 @@
         <v>180059</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E64" s="6">
         <v>18</v>
       </c>
       <c r="F64" s="30" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="3:6">
@@ -5520,13 +5620,13 @@
         <v>180060</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="E65" s="6">
         <v>18</v>
       </c>
       <c r="F65" s="30" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:6">
@@ -5534,13 +5634,13 @@
         <v>180061</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="E66" s="6">
         <v>18</v>
       </c>
       <c r="F66" s="30" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:6">
@@ -5548,13 +5648,13 @@
         <v>180062</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="E67" s="6">
         <v>18</v>
       </c>
       <c r="F67" s="30" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:6">
@@ -5562,13 +5662,13 @@
         <v>180063</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="E68" s="6">
         <v>18</v>
       </c>
       <c r="F68" s="30" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:6">
@@ -5576,13 +5676,13 @@
         <v>180064</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="E69" s="6">
         <v>18</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:6">
@@ -5590,13 +5690,13 @@
         <v>180065</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="E70" s="6">
         <v>18</v>
       </c>
       <c r="F70" s="30" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:6">
@@ -5604,13 +5704,13 @@
         <v>180066</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="E71" s="6">
         <v>18</v>
       </c>
       <c r="F71" s="30" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:6">
@@ -5618,13 +5718,13 @@
         <v>180067</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="E72" s="6">
         <v>18</v>
       </c>
       <c r="F72" s="30" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:6">
@@ -5632,13 +5732,13 @@
         <v>180068</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="E73" s="6">
         <v>18</v>
       </c>
       <c r="F73" s="30" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:6">
@@ -5646,13 +5746,13 @@
         <v>180069</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="E74" s="6">
         <v>18</v>
       </c>
       <c r="F74" s="30" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:6">
@@ -5660,13 +5760,13 @@
         <v>180070</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E75" s="6">
         <v>18</v>
       </c>
       <c r="F75" s="30" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:6">
@@ -5674,13 +5774,13 @@
         <v>180071</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="E76" s="6">
         <v>18</v>
       </c>
       <c r="F76" s="30" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:6">
@@ -5688,13 +5788,13 @@
         <v>180072</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="E77" s="6">
         <v>18</v>
       </c>
       <c r="F77" s="30" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
@@ -5776,13 +5876,13 @@
         <v>30001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="E6" s="6">
         <v>3</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="3:3">
@@ -5868,13 +5968,13 @@
         <v>40001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5882,13 +5982,13 @@
         <v>40002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5896,13 +5996,13 @@
         <v>40003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5910,13 +6010,13 @@
         <v>40004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5924,13 +6024,13 @@
         <v>40005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5938,13 +6038,13 @@
         <v>40006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5952,13 +6052,13 @@
         <v>40007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -5966,13 +6066,13 @@
         <v>40008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:6">
@@ -5980,13 +6080,13 @@
         <v>40009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="6:6">
@@ -6096,13 +6196,13 @@
         <v>50001</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="F6" s="30" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6110,13 +6210,13 @@
         <v>50002</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="F7" s="30" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6124,13 +6224,13 @@
         <v>50003</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6138,13 +6238,13 @@
         <v>50004</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6152,13 +6252,13 @@
         <v>50005</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="F10" s="30" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6166,13 +6266,13 @@
         <v>50006</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="F11" s="30" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6180,13 +6280,13 @@
         <v>50007</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="F12" s="30" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6194,13 +6294,13 @@
         <v>50008</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="F13" s="30" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6208,13 +6308,13 @@
         <v>50009</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:6">
@@ -6222,13 +6322,13 @@
         <v>50010</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="30" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:6">
@@ -6236,13 +6336,13 @@
         <v>50011</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="F16" s="30" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:6">
@@ -6250,13 +6350,13 @@
         <v>50012</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="30" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:6">
@@ -6264,13 +6364,13 @@
         <v>50013</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="E18" s="1">
         <v>6</v>
       </c>
       <c r="F18" s="30" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:6">
@@ -6278,13 +6378,13 @@
         <v>50014</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E19" s="1">
         <v>6</v>
       </c>
       <c r="F19" s="30" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:6">
@@ -6292,13 +6392,13 @@
         <v>50015</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="E20" s="1">
         <v>6</v>
       </c>
       <c r="F20" s="30" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:6">
@@ -6306,13 +6406,13 @@
         <v>50016</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="E21" s="1">
         <v>6</v>
       </c>
       <c r="F21" s="30" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:6">
@@ -6320,13 +6420,13 @@
         <v>50017</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="E22" s="1">
         <v>6</v>
       </c>
       <c r="F22" s="30" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="3:6">
@@ -6334,13 +6434,13 @@
         <v>50018</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="E23" s="1">
         <v>6</v>
       </c>
       <c r="F23" s="30" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6348,13 +6448,13 @@
         <v>50019</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="E24" s="1">
         <v>6</v>
       </c>
       <c r="F24" s="30" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6362,13 +6462,13 @@
         <v>50020</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="E25" s="1">
         <v>6</v>
       </c>
       <c r="F25" s="30" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6376,13 +6476,13 @@
         <v>50021</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="E26" s="1">
         <v>6</v>
       </c>
       <c r="F26" s="30" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6390,13 +6490,13 @@
         <v>50022</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="E27" s="1">
         <v>6</v>
       </c>
       <c r="F27" s="30" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6404,13 +6504,13 @@
         <v>50023</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="E28" s="1">
         <v>6</v>
       </c>
       <c r="F28" s="30" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6418,13 +6518,13 @@
         <v>50024</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="E29" s="1">
         <v>6</v>
       </c>
       <c r="F29" s="30" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6432,13 +6532,13 @@
         <v>50025</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="E30" s="1">
         <v>6</v>
       </c>
       <c r="F30" s="30" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6446,13 +6546,13 @@
         <v>50026</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="E31" s="1">
         <v>6</v>
       </c>
       <c r="F31" s="30" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:6">
@@ -6460,13 +6560,13 @@
         <v>50027</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="E32" s="1">
         <v>6</v>
       </c>
       <c r="F32" s="30" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:6">
@@ -6474,13 +6574,13 @@
         <v>50028</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="E33" s="1">
         <v>6</v>
       </c>
       <c r="F33" s="30" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:6">
@@ -6488,13 +6588,13 @@
         <v>50029</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="E34" s="1">
         <v>6</v>
       </c>
       <c r="F34" s="30" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="3:6">
@@ -6502,13 +6602,13 @@
         <v>50030</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="E35" s="1">
         <v>6</v>
       </c>
       <c r="F35" s="30" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:6">
@@ -6516,13 +6616,13 @@
         <v>50031</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="E36" s="1">
         <v>6</v>
       </c>
       <c r="F36" s="30" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:6">
@@ -6530,13 +6630,13 @@
         <v>50032</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="E37" s="1">
         <v>6</v>
       </c>
       <c r="F37" s="30" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:6">
@@ -6544,13 +6644,13 @@
         <v>50033</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="E38" s="1">
         <v>6</v>
       </c>
       <c r="F38" s="30" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:6">
@@ -6558,13 +6658,13 @@
         <v>50034</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="E39" s="1">
         <v>6</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:6">
@@ -6572,13 +6672,13 @@
         <v>50035</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="E40" s="1">
         <v>6</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="3:6">
@@ -6586,13 +6686,13 @@
         <v>50036</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="E41" s="1">
         <v>6</v>
       </c>
       <c r="F41" s="30" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
